--- a/2026/GALERIA MITRE/Septiembre/Septiembre MITRE.xlsx
+++ b/2026/GALERIA MITRE/Septiembre/Septiembre MITRE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B759F684-8407-450A-A485-F4604917FCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8616A2-FA23-427D-AEFB-977BD72DF709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="213">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -669,6 +669,12 @@
   </si>
   <si>
     <t>Debito 09/09</t>
+  </si>
+  <si>
+    <t>Local 10 transfirio $162.877 el 26/09</t>
+  </si>
+  <si>
+    <t>Local 10</t>
   </si>
 </sst>
 </file>
@@ -859,7 +865,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -953,6 +959,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1316,7 +1328,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1564,6 +1576,13 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1714,8 +1733,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2109,28 +2126,28 @@
       <c r="D3" s="123"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="185" t="s">
+      <c r="A4" s="192" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="185"/>
+      <c r="B4" s="192"/>
       <c r="C4" s="124"/>
       <c r="D4" s="124"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="185"/>
-      <c r="B5" s="185"/>
+      <c r="A5" s="192"/>
+      <c r="B5" s="192"/>
       <c r="C5" s="124"/>
       <c r="D5" s="124"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="185"/>
-      <c r="B6" s="185"/>
+      <c r="A6" s="192"/>
+      <c r="B6" s="192"/>
       <c r="C6" s="124"/>
       <c r="D6" s="124"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="185"/>
-      <c r="B7" s="185"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="192"/>
       <c r="C7" s="124"/>
       <c r="D7" s="124"/>
     </row>
@@ -2142,7 +2159,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="61"/>
-      <c r="B9" s="180" t="s">
+      <c r="B9" s="187" t="s">
         <v>196</v>
       </c>
       <c r="C9" s="61"/>
@@ -2150,13 +2167,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
-      <c r="B10" s="180"/>
+      <c r="B10" s="187"/>
       <c r="C10" s="61"/>
       <c r="D10" s="61"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="61"/>
-      <c r="B11" s="180"/>
+      <c r="B11" s="187"/>
       <c r="C11" s="61"/>
       <c r="D11" s="61"/>
     </row>
@@ -2173,30 +2190,30 @@
       <c r="D13" s="61"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="185" t="s">
+      <c r="A14" s="192" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
+      <c r="B14" s="192"/>
+      <c r="C14" s="192"/>
+      <c r="D14" s="192"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="185"/>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="185"/>
+      <c r="A15" s="192"/>
+      <c r="B15" s="192"/>
+      <c r="C15" s="192"/>
+      <c r="D15" s="192"/>
     </row>
     <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="185"/>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
+      <c r="A16" s="192"/>
+      <c r="B16" s="192"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
     </row>
     <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="185"/>
-      <c r="B17" s="185"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
+      <c r="A17" s="192"/>
+      <c r="B17" s="192"/>
+      <c r="C17" s="192"/>
+      <c r="D17" s="192"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="61"/>
@@ -2239,10 +2256,10 @@
       <c r="F22" s="118"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="178" t="s">
+      <c r="A23" s="185" t="s">
         <v>198</v>
       </c>
-      <c r="B23" s="179"/>
+      <c r="B23" s="186"/>
       <c r="C23" s="160">
         <v>1322255.05</v>
       </c>
@@ -2289,10 +2306,10 @@
       <c r="F26" s="118"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="178" t="s">
+      <c r="A27" s="185" t="s">
         <v>199</v>
       </c>
-      <c r="B27" s="179"/>
+      <c r="B27" s="186"/>
       <c r="C27" s="160">
         <v>941573.23</v>
       </c>
@@ -2381,10 +2398,10 @@
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="181" t="s">
+      <c r="A36" s="188" t="s">
         <v>200</v>
       </c>
-      <c r="B36" s="182"/>
+      <c r="B36" s="189"/>
       <c r="C36" s="160">
         <v>650000</v>
       </c>
@@ -2394,10 +2411,10 @@
       <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="181" t="s">
+      <c r="A37" s="188" t="s">
         <v>178</v>
       </c>
-      <c r="B37" s="182"/>
+      <c r="B37" s="189"/>
       <c r="C37" s="81">
         <v>100000</v>
       </c>
@@ -2407,11 +2424,11 @@
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="181" t="s">
+      <c r="A38" s="188" t="s">
         <v>208</v>
       </c>
-      <c r="B38" s="182"/>
-      <c r="C38" s="227">
+      <c r="B38" s="189"/>
+      <c r="C38" s="177">
         <v>100000</v>
       </c>
       <c r="D38" s="75" t="s">
@@ -2420,11 +2437,11 @@
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="181" t="s">
+      <c r="A39" s="188" t="s">
         <v>207</v>
       </c>
-      <c r="B39" s="182"/>
-      <c r="C39" s="228">
+      <c r="B39" s="189"/>
+      <c r="C39" s="178">
         <v>200000</v>
       </c>
       <c r="D39" s="75" t="s">
@@ -2452,10 +2469,10 @@
       <c r="D41" s="29"/>
     </row>
     <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="181" t="s">
+      <c r="A42" s="188" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="182"/>
+      <c r="B42" s="189"/>
       <c r="C42" s="161">
         <v>111108.81</v>
       </c>
@@ -2494,10 +2511,10 @@
       <c r="F45" s="72"/>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="181" t="s">
+      <c r="A46" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="B46" s="182"/>
+      <c r="B46" s="189"/>
       <c r="C46" s="81">
         <v>11596.99</v>
       </c>
@@ -2507,10 +2524,10 @@
       <c r="F46" s="72"/>
     </row>
     <row r="47" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="181" t="s">
+      <c r="A47" s="188" t="s">
         <v>175</v>
       </c>
-      <c r="B47" s="182"/>
+      <c r="B47" s="189"/>
       <c r="C47" s="81">
         <v>11930.96</v>
       </c>
@@ -2582,7 +2599,7 @@
         <v>127</v>
       </c>
       <c r="B53" s="71"/>
-      <c r="C53" s="227">
+      <c r="C53" s="177">
         <v>363925.4</v>
       </c>
       <c r="D53" s="77" t="s">
@@ -2594,7 +2611,7 @@
         <v>126</v>
       </c>
       <c r="B54" s="71"/>
-      <c r="C54" s="227">
+      <c r="C54" s="177">
         <v>394235.68</v>
       </c>
       <c r="D54" s="77" t="s">
@@ -2630,7 +2647,7 @@
         <v>128</v>
       </c>
       <c r="B57" s="71"/>
-      <c r="C57" s="227">
+      <c r="C57" s="177">
         <v>36551.61</v>
       </c>
       <c r="D57" s="77" t="s">
@@ -2669,11 +2686,11 @@
       <c r="D60" s="53"/>
     </row>
     <row r="61" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="181" t="s">
+      <c r="A61" s="188" t="s">
         <v>203</v>
       </c>
-      <c r="B61" s="182"/>
-      <c r="C61" s="227">
+      <c r="B61" s="189"/>
+      <c r="C61" s="177">
         <v>202000</v>
       </c>
       <c r="D61" s="75" t="s">
@@ -2684,10 +2701,10 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="181" t="s">
+      <c r="A62" s="188" t="s">
         <v>181</v>
       </c>
-      <c r="B62" s="182"/>
+      <c r="B62" s="189"/>
       <c r="C62" s="81">
         <v>650000</v>
       </c>
@@ -2697,10 +2714,10 @@
       <c r="F62" s="22"/>
     </row>
     <row r="63" spans="1:7" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="181" t="s">
+      <c r="A63" s="188" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="182"/>
+      <c r="B63" s="189"/>
       <c r="C63" s="81">
         <v>166345.46</v>
       </c>
@@ -2710,11 +2727,11 @@
       <c r="F63" s="22"/>
     </row>
     <row r="64" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="181" t="s">
+      <c r="A64" s="188" t="s">
         <v>204</v>
       </c>
-      <c r="B64" s="182"/>
-      <c r="C64" s="227">
+      <c r="B64" s="189"/>
+      <c r="C64" s="177">
         <v>128900</v>
       </c>
       <c r="D64" s="75" t="s">
@@ -2743,10 +2760,10 @@
       <c r="D66" s="53"/>
     </row>
     <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="178" t="s">
+      <c r="A67" s="185" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="179"/>
+      <c r="B67" s="186"/>
       <c r="C67" s="81">
         <v>75000</v>
       </c>
@@ -2780,11 +2797,11 @@
       <c r="D70" s="59"/>
     </row>
     <row r="71" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="186" t="s">
+      <c r="A71" s="193" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="187"/>
-      <c r="C71" s="188"/>
+      <c r="B71" s="194"/>
+      <c r="C71" s="195"/>
       <c r="D71" s="60">
         <v>1000000</v>
       </c>
@@ -2831,14 +2848,14 @@
       <c r="D76" s="66"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="178"/>
-      <c r="B77" s="179"/>
+      <c r="A77" s="185"/>
+      <c r="B77" s="186"/>
       <c r="C77" s="54"/>
       <c r="D77" s="52"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="178"/>
-      <c r="B78" s="179"/>
+      <c r="A78" s="185"/>
+      <c r="B78" s="186"/>
       <c r="C78" s="54"/>
       <c r="D78" s="52"/>
     </row>
@@ -2947,132 +2964,132 @@
       <c r="D90" s="61"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="183" t="s">
+      <c r="A93" s="190" t="s">
         <v>190</v>
       </c>
-      <c r="B93" s="184"/>
-      <c r="C93" s="184"/>
-      <c r="D93" s="184"/>
+      <c r="B93" s="191"/>
+      <c r="C93" s="191"/>
+      <c r="D93" s="191"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="184"/>
-      <c r="B94" s="184"/>
-      <c r="C94" s="184"/>
-      <c r="D94" s="184"/>
+      <c r="A94" s="191"/>
+      <c r="B94" s="191"/>
+      <c r="C94" s="191"/>
+      <c r="D94" s="191"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="184"/>
-      <c r="B95" s="184"/>
-      <c r="C95" s="184"/>
-      <c r="D95" s="184"/>
+      <c r="A95" s="191"/>
+      <c r="B95" s="191"/>
+      <c r="C95" s="191"/>
+      <c r="D95" s="191"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="184"/>
-      <c r="B96" s="184"/>
-      <c r="C96" s="184"/>
-      <c r="D96" s="184"/>
+      <c r="A96" s="191"/>
+      <c r="B96" s="191"/>
+      <c r="C96" s="191"/>
+      <c r="D96" s="191"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="184"/>
-      <c r="B97" s="184"/>
-      <c r="C97" s="184"/>
-      <c r="D97" s="184"/>
+      <c r="A97" s="191"/>
+      <c r="B97" s="191"/>
+      <c r="C97" s="191"/>
+      <c r="D97" s="191"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="184"/>
-      <c r="B98" s="184"/>
-      <c r="C98" s="184"/>
-      <c r="D98" s="184"/>
+      <c r="A98" s="191"/>
+      <c r="B98" s="191"/>
+      <c r="C98" s="191"/>
+      <c r="D98" s="191"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="184"/>
-      <c r="B99" s="184"/>
-      <c r="C99" s="184"/>
-      <c r="D99" s="184"/>
+      <c r="A99" s="191"/>
+      <c r="B99" s="191"/>
+      <c r="C99" s="191"/>
+      <c r="D99" s="191"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="184"/>
-      <c r="B100" s="184"/>
-      <c r="C100" s="184"/>
-      <c r="D100" s="184"/>
+      <c r="A100" s="191"/>
+      <c r="B100" s="191"/>
+      <c r="C100" s="191"/>
+      <c r="D100" s="191"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="184"/>
-      <c r="B101" s="184"/>
-      <c r="C101" s="184"/>
-      <c r="D101" s="184"/>
+      <c r="A101" s="191"/>
+      <c r="B101" s="191"/>
+      <c r="C101" s="191"/>
+      <c r="D101" s="191"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="184"/>
-      <c r="B102" s="184"/>
-      <c r="C102" s="184"/>
-      <c r="D102" s="184"/>
+      <c r="A102" s="191"/>
+      <c r="B102" s="191"/>
+      <c r="C102" s="191"/>
+      <c r="D102" s="191"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="184"/>
-      <c r="B103" s="184"/>
-      <c r="C103" s="184"/>
-      <c r="D103" s="184"/>
+      <c r="A103" s="191"/>
+      <c r="B103" s="191"/>
+      <c r="C103" s="191"/>
+      <c r="D103" s="191"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="184"/>
-      <c r="B104" s="184"/>
-      <c r="C104" s="184"/>
-      <c r="D104" s="184"/>
+      <c r="A104" s="191"/>
+      <c r="B104" s="191"/>
+      <c r="C104" s="191"/>
+      <c r="D104" s="191"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="184"/>
-      <c r="B105" s="184"/>
-      <c r="C105" s="184"/>
-      <c r="D105" s="184"/>
+      <c r="A105" s="191"/>
+      <c r="B105" s="191"/>
+      <c r="C105" s="191"/>
+      <c r="D105" s="191"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="184"/>
-      <c r="B106" s="184"/>
-      <c r="C106" s="184"/>
-      <c r="D106" s="184"/>
+      <c r="A106" s="191"/>
+      <c r="B106" s="191"/>
+      <c r="C106" s="191"/>
+      <c r="D106" s="191"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="184"/>
-      <c r="B107" s="184"/>
-      <c r="C107" s="184"/>
-      <c r="D107" s="184"/>
+      <c r="A107" s="191"/>
+      <c r="B107" s="191"/>
+      <c r="C107" s="191"/>
+      <c r="D107" s="191"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="184"/>
-      <c r="B108" s="184"/>
-      <c r="C108" s="184"/>
-      <c r="D108" s="184"/>
+      <c r="A108" s="191"/>
+      <c r="B108" s="191"/>
+      <c r="C108" s="191"/>
+      <c r="D108" s="191"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="184"/>
-      <c r="B109" s="184"/>
-      <c r="C109" s="184"/>
-      <c r="D109" s="184"/>
+      <c r="A109" s="191"/>
+      <c r="B109" s="191"/>
+      <c r="C109" s="191"/>
+      <c r="D109" s="191"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="184"/>
-      <c r="B110" s="184"/>
-      <c r="C110" s="184"/>
-      <c r="D110" s="184"/>
+      <c r="A110" s="191"/>
+      <c r="B110" s="191"/>
+      <c r="C110" s="191"/>
+      <c r="D110" s="191"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="184"/>
-      <c r="B111" s="184"/>
-      <c r="C111" s="184"/>
-      <c r="D111" s="184"/>
+      <c r="A111" s="191"/>
+      <c r="B111" s="191"/>
+      <c r="C111" s="191"/>
+      <c r="D111" s="191"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="184"/>
-      <c r="B112" s="184"/>
-      <c r="C112" s="184"/>
-      <c r="D112" s="184"/>
+      <c r="A112" s="191"/>
+      <c r="B112" s="191"/>
+      <c r="C112" s="191"/>
+      <c r="D112" s="191"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="184"/>
-      <c r="B113" s="184"/>
-      <c r="C113" s="184"/>
-      <c r="D113" s="184"/>
+      <c r="A113" s="191"/>
+      <c r="B113" s="191"/>
+      <c r="C113" s="191"/>
+      <c r="D113" s="191"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
@@ -3204,14 +3221,14 @@
       <c r="D131" s="93"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="177" t="s">
+      <c r="A132" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="B132" s="177"/>
+      <c r="B132" s="184"/>
     </row>
     <row r="133" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="177"/>
-      <c r="B133" s="177"/>
+      <c r="A133" s="184"/>
+      <c r="B133" s="184"/>
     </row>
     <row r="134" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="67"/>
@@ -3291,17 +3308,17 @@
   <sheetData>
     <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="195" t="s">
+      <c r="B1" s="202" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="197"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="204"/>
       <c r="K1" s="102" t="s">
         <v>4</v>
       </c>
@@ -3319,15 +3336,15 @@
     </row>
     <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="198"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="200"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="206"/>
+      <c r="I2" s="206"/>
+      <c r="J2" s="207"/>
       <c r="K2" s="104" t="s">
         <v>63</v>
       </c>
@@ -3364,115 +3381,115 @@
     </row>
     <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="219" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="214"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="221"/>
     </row>
     <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="215" t="s">
+      <c r="B5" s="222" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="216"/>
-      <c r="N5" s="216"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="217"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="223"/>
+      <c r="O5" s="223"/>
+      <c r="P5" s="224"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="196" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="191" t="s">
+      <c r="B6" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="193" t="s">
+      <c r="C6" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="193" t="s">
+      <c r="D6" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="193" t="s">
+      <c r="E6" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="193" t="s">
+      <c r="F6" s="200" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="193" t="s">
+      <c r="G6" s="200" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="193" t="s">
+      <c r="H6" s="200" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="207" t="s">
+      <c r="I6" s="214" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="205" t="s">
+      <c r="J6" s="212" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="205" t="s">
+      <c r="K6" s="212" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="205" t="s">
+      <c r="L6" s="212" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="205" t="s">
+      <c r="M6" s="212" t="s">
         <v>189</v>
       </c>
-      <c r="N6" s="210" t="s">
+      <c r="N6" s="217" t="s">
         <v>58</v>
       </c>
       <c r="O6" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="201" t="s">
+      <c r="P6" s="208" t="s">
         <v>56</v>
       </c>
       <c r="S6" s="22"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="190"/>
-      <c r="B7" s="192"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="208"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="209"/>
-      <c r="L7" s="206"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="211"/>
+      <c r="A7" s="197"/>
+      <c r="B7" s="199"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="215"/>
+      <c r="J7" s="213"/>
+      <c r="K7" s="216"/>
+      <c r="L7" s="213"/>
+      <c r="M7" s="213"/>
+      <c r="N7" s="218"/>
       <c r="O7" s="26" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P7" s="202"/>
+      <c r="P7" s="209"/>
     </row>
     <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="119" t="s">
@@ -4055,14 +4072,14 @@
     </row>
     <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="119"/>
-      <c r="B18" s="149">
+      <c r="B18" s="183">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C18" s="149" t="s">
+      <c r="C18" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="149" t="s">
+      <c r="D18" s="183" t="s">
         <v>83</v>
       </c>
       <c r="E18" s="150">
@@ -7085,90 +7102,90 @@
     </row>
     <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="203" t="s">
+      <c r="D71" s="210" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="203"/>
-      <c r="F71" s="203"/>
-      <c r="G71" s="203"/>
-      <c r="H71" s="203"/>
-      <c r="I71" s="203"/>
-      <c r="J71" s="203"/>
-      <c r="K71" s="203"/>
-      <c r="L71" s="203"/>
-      <c r="M71" s="203"/>
-      <c r="N71" s="203"/>
-      <c r="O71" s="203"/>
+      <c r="E71" s="210"/>
+      <c r="F71" s="210"/>
+      <c r="G71" s="210"/>
+      <c r="H71" s="210"/>
+      <c r="I71" s="210"/>
+      <c r="J71" s="210"/>
+      <c r="K71" s="210"/>
+      <c r="L71" s="210"/>
+      <c r="M71" s="210"/>
+      <c r="N71" s="210"/>
+      <c r="O71" s="210"/>
     </row>
     <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="203"/>
-      <c r="E72" s="203"/>
-      <c r="F72" s="203"/>
-      <c r="G72" s="203"/>
-      <c r="H72" s="203"/>
-      <c r="I72" s="203"/>
-      <c r="J72" s="203"/>
-      <c r="K72" s="203"/>
-      <c r="L72" s="203"/>
-      <c r="M72" s="203"/>
-      <c r="N72" s="203"/>
-      <c r="O72" s="203"/>
+      <c r="D72" s="210"/>
+      <c r="E72" s="210"/>
+      <c r="F72" s="210"/>
+      <c r="G72" s="210"/>
+      <c r="H72" s="210"/>
+      <c r="I72" s="210"/>
+      <c r="J72" s="210"/>
+      <c r="K72" s="210"/>
+      <c r="L72" s="210"/>
+      <c r="M72" s="210"/>
+      <c r="N72" s="210"/>
+      <c r="O72" s="210"/>
     </row>
     <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="203"/>
-      <c r="E73" s="203"/>
-      <c r="F73" s="203"/>
-      <c r="G73" s="203"/>
-      <c r="H73" s="203"/>
-      <c r="I73" s="203"/>
-      <c r="J73" s="203"/>
-      <c r="K73" s="203"/>
-      <c r="L73" s="203"/>
-      <c r="M73" s="203"/>
-      <c r="N73" s="203"/>
-      <c r="O73" s="203"/>
+      <c r="D73" s="210"/>
+      <c r="E73" s="210"/>
+      <c r="F73" s="210"/>
+      <c r="G73" s="210"/>
+      <c r="H73" s="210"/>
+      <c r="I73" s="210"/>
+      <c r="J73" s="210"/>
+      <c r="K73" s="210"/>
+      <c r="L73" s="210"/>
+      <c r="M73" s="210"/>
+      <c r="N73" s="210"/>
+      <c r="O73" s="210"/>
     </row>
     <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="203"/>
-      <c r="E74" s="203"/>
-      <c r="F74" s="203"/>
-      <c r="G74" s="203"/>
-      <c r="H74" s="203"/>
-      <c r="I74" s="203"/>
-      <c r="J74" s="203"/>
-      <c r="K74" s="203"/>
-      <c r="L74" s="203"/>
-      <c r="M74" s="203"/>
-      <c r="N74" s="203"/>
-      <c r="O74" s="203"/>
+      <c r="D74" s="210"/>
+      <c r="E74" s="210"/>
+      <c r="F74" s="210"/>
+      <c r="G74" s="210"/>
+      <c r="H74" s="210"/>
+      <c r="I74" s="210"/>
+      <c r="J74" s="210"/>
+      <c r="K74" s="210"/>
+      <c r="L74" s="210"/>
+      <c r="M74" s="210"/>
+      <c r="N74" s="210"/>
+      <c r="O74" s="210"/>
     </row>
     <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D75" s="203"/>
-      <c r="E75" s="203"/>
-      <c r="F75" s="203"/>
-      <c r="G75" s="203"/>
-      <c r="H75" s="203"/>
-      <c r="I75" s="203"/>
-      <c r="J75" s="203"/>
-      <c r="K75" s="203"/>
-      <c r="L75" s="203"/>
-      <c r="M75" s="203"/>
-      <c r="N75" s="203"/>
-      <c r="O75" s="203"/>
+      <c r="D75" s="210"/>
+      <c r="E75" s="210"/>
+      <c r="F75" s="210"/>
+      <c r="G75" s="210"/>
+      <c r="H75" s="210"/>
+      <c r="I75" s="210"/>
+      <c r="J75" s="210"/>
+      <c r="K75" s="210"/>
+      <c r="L75" s="210"/>
+      <c r="M75" s="210"/>
+      <c r="N75" s="210"/>
+      <c r="O75" s="210"/>
     </row>
     <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D76" s="203"/>
-      <c r="E76" s="203"/>
-      <c r="F76" s="203"/>
-      <c r="G76" s="203"/>
-      <c r="H76" s="203"/>
-      <c r="I76" s="203"/>
-      <c r="J76" s="203"/>
-      <c r="K76" s="203"/>
-      <c r="L76" s="203"/>
-      <c r="M76" s="203"/>
-      <c r="N76" s="203"/>
-      <c r="O76" s="203"/>
+      <c r="D76" s="210"/>
+      <c r="E76" s="210"/>
+      <c r="F76" s="210"/>
+      <c r="G76" s="210"/>
+      <c r="H76" s="210"/>
+      <c r="I76" s="210"/>
+      <c r="J76" s="210"/>
+      <c r="K76" s="210"/>
+      <c r="L76" s="210"/>
+      <c r="M76" s="210"/>
+      <c r="N76" s="210"/>
+      <c r="O76" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -7199,7 +7216,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="C2:K24"/>
+  <dimension ref="C2:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7243,36 +7260,36 @@
       <c r="K5" s="72"/>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C6" s="218" t="s">
+      <c r="C6" s="225" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="219"/>
-      <c r="E6" s="219"/>
-      <c r="F6" s="219"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="220"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="227"/>
       <c r="I6" s="21"/>
       <c r="J6" s="21"/>
       <c r="K6" s="72"/>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C7" s="221"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="223"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="230"/>
       <c r="I7" s="21"/>
       <c r="J7" s="21"/>
       <c r="K7" s="72"/>
     </row>
     <row r="8" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="224"/>
-      <c r="D8" s="225"/>
-      <c r="E8" s="225"/>
-      <c r="F8" s="225"/>
-      <c r="G8" s="225"/>
-      <c r="H8" s="226"/>
+      <c r="C8" s="231"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="233"/>
       <c r="I8" s="72"/>
       <c r="J8" s="72"/>
       <c r="K8" s="72"/>
@@ -7311,30 +7328,30 @@
       <c r="H13" s="110"/>
     </row>
     <row r="14" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="218" t="s">
+      <c r="C14" s="225" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="219"/>
-      <c r="G14" s="219"/>
-      <c r="H14" s="220"/>
+      <c r="D14" s="226"/>
+      <c r="E14" s="226"/>
+      <c r="F14" s="226"/>
+      <c r="G14" s="226"/>
+      <c r="H14" s="227"/>
     </row>
     <row r="15" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C15" s="221"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
-      <c r="F15" s="222"/>
-      <c r="G15" s="222"/>
-      <c r="H15" s="223"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
+      <c r="F15" s="229"/>
+      <c r="G15" s="229"/>
+      <c r="H15" s="230"/>
     </row>
     <row r="16" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="224"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="225"/>
-      <c r="G16" s="225"/>
-      <c r="H16" s="226"/>
+      <c r="C16" s="231"/>
+      <c r="D16" s="232"/>
+      <c r="E16" s="232"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="233"/>
     </row>
     <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
@@ -7368,36 +7385,91 @@
       <c r="H21" s="110"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="218" t="s">
+      <c r="C22" s="225" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="219"/>
-      <c r="E22" s="219"/>
-      <c r="F22" s="219"/>
-      <c r="G22" s="219"/>
-      <c r="H22" s="220"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="226"/>
+      <c r="G22" s="226"/>
+      <c r="H22" s="227"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="221"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="223"/>
+      <c r="C23" s="228"/>
+      <c r="D23" s="229"/>
+      <c r="E23" s="229"/>
+      <c r="F23" s="229"/>
+      <c r="G23" s="229"/>
+      <c r="H23" s="230"/>
     </row>
     <row r="24" spans="3:8" ht="62.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="224"/>
-      <c r="D24" s="225"/>
-      <c r="E24" s="225"/>
-      <c r="F24" s="225"/>
-      <c r="G24" s="225"/>
-      <c r="H24" s="226"/>
+      <c r="C24" s="231"/>
+      <c r="D24" s="232"/>
+      <c r="E24" s="232"/>
+      <c r="F24" s="232"/>
+      <c r="G24" s="232"/>
+      <c r="H24" s="233"/>
+    </row>
+    <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C27" s="179" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="180">
+        <f>D19+1</f>
+        <v>4</v>
+      </c>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="109"/>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C28" s="181" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="182" t="s">
+        <v>212</v>
+      </c>
+      <c r="H28" s="110"/>
+    </row>
+    <row r="29" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C29" s="181"/>
+      <c r="D29" s="182"/>
+      <c r="H29" s="110"/>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C30" s="225" t="s">
+        <v>211</v>
+      </c>
+      <c r="D30" s="226"/>
+      <c r="E30" s="226"/>
+      <c r="F30" s="226"/>
+      <c r="G30" s="226"/>
+      <c r="H30" s="227"/>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C31" s="228"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="229"/>
+      <c r="G31" s="229"/>
+      <c r="H31" s="230"/>
+    </row>
+    <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="231"/>
+      <c r="D32" s="232"/>
+      <c r="E32" s="232"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="233"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="C6:H8"/>
     <mergeCell ref="C14:H16"/>
     <mergeCell ref="C22:H24"/>
+    <mergeCell ref="C30:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/GALERIA MITRE/Septiembre/Septiembre MITRE.xlsx
+++ b/2026/GALERIA MITRE/Septiembre/Septiembre MITRE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8616A2-FA23-427D-AEFB-977BD72DF709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07BD377-8C45-4D96-8F42-EC8D74AD867A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$77</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$137</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$130</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="209">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -509,9 +514,6 @@
     <t>QUIENES ESTAN EN VIOLETA NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR.</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA ARCA</t>
-  </si>
-  <si>
     <t>Rocio Aylin</t>
   </si>
   <si>
@@ -533,60 +535,12 @@
     <t>Yesica Romina</t>
   </si>
   <si>
-    <t>Transf 18/8</t>
-  </si>
-  <si>
-    <t>Transf 03/08</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Transf 18/08</t>
-  </si>
-  <si>
-    <t>Debito 26/08</t>
-  </si>
-  <si>
-    <t>AySa - Vto. 25/08 - Cuenta de servicios 3483943</t>
-  </si>
-  <si>
-    <t>AySa - Vto. 21/07 - Cuenta de servicios 3483943</t>
-  </si>
-  <si>
     <t xml:space="preserve">Planes de pago - Afip - aportes de seg. social 06/2022 y 12/2022 </t>
   </si>
   <si>
-    <t>Debito 18/08</t>
-  </si>
-  <si>
-    <t>Cuota 35/36 - planes de pago - Afip - contrib. de seg. social 06/2022 y 12/2022</t>
-  </si>
-  <si>
-    <t>Gustavo Padron - Sr. Contador - CUIT: 20-20027122-0 - Mes de Junio - Fc.  000001110</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Dinero Fondo FIMA - Al 04/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E&amp;G Soluciones - Se realizaron trabajos de instalación hidráulica, eléctrica y de sistema de alarma. En lo que respecta a la instalación hidráulica, se efectuó el montaje y colocación de válvulas antirretorno de 1 1/2”, con correspondiente sellado industrial. Asimismo, se realizó la instalación completa del sistema eléctrico, incluyendo la colocación de un interruptor termomagnético de 20 A y un disyuntor diferencial de 2x25 A/30 mA, junto con el tendido de cableado tipo taller de 2x1,5 mm² y la instalación de un tomacorriente exterior estanco. Finalmente, se llevó a cabo la instalación y configuración de un sistema de alarma sonora por desborde de pozo, operado mediante transformador de 220 V/24 V y equipado con relé de control para garantizar su correcto funcionamiento y seguridad operativa. </t>
-  </si>
-  <si>
-    <t>Eleco - Presupuesto nro. 0000265 -  Compra de materiales electricos: termica 2x20A cuva C, 2 disyuntores 2x25A, flotantes automaticos, tiras de caño rigido, curvas de 90 grados PVC, union PVC, 1 zumbador 220V, Recorte cable tipo taller, 20 grampas y tornillos numero 6, 1 caja de 4 modulos, 2 modulo toma simple blanco, 2 tapones ciegos, cinta aisladora y precintos</t>
-  </si>
-  <si>
-    <t>Transf 21/08</t>
-  </si>
-  <si>
     <t>Frisco - Capetello Silvina Viviana</t>
   </si>
   <si>
-    <t>Deposito ya identificado mes de junio</t>
-  </si>
-  <si>
     <t>Nahuel gutierrez Almicar</t>
   </si>
   <si>
@@ -597,12 +551,6 @@
   </si>
   <si>
     <t>Gasto oficinas - Ascensor</t>
-  </si>
-  <si>
-    <t>Para poder afrontar el gasto correspondiente a los trabajos a realizar en el ascensor de las oficinas, es necesario recaudar un total de $2.500.000.
-Si bien el gasto a cubrir es de $2.500.000, el monto que se prorratea es superior, superando los $4.000.000. Esto se debe a que el gasto es exclusivo de las oficinas y, por lo tanto, los locales y sus respectivos porcentuales quedan excluidos del cálculo.
-Al no representar las oficinas el 100% de los porcentuales del edificio, si se prorratearan únicamente $2.500.000, la recaudación efectiva sería inferior al monto necesario.
-Por este motivo, se prorratea un importe superior a $4.000.000, de manera que, al distribuirlo exclusivamente entre las oficinas y aplicando sus respectivos porcentuales, se logre recaudar finalmente los $2.500.000 necesarios para afrontar el gasto del ascensor.</t>
   </si>
   <si>
     <t xml:space="preserve">Uf que paga con 54 centavos abono $186.000 el 08/9
@@ -632,18 +580,9 @@
     <t>A andes elevadores hay una diferencia (pagamos $229.000 en SEPTIEMBRE que NO incluimos en los gastos) - Debemos evaluar los pagos pq nos reclaman una deuda de servicios de Mayo y Abril</t>
   </si>
   <si>
-    <t>Carrafiele SEPTIEMBRE -  Mes de AGOSTO</t>
-  </si>
-  <si>
     <t>Ivana del Carmen Roldan -  Mes de AGOSTO</t>
   </si>
   <si>
-    <t>Honorarios administracion RC - CUIT: 27-23125687-9 - Se adeudan $90.000, JUNIO Y AGOSTO completo ($650.000 C/U) - Se abona SEPTIEMBRE 2026</t>
-  </si>
-  <si>
-    <t>Deposito ya identificado mes de AGOSTO</t>
-  </si>
-  <si>
     <t>Transf 18/09</t>
   </si>
   <si>
@@ -675,6 +614,61 @@
   </si>
   <si>
     <t>Local 10</t>
+  </si>
+  <si>
+    <t>Transf 07/09</t>
+  </si>
+  <si>
+    <t>Honorarios administracion RC - CUIT: 27-23125687-9 - Se adeudan $90.000, JUNIO Y JULIO completo ($650.000 C/U) - Se abona SEPTIEMBRE 2026</t>
+  </si>
+  <si>
+    <t>Honorarios Sra. Abogada - CUIT: 27-26023414-0 - Gastos inicio carpeta Juicio consorcio c/ Di Lauro</t>
+  </si>
+  <si>
+    <t>Debito 14/09</t>
+  </si>
+  <si>
+    <t>Transf 21/09</t>
+  </si>
+  <si>
+    <t>Andes elevadores - CUIT: 30-71177858-2 - Fc. 00000010635 - Reparación en sala de máquinas, consistente en el ordenamiento y adecuación de la instalación eléctrica, incluyendo la colocación de extensiones de cables, canaletas de chapa galvanizada y tapa en el hueco de conexión con la fosa. Reparación en Ascensor N.º 1, consistente en la renovación de la instalación eléctrica en el pasadizo, incluyendo el tendido de cables de comando, llamadas exteriores y seguridades del pasadizo, como así también la colocación de cable mallado desde el control hasta el motor para protección del variador de frecuencia. Asimismo, se realizó la provisión y colocación de un nuevo botón de luz en la cabina del Ascensor N.º 1, debido a la rotura del existente.</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA</t>
+  </si>
+  <si>
+    <t>Transf 28/09</t>
+  </si>
+  <si>
+    <t>AySa - Cuenta de servicios 3483943</t>
+  </si>
+  <si>
+    <t>Debito 25/09</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - CUIT: 27319702445 - Fc. 00001735</t>
+  </si>
+  <si>
+    <t>Debito 16/09</t>
+  </si>
+  <si>
+    <t>Sr. Carrafiele -  Mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Transferencia 29/09</t>
+  </si>
+  <si>
+    <t>Dinero Fondo FIMA - Al 06/10/2026</t>
+  </si>
+  <si>
+    <t>Deposita</t>
+  </si>
+  <si>
+    <t>Se informa que durante el mes anterior se prorrateó, exclusivamente entre las unidades correspondientes a las oficinas, la suma de PESOS DOS MILLONES QUINIENTOS MIL ($2.500.000), destinada a abonar el 50% de los trabajos realizados en el ascensor N.º 1, correspondiente a la primera cuota.
+Para el presente mes de septiembre, corresponde afrontar la segunda cuota de los trabajos, cuyo importe asciende a PESOS DOS MILLONES OCHOCIENTOS SETENTA Y TRES MIL OCHOCIENTOS ($2.873.800).
+Asimismo, se contempla un gasto adicional de PESOS CIENTO OCHENTA MIL ($180.000), vinculado a trabajos y/o gastos complementarios relacionados con la intervención realizada en el ascensor.
+En consecuencia, durante el presente mes resulta necesario reunir un total de PESOS TRES MILLONES CINCUENTA Y TRES MIL OCHOCIENTOS ($3.053.800), monto que será prorrateado exclusivamente entre las oficinas.
+De esta manera, el importe a prorratear se incrementa respecto del mes anterior debido tanto al mayor valor de la segunda cuota como a los gastos adicionales mencionados.</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1322,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1561,13 +1555,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="9" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="16" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1575,49 +1563,120 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1631,81 +1690,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1733,6 +1717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1801,9 +1786,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1841,9 +1826,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1876,9 +1861,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1911,9 +1913,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2087,21 +2106,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L137"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L130"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="120" t="s">
         <v>64</v>
       </c>
@@ -2109,7 +2128,7 @@
       <c r="C1" s="122"/>
       <c r="D1" s="122"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="123" t="s">
         <v>125</v>
       </c>
@@ -2117,7 +2136,7 @@
       <c r="C2" s="123"/>
       <c r="D2" s="123"/>
     </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123" t="s">
         <v>70</v>
       </c>
@@ -2125,115 +2144,115 @@
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="192" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="176" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="192"/>
+      <c r="B4" s="176"/>
       <c r="C4" s="124"/>
       <c r="D4" s="124"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="192"/>
-      <c r="B5" s="192"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="176"/>
+      <c r="B5" s="176"/>
       <c r="C5" s="124"/>
       <c r="D5" s="124"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="192"/>
-      <c r="B6" s="192"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
       <c r="C6" s="124"/>
       <c r="D6" s="124"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="192"/>
-      <c r="B7" s="192"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="176"/>
+      <c r="B7" s="176"/>
       <c r="C7" s="124"/>
       <c r="D7" s="124"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="61"/>
-      <c r="B9" s="187" t="s">
-        <v>196</v>
+      <c r="B9" s="185" t="s">
+        <v>178</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="61"/>
-      <c r="B10" s="187"/>
+      <c r="B10" s="185"/>
       <c r="C10" s="61"/>
       <c r="D10" s="61"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="61"/>
-      <c r="B11" s="187"/>
+      <c r="B11" s="185"/>
       <c r="C11" s="61"/>
       <c r="D11" s="61"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="192" t="s">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="176" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="192"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="192"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
-      <c r="B15" s="192"/>
-      <c r="C15" s="192"/>
-      <c r="D15" s="192"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="192"/>
-      <c r="B16" s="192"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="192"/>
-    </row>
-    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="192"/>
-      <c r="B17" s="192"/>
-      <c r="C17" s="192"/>
-      <c r="D17" s="192"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="176"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="176"/>
+      <c r="B15" s="176"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="176"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+    </row>
+    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="176"/>
+      <c r="B17" s="176"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="176"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
       <c r="C18" s="61"/>
       <c r="D18" s="61"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="125"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
       <c r="D19" s="61"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
       <c r="C20" s="61"/>
       <c r="D20" s="61"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="126" t="s">
         <v>26</v>
       </c>
@@ -2245,7 +2264,7 @@
       </c>
       <c r="F21" s="118"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>52</v>
       </c>
@@ -2255,31 +2274,31 @@
       <c r="E22" s="118"/>
       <c r="F22" s="118"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="185" t="s">
-        <v>198</v>
-      </c>
-      <c r="B23" s="186"/>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="182" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" s="183"/>
       <c r="C23" s="160">
-        <v>1322255.05</v>
+        <v>1416263.46</v>
       </c>
       <c r="D23" s="46"/>
       <c r="E23" s="118"/>
       <c r="F23" s="118"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="46"/>
       <c r="C24" s="160">
-        <v>-208255.05</v>
+        <v>-223061.46</v>
       </c>
       <c r="D24" s="46"/>
       <c r="E24" s="118"/>
       <c r="F24" s="118"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
         <v>54</v>
       </c>
@@ -2292,44 +2311,44 @@
       <c r="F25" s="118"/>
       <c r="G25" s="89"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="128" t="s">
         <v>53</v>
       </c>
       <c r="B26" s="128"/>
       <c r="C26" s="70">
         <f>SUM(C23:C25)</f>
-        <v>1114000</v>
+        <v>1193202</v>
       </c>
       <c r="D26" s="128"/>
       <c r="E26" s="118"/>
       <c r="F26" s="118"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="185" t="s">
-        <v>199</v>
-      </c>
-      <c r="B27" s="186"/>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="182" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="183"/>
       <c r="C27" s="160">
-        <v>941573.23</v>
+        <v>967913.48</v>
       </c>
       <c r="D27" s="46"/>
       <c r="E27" s="118"/>
       <c r="F27" s="118"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B28" s="46"/>
       <c r="C28" s="160">
-        <v>233039.23</v>
+        <v>-239558.48</v>
       </c>
       <c r="D28" s="71"/>
       <c r="E28" s="118"/>
       <c r="F28" s="118"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
         <v>54</v>
       </c>
@@ -2339,18 +2358,18 @@
       </c>
       <c r="D29" s="71"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="128" t="s">
         <v>53</v>
       </c>
       <c r="B30" s="129"/>
       <c r="C30" s="25">
         <f>SUM(C27:C29)</f>
-        <v>1174612.46</v>
+        <v>728355</v>
       </c>
       <c r="D30" s="47"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
       <c r="C31" s="91">
@@ -2358,13 +2377,13 @@
       </c>
       <c r="D31" s="71"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
       <c r="C32" s="91"/>
       <c r="D32" s="71"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="128" t="s">
         <v>53</v>
       </c>
@@ -2375,7 +2394,7 @@
       </c>
       <c r="D33" s="47"/>
     </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>0</v>
       </c>
@@ -2383,12 +2402,12 @@
       <c r="C34" s="7"/>
       <c r="D34" s="48">
         <f>+C26+C33+C30</f>
-        <v>2288612.46</v>
+        <v>1921557</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -2397,59 +2416,59 @@
       <c r="D35" s="49"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="188" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="189"/>
+    <row r="36" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="180" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="181"/>
       <c r="C36" s="160">
         <v>650000</v>
       </c>
       <c r="D36" s="78" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="188" t="s">
-        <v>178</v>
-      </c>
-      <c r="B37" s="189"/>
+    <row r="37" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="180" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="181"/>
       <c r="C37" s="81">
         <v>100000</v>
       </c>
       <c r="D37" s="75" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="188" t="s">
-        <v>208</v>
-      </c>
-      <c r="B38" s="189"/>
-      <c r="C38" s="177">
-        <v>100000</v>
+    <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="180" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="181"/>
+      <c r="C38" s="81">
+        <v>495000</v>
       </c>
       <c r="D38" s="75" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="188" t="s">
-        <v>207</v>
-      </c>
-      <c r="B39" s="189"/>
-      <c r="C39" s="178">
+    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="180" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="181"/>
+      <c r="C39" s="160">
         <v>200000</v>
       </c>
       <c r="D39" s="75" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>34</v>
       </c>
@@ -2457,10 +2476,10 @@
       <c r="C40" s="115"/>
       <c r="D40" s="48">
         <f>SUM(C36:C39)</f>
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1445000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>49</v>
       </c>
@@ -2468,19 +2487,19 @@
       <c r="C41" s="13"/>
       <c r="D41" s="29"/>
     </row>
-    <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="188" t="s">
+    <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="189"/>
+      <c r="B42" s="181"/>
       <c r="C42" s="161">
-        <v>111108.81</v>
+        <v>128114</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>1</v>
       </c>
@@ -2488,10 +2507,10 @@
       <c r="C43" s="15"/>
       <c r="D43" s="50">
         <f>SUM(C42:C42)</f>
-        <v>111108.81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>128114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>35</v>
       </c>
@@ -2499,7 +2518,7 @@
       <c r="C44" s="16"/>
       <c r="D44" s="51"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="71" t="s">
         <v>65</v>
       </c>
@@ -2510,770 +2529,709 @@
       <c r="D45" s="75"/>
       <c r="F45" s="72"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="188" t="s">
-        <v>177</v>
-      </c>
-      <c r="B46" s="189"/>
+    <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="180" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="181"/>
       <c r="C46" s="81">
-        <v>11596.99</v>
-      </c>
-      <c r="D46" s="77" t="s">
-        <v>176</v>
+        <v>11930.96</v>
+      </c>
+      <c r="D46" s="75" t="s">
+        <v>203</v>
       </c>
       <c r="F46" s="72"/>
     </row>
-    <row r="47" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="188" t="s">
-        <v>175</v>
-      </c>
-      <c r="B47" s="189"/>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="71"/>
       <c r="C47" s="81">
-        <v>11930.96</v>
-      </c>
-      <c r="D47" s="75" t="str">
-        <f>D46</f>
-        <v>Debito 18/08</v>
-      </c>
-      <c r="F47" s="72"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>107287.94</v>
+      </c>
+      <c r="D47" s="77" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48" s="71"/>
       <c r="C48" s="81">
-        <v>101872.21</v>
-      </c>
-      <c r="D48" s="77" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11920.89</v>
+      </c>
+      <c r="D48" s="77" t="str">
+        <f>D47</f>
+        <v>Debito 14/09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="71" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B49" s="71"/>
       <c r="C49" s="81">
-        <v>11319.13</v>
-      </c>
-      <c r="D49" s="77" t="str">
-        <f>D48</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="71" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" s="71"/>
-      <c r="C50" s="81">
-        <v>221236.75</v>
-      </c>
-      <c r="D50" s="76" t="str">
-        <f>D48</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
+        <v>230466.45</v>
+      </c>
+      <c r="D49" s="76" t="str">
+        <f>D47</f>
+        <v>Debito 14/09</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
         <v>2</v>
       </c>
+      <c r="B50" s="80"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="50">
+        <f>SUM(C45:C49)</f>
+        <v>361606.24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="B51" s="80"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="50">
-        <f>SUM(C45:C50)</f>
-        <v>357956.04000000004</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="80"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="51"/>
-    </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="16"/>
+      <c r="D51" s="51"/>
+    </row>
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="71"/>
+      <c r="C52" s="81">
+        <v>363925.4</v>
+      </c>
+      <c r="D52" s="77" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B53" s="71"/>
-      <c r="C53" s="177">
-        <v>363925.4</v>
+      <c r="C53" s="81">
+        <v>394235.68</v>
       </c>
       <c r="D53" s="77" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="71" t="s">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="B54" s="71"/>
-      <c r="C54" s="177">
-        <v>394235.68</v>
-      </c>
-      <c r="D54" s="77" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="81">
+        <v>1439199.84</v>
+      </c>
+      <c r="D54" s="75" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="71" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="B55" s="71"/>
       <c r="C55" s="81">
-        <v>1432816.72</v>
-      </c>
-      <c r="D55" s="75" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>36551.61</v>
+      </c>
+      <c r="D55" s="77" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="71" t="s">
-        <v>173</v>
-      </c>
-      <c r="B56" s="71"/>
+        <v>155</v>
+      </c>
+      <c r="B56" s="159"/>
       <c r="C56" s="81">
-        <v>1411636.23</v>
-      </c>
-      <c r="D56" s="77" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="71"/>
-      <c r="C57" s="177">
-        <v>36551.61</v>
-      </c>
-      <c r="D57" s="77" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="71" t="s">
-        <v>155</v>
-      </c>
-      <c r="B58" s="159"/>
-      <c r="C58" s="81">
-        <v>83831</v>
-      </c>
-      <c r="D58" s="75" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="11" t="s">
+        <v>85591</v>
+      </c>
+      <c r="D56" s="75" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="50">
-        <f>SUM(C53:C58)</f>
-        <v>3722996.6399999997</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="10" t="s">
+      <c r="B57" s="11"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="50">
+        <f>SUM(C52:C56)</f>
+        <v>2319503.5299999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="11"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="53"/>
-    </row>
-    <row r="61" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="188" t="s">
-        <v>203</v>
-      </c>
-      <c r="B61" s="189"/>
-      <c r="C61" s="177">
+      <c r="B58" s="11"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="53"/>
+    </row>
+    <row r="59" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="180" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="181"/>
+      <c r="C59" s="81">
         <v>202000</v>
       </c>
+      <c r="D59" s="75" t="s">
+        <v>181</v>
+      </c>
+      <c r="G59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="180" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="181"/>
+      <c r="C60" s="81">
+        <v>2866240</v>
+      </c>
+      <c r="D60" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="F60" s="22"/>
+    </row>
+    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="180" t="s">
+        <v>202</v>
+      </c>
+      <c r="B61" s="181"/>
+      <c r="C61" s="81">
+        <v>157100</v>
+      </c>
       <c r="D61" s="75" t="s">
-        <v>202</v>
-      </c>
-      <c r="G61" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="188" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="189"/>
+        <v>199</v>
+      </c>
+      <c r="F61" s="22"/>
+    </row>
+    <row r="62" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="180" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" s="181"/>
       <c r="C62" s="81">
-        <v>650000</v>
+        <v>128900</v>
       </c>
       <c r="D62" s="75" t="s">
-        <v>183</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="E62" s="116"/>
       <c r="F62" s="22"/>
     </row>
-    <row r="63" spans="1:7" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="188" t="s">
-        <v>182</v>
-      </c>
-      <c r="B63" s="189"/>
-      <c r="C63" s="81">
-        <v>166345.46</v>
-      </c>
-      <c r="D63" s="75" t="s">
-        <v>171</v>
-      </c>
-      <c r="F63" s="22"/>
-    </row>
-    <row r="64" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="188" t="s">
-        <v>204</v>
-      </c>
-      <c r="B64" s="189"/>
-      <c r="C64" s="177">
-        <v>128900</v>
-      </c>
-      <c r="D64" s="75" t="s">
-        <v>205</v>
-      </c>
-      <c r="E64" s="116"/>
-      <c r="F64" s="22"/>
-    </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="11" t="s">
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="56">
-        <f>SUM(C61:C64)</f>
-        <v>1147245.46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="10" t="s">
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="56">
+        <f>SUM(C59:C62)</f>
+        <v>3354240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B66" s="82"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="53"/>
-    </row>
-    <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="185" t="s">
+      <c r="B64" s="82"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="53"/>
+    </row>
+    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="182" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="186"/>
-      <c r="C67" s="81">
+      <c r="B65" s="183"/>
+      <c r="C65" s="81">
         <v>75000</v>
       </c>
-      <c r="D67" s="57"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46" t="s">
+      <c r="D65" s="57"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="46" t="s">
         <v>71</v>
       </c>
+      <c r="B66" s="46"/>
+      <c r="C66" s="81">
+        <v>241170.56</v>
+      </c>
+      <c r="D66" s="55"/>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="130" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" s="130"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="50">
+        <f>SUM(C65:C66)</f>
+        <v>316170.56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="46"/>
       <c r="B68" s="46"/>
-      <c r="C68" s="81">
-        <v>172775.23</v>
-      </c>
-      <c r="D68" s="55"/>
-    </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="B69" s="130"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="50">
-        <f>SUM(C67:C68)</f>
-        <v>247775.23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="46"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="59"/>
-    </row>
-    <row r="71" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="193" t="s">
-        <v>160</v>
-      </c>
-      <c r="B71" s="194"/>
-      <c r="C71" s="195"/>
-      <c r="D71" s="60">
+      <c r="C68" s="46"/>
+      <c r="D68" s="59"/>
+    </row>
+    <row r="69" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="177" t="s">
+        <v>198</v>
+      </c>
+      <c r="B69" s="178"/>
+      <c r="C69" s="179"/>
+      <c r="D69" s="60">
         <v>1000000</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="131"/>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="131"/>
+      <c r="B70" s="61"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="22"/>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="B71" s="133"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="64">
+        <f>(SUM(D23:D69))</f>
+        <v>10846191.33</v>
+      </c>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="61"/>
       <c r="B72" s="61"/>
       <c r="C72" s="61"/>
-      <c r="D72" s="62"/>
-      <c r="E72" s="22"/>
-    </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="132" t="s">
-        <v>30</v>
-      </c>
-      <c r="B73" s="133"/>
-      <c r="C73" s="63"/>
-      <c r="D73" s="64">
-        <f>(SUM(D23:D71))</f>
-        <v>9925694.6400000006</v>
-      </c>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="61"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="F74" s="73"/>
-    </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="61"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="126" t="s">
+      <c r="D72" s="61"/>
+      <c r="F72" s="73"/>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="61"/>
+      <c r="B73" s="61"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="61"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="B76" s="127"/>
-      <c r="C76" s="65"/>
-      <c r="D76" s="66"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="185"/>
-      <c r="B77" s="186"/>
+      <c r="B74" s="127"/>
+      <c r="C74" s="65"/>
+      <c r="D74" s="66"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="182"/>
+      <c r="B75" s="183"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="52"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="182"/>
+      <c r="B76" s="183"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="52"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="117"/>
+      <c r="B77" s="134"/>
       <c r="C77" s="54"/>
       <c r="D77" s="52"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="185"/>
-      <c r="B78" s="186"/>
-      <c r="C78" s="54"/>
-      <c r="D78" s="52"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="117"/>
-      <c r="B79" s="134"/>
-      <c r="C79" s="54"/>
-      <c r="D79" s="52"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="135"/>
-      <c r="B80" s="136"/>
-      <c r="C80" s="137"/>
-      <c r="D80" s="137">
-        <f>SUM(C77:C79)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="61"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-    </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="135"/>
+      <c r="B78" s="136"/>
+      <c r="C78" s="137"/>
+      <c r="D78" s="137">
+        <f>SUM(C75:C77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="61"/>
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="61"/>
+    </row>
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="61"/>
+      <c r="B80" s="61"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="61"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="138" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="138"/>
+      <c r="C81" s="139"/>
+      <c r="D81" s="140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="61"/>
       <c r="B82" s="61"/>
       <c r="C82" s="61"/>
       <c r="D82" s="61"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="138" t="s">
-        <v>40</v>
-      </c>
-      <c r="B83" s="138"/>
-      <c r="C83" s="139"/>
-      <c r="D83" s="140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83" s="133"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="64">
+        <f>D78+D81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="61"/>
       <c r="B84" s="61"/>
       <c r="C84" s="61"/>
       <c r="D84" s="61"/>
     </row>
-    <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="132" t="s">
-        <v>41</v>
-      </c>
-      <c r="B85" s="133"/>
-      <c r="C85" s="63"/>
-      <c r="D85" s="64">
-        <f>D80+D83</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="61"/>
-      <c r="B86" s="61"/>
+    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" s="142">
+        <f>D71</f>
+        <v>10846191.33</v>
+      </c>
+      <c r="C85" s="143"/>
+      <c r="D85" s="61"/>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="B86" s="142">
+        <f>D71-D69</f>
+        <v>9846191.3300000001</v>
+      </c>
       <c r="C86" s="61"/>
       <c r="D86" s="61"/>
     </row>
-    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="141" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B87" s="142">
-        <f>D73</f>
-        <v>9925694.6400000006</v>
-      </c>
-      <c r="C87" s="143"/>
+        <f>D83-D81</f>
+        <v>0</v>
+      </c>
+      <c r="C87" s="61"/>
       <c r="D87" s="61"/>
     </row>
-    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="141" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B88" s="142">
-        <f>D73-D71</f>
-        <v>8925694.6400000006</v>
+        <f>D83</f>
+        <v>0</v>
       </c>
       <c r="C88" s="61"/>
       <c r="D88" s="61"/>
     </row>
-    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="141" t="s">
-        <v>42</v>
-      </c>
-      <c r="B89" s="142">
-        <f>D85-D83</f>
-        <v>0</v>
-      </c>
-      <c r="C89" s="61"/>
-      <c r="D89" s="61"/>
-    </row>
-    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="141" t="s">
-        <v>59</v>
-      </c>
-      <c r="B90" s="142">
-        <f>D85</f>
-        <v>0</v>
-      </c>
-      <c r="C90" s="61"/>
-      <c r="D90" s="61"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="190" t="s">
-        <v>190</v>
-      </c>
-      <c r="B93" s="191"/>
-      <c r="C93" s="191"/>
-      <c r="D93" s="191"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="191"/>
-      <c r="B94" s="191"/>
-      <c r="C94" s="191"/>
-      <c r="D94" s="191"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="191"/>
-      <c r="B95" s="191"/>
-      <c r="C95" s="191"/>
-      <c r="D95" s="191"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="191"/>
-      <c r="B96" s="191"/>
-      <c r="C96" s="191"/>
-      <c r="D96" s="191"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="191"/>
-      <c r="B97" s="191"/>
-      <c r="C97" s="191"/>
-      <c r="D97" s="191"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="191"/>
-      <c r="B98" s="191"/>
-      <c r="C98" s="191"/>
-      <c r="D98" s="191"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="191"/>
-      <c r="B99" s="191"/>
-      <c r="C99" s="191"/>
-      <c r="D99" s="191"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="191"/>
-      <c r="B100" s="191"/>
-      <c r="C100" s="191"/>
-      <c r="D100" s="191"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="191"/>
-      <c r="B101" s="191"/>
-      <c r="C101" s="191"/>
-      <c r="D101" s="191"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="191"/>
-      <c r="B102" s="191"/>
-      <c r="C102" s="191"/>
-      <c r="D102" s="191"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="191"/>
-      <c r="B103" s="191"/>
-      <c r="C103" s="191"/>
-      <c r="D103" s="191"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="191"/>
-      <c r="B104" s="191"/>
-      <c r="C104" s="191"/>
-      <c r="D104" s="191"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="191"/>
-      <c r="B105" s="191"/>
-      <c r="C105" s="191"/>
-      <c r="D105" s="191"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="191"/>
-      <c r="B106" s="191"/>
-      <c r="C106" s="191"/>
-      <c r="D106" s="191"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="191"/>
-      <c r="B107" s="191"/>
-      <c r="C107" s="191"/>
-      <c r="D107" s="191"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="191"/>
-      <c r="B108" s="191"/>
-      <c r="C108" s="191"/>
-      <c r="D108" s="191"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="191"/>
-      <c r="B109" s="191"/>
-      <c r="C109" s="191"/>
-      <c r="D109" s="191"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="191"/>
-      <c r="B110" s="191"/>
-      <c r="C110" s="191"/>
-      <c r="D110" s="191"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="191"/>
-      <c r="B111" s="191"/>
-      <c r="C111" s="191"/>
-      <c r="D111" s="191"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="191"/>
-      <c r="B112" s="191"/>
-      <c r="C112" s="191"/>
-      <c r="D112" s="191"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="191"/>
-      <c r="B113" s="191"/>
-      <c r="C113" s="191"/>
-      <c r="D113" s="191"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="5" t="s">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="186" t="s">
+        <v>208</v>
+      </c>
+      <c r="B91" s="187"/>
+      <c r="C91" s="187"/>
+      <c r="D91" s="187"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="187"/>
+      <c r="B92" s="187"/>
+      <c r="C92" s="187"/>
+      <c r="D92" s="187"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="187"/>
+      <c r="B93" s="187"/>
+      <c r="C93" s="187"/>
+      <c r="D93" s="187"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="187"/>
+      <c r="B94" s="187"/>
+      <c r="C94" s="187"/>
+      <c r="D94" s="187"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="187"/>
+      <c r="B95" s="187"/>
+      <c r="C95" s="187"/>
+      <c r="D95" s="187"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="187"/>
+      <c r="B96" s="187"/>
+      <c r="C96" s="187"/>
+      <c r="D96" s="187"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="187"/>
+      <c r="B97" s="187"/>
+      <c r="C97" s="187"/>
+      <c r="D97" s="187"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="187"/>
+      <c r="B98" s="187"/>
+      <c r="C98" s="187"/>
+      <c r="D98" s="187"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="187"/>
+      <c r="B99" s="187"/>
+      <c r="C99" s="187"/>
+      <c r="D99" s="187"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="187"/>
+      <c r="B100" s="187"/>
+      <c r="C100" s="187"/>
+      <c r="D100" s="187"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="187"/>
+      <c r="B101" s="187"/>
+      <c r="C101" s="187"/>
+      <c r="D101" s="187"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="187"/>
+      <c r="B102" s="187"/>
+      <c r="C102" s="187"/>
+      <c r="D102" s="187"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="187"/>
+      <c r="B103" s="187"/>
+      <c r="C103" s="187"/>
+      <c r="D103" s="187"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="187"/>
+      <c r="B104" s="187"/>
+      <c r="C104" s="187"/>
+      <c r="D104" s="187"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="187"/>
+      <c r="B105" s="187"/>
+      <c r="C105" s="187"/>
+      <c r="D105" s="187"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="187"/>
+      <c r="B106" s="187"/>
+      <c r="C106" s="187"/>
+      <c r="D106" s="187"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="187"/>
+      <c r="B107" s="187"/>
+      <c r="C107" s="187"/>
+      <c r="D107" s="187"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="187"/>
+      <c r="B108" s="187"/>
+      <c r="C108" s="187"/>
+      <c r="D108" s="187"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="187"/>
+      <c r="B109" s="187"/>
+      <c r="C109" s="187"/>
+      <c r="D109" s="187"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="187"/>
+      <c r="B110" s="187"/>
+      <c r="C110" s="187"/>
+      <c r="D110" s="187"/>
+    </row>
+    <row r="111" spans="1:4" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="187"/>
+      <c r="B111" s="187"/>
+      <c r="C111" s="187"/>
+      <c r="D111" s="187"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B116" s="19"/>
-    </row>
-    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="9" t="s">
+      <c r="B114" s="19"/>
+    </row>
+    <row r="115" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B117" s="69">
-        <v>2649072.209999999</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="94" t="s">
+      <c r="B115" s="69">
+        <v>3201830.870000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="B118" s="20">
+      <c r="B116" s="20">
         <f>PRORRATEO!G68</f>
-        <v>10043048.190000001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="94" t="s">
+        <v>9927701.9800000004</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="B119" s="55">
-        <f>B136</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="55">
+        <f>B129</f>
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B118" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" s="74">
+        <f>-B86</f>
+        <v>-9846191.3300000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B120" s="74">
-        <v>-92118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B121" s="74">
-        <v>-262000</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B122" s="74">
-        <v>-104955.29</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B123" s="74">
-        <v>-260000</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B124" s="74">
-        <f>-6906-3096</f>
-        <v>-10002</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B125" s="74">
-        <f>-B88</f>
-        <v>-8925694.6400000006</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B126" s="55">
-        <f>-(B89)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="8" t="s">
+      <c r="B120" s="55">
+        <f>-(B87)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B127" s="69">
-        <f>SUM(B117:B126)</f>
-        <v>3037350.4700000007</v>
-      </c>
-      <c r="C127" s="22"/>
-      <c r="D127" s="92"/>
-    </row>
-    <row r="128" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="1"/>
-      <c r="B128" s="95"/>
-      <c r="D128" s="92"/>
-    </row>
-    <row r="129" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="106" t="s">
-        <v>180</v>
-      </c>
-      <c r="B129" s="107">
-        <v>1397979.91</v>
-      </c>
-      <c r="D129" s="92"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="162" t="s">
-        <v>188</v>
-      </c>
-      <c r="B130" s="163">
-        <f>1465817.44-B129</f>
-        <v>67837.530000000028</v>
-      </c>
-      <c r="D130" s="92"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D131" s="93"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="184" t="s">
+      <c r="B121" s="69">
+        <f>SUM(B115:B120)</f>
+        <v>3833341.5200000014</v>
+      </c>
+      <c r="C121" s="22"/>
+      <c r="D121" s="92"/>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1"/>
+      <c r="B122" s="95"/>
+      <c r="D122" s="92"/>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="106" t="s">
+        <v>206</v>
+      </c>
+      <c r="B123" s="107">
+        <v>1305847.3899999999</v>
+      </c>
+      <c r="D123" s="92"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="162" t="s">
+        <v>171</v>
+      </c>
+      <c r="B124" s="163">
+        <v>92133</v>
+      </c>
+      <c r="D124" s="92"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D125" s="93"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="B132" s="184"/>
-    </row>
-    <row r="133" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="184"/>
-      <c r="B133" s="184"/>
-    </row>
-    <row r="134" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="67"/>
-      <c r="B134" s="14"/>
-    </row>
-    <row r="135" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="67"/>
-      <c r="B135" s="14"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="23" t="s">
+      <c r="B126" s="184"/>
+    </row>
+    <row r="127" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="184"/>
+      <c r="B127" s="184"/>
+    </row>
+    <row r="128" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="B128" s="14">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B136" s="68">
-        <f>SUM(B134:B135)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L137" s="3"/>
+      <c r="B129" s="68">
+        <f>SUM(B128:B128)</f>
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L130" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A132:B133"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A77:B77"/>
+  <mergeCells count="21">
+    <mergeCell ref="A126:B127"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:B75"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A91:D111"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A93:D113"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A62:B62"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3284,41 +3242,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="188" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="204"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
+      <c r="J1" s="190"/>
       <c r="K1" s="102" t="s">
         <v>4</v>
       </c>
@@ -3326,7 +3284,7 @@
       <c r="M1" s="103"/>
       <c r="N1" s="103"/>
       <c r="O1" s="99">
-        <v>9761214.2400000002</v>
+        <v>7979951.3300000001</v>
       </c>
       <c r="P1" s="100"/>
       <c r="Q1" s="4"/>
@@ -3334,17 +3292,17 @@
         <v>8136047.4719999991</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="206"/>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
+      <c r="F2" s="192"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
+      <c r="I2" s="192"/>
+      <c r="J2" s="193"/>
       <c r="K2" s="104" t="s">
         <v>63</v>
       </c>
@@ -3356,7 +3314,7 @@
       </c>
       <c r="P2" s="101"/>
     </row>
-    <row r="3" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="146"/>
       <c r="C3" s="147"/>
@@ -3368,130 +3326,130 @@
       <c r="I3" s="147"/>
       <c r="J3" s="147"/>
       <c r="K3" s="155" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="L3" s="156"/>
       <c r="M3" s="156"/>
       <c r="N3" s="156"/>
       <c r="O3" s="157">
-        <f>700+4389375+300+150+50+10+1+1</f>
-        <v>4390587</v>
+        <f>5361706-200-50-15-5-2-1</f>
+        <v>5361433</v>
       </c>
       <c r="P3" s="158"/>
     </row>
-    <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="207" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="221"/>
-    </row>
-    <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="209"/>
+    </row>
+    <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="222" t="s">
+      <c r="B5" s="210" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="223"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="223"/>
-      <c r="O5" s="223"/>
-      <c r="P5" s="224"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="196" t="s">
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="M5" s="211"/>
+      <c r="N5" s="211"/>
+      <c r="O5" s="211"/>
+      <c r="P5" s="212"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="198" t="s">
+      <c r="B6" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="200" t="s">
+      <c r="C6" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="200" t="s">
+      <c r="D6" s="197" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="200" t="s">
+      <c r="E6" s="197" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="200" t="s">
+      <c r="F6" s="197" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="200" t="s">
+      <c r="G6" s="197" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="200" t="s">
+      <c r="H6" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="214" t="s">
+      <c r="I6" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="212" t="s">
+      <c r="J6" s="199" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="212" t="s">
+      <c r="K6" s="199" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="212" t="s">
+      <c r="L6" s="199" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="212" t="s">
-        <v>189</v>
-      </c>
-      <c r="N6" s="217" t="s">
+      <c r="M6" s="199" t="s">
+        <v>172</v>
+      </c>
+      <c r="N6" s="205" t="s">
         <v>58</v>
       </c>
       <c r="O6" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="208" t="s">
+      <c r="P6" s="194" t="s">
         <v>56</v>
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="197"/>
-      <c r="B7" s="199"/>
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="214"/>
+      <c r="B7" s="216"/>
       <c r="C7" s="201"/>
       <c r="D7" s="201"/>
       <c r="E7" s="201"/>
       <c r="F7" s="201"/>
       <c r="G7" s="201"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="215"/>
-      <c r="J7" s="213"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="213"/>
-      <c r="M7" s="213"/>
-      <c r="N7" s="218"/>
+      <c r="H7" s="198"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="204"/>
+      <c r="L7" s="200"/>
+      <c r="M7" s="200"/>
+      <c r="N7" s="206"/>
       <c r="O7" s="26" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P7" s="209"/>
-    </row>
-    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P7" s="195"/>
+    </row>
+    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="119" t="s">
         <v>12</v>
       </c>
@@ -3508,7 +3466,7 @@
         <v>1.58</v>
       </c>
       <c r="F8" s="32">
-        <v>1939610</v>
+        <v>2151056</v>
       </c>
       <c r="G8" s="32">
         <v>0</v>
@@ -3516,11 +3474,11 @@
       <c r="H8" s="33"/>
       <c r="I8" s="34">
         <f>F8-G8</f>
-        <v>1939610</v>
+        <v>2151056</v>
       </c>
       <c r="J8" s="34">
         <f>IF(I8&gt;0,I8*2.95%,0)</f>
-        <v>57218.495000000003</v>
+        <v>63456.152000000002</v>
       </c>
       <c r="K8" s="35">
         <f t="shared" ref="K8:K39" si="0">O$2*E8%</f>
@@ -3528,7 +3486,7 @@
       </c>
       <c r="L8" s="35">
         <f t="shared" ref="L8:L39" si="1">O$1*E8%</f>
-        <v>154227.18499200002</v>
+        <v>126083.23101400002</v>
       </c>
       <c r="M8" s="153"/>
       <c r="N8" s="36">
@@ -3536,17 +3494,17 @@
       </c>
       <c r="O8" s="37">
         <f t="shared" ref="O8:O39" si="2">ROUND(SUM(I8:N8),0) + Q8</f>
-        <v>2151056</v>
+        <v>2340595</v>
       </c>
       <c r="P8" s="38">
         <f t="shared" ref="P8:P66" si="3">ROUND(O8*3%,0) + O8</f>
-        <v>2215588</v>
+        <v>2410813</v>
       </c>
       <c r="Q8" s="22">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="148"/>
       <c r="B9" s="149">
         <v>1</v>
@@ -3561,11 +3519,11 @@
         <v>2.91</v>
       </c>
       <c r="F9" s="32">
-        <v>970685.01</v>
+        <v>292573.01</v>
       </c>
       <c r="G9" s="32">
-        <f>476368+222884.01+271433</f>
-        <v>970685.01</v>
+        <f>F9</f>
+        <v>292573.01</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="34">
@@ -3582,7 +3540,7 @@
       </c>
       <c r="L9" s="35">
         <f t="shared" si="1"/>
-        <v>284051.33438399999</v>
+        <v>232216.58370300001</v>
       </c>
       <c r="M9" s="153"/>
       <c r="N9" s="36">
@@ -3590,21 +3548,21 @@
       </c>
       <c r="O9" s="37">
         <f t="shared" si="2"/>
-        <v>284051.01</v>
+        <v>232217.01</v>
       </c>
       <c r="P9" s="38">
         <f t="shared" si="3"/>
-        <v>292573.01</v>
+        <v>239184.01</v>
       </c>
       <c r="Q9" s="22">
         <f>Q7+0.01</f>
         <v>0.01</v>
       </c>
       <c r="R9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="119" t="s">
         <v>13</v>
       </c>
@@ -3622,19 +3580,19 @@
         <v>1.94</v>
       </c>
       <c r="F10" s="32">
-        <v>1580099.02</v>
+        <v>1713129.02</v>
       </c>
       <c r="G10" s="32">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="33"/>
       <c r="I10" s="84">
         <f t="shared" ref="I10:I66" si="4">F10-G10</f>
-        <v>1480099.02</v>
+        <v>1713129.02</v>
       </c>
       <c r="J10" s="84">
         <f t="shared" ref="J10:J66" si="5">IF(I10&gt;0,I10*2.95%,0)</f>
-        <v>43662.921090000003</v>
+        <v>50537.306090000005</v>
       </c>
       <c r="K10" s="85">
         <f t="shared" si="0"/>
@@ -3642,7 +3600,7 @@
       </c>
       <c r="L10" s="85">
         <f t="shared" si="1"/>
-        <v>189367.55625600001</v>
+        <v>154811.05580200002</v>
       </c>
       <c r="M10" s="154"/>
       <c r="N10" s="86">
@@ -3650,21 +3608,21 @@
       </c>
       <c r="O10" s="87">
         <f t="shared" si="2"/>
-        <v>1713129.02</v>
+        <v>1918477.02</v>
       </c>
       <c r="P10" s="88">
         <f t="shared" si="3"/>
-        <v>1764523.02</v>
+        <v>1976031.02</v>
       </c>
       <c r="Q10" s="22">
         <f>Q9+0.01</f>
         <v>0.02</v>
       </c>
       <c r="R10" s="22" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="119" t="s">
         <v>13</v>
       </c>
@@ -3682,11 +3640,11 @@
         <v>1.78</v>
       </c>
       <c r="F11" s="32">
-        <v>144822.03</v>
+        <v>173750.03</v>
       </c>
       <c r="G11" s="32">
         <f>F11</f>
-        <v>144822.03</v>
+        <v>173750.03</v>
       </c>
       <c r="H11" s="33"/>
       <c r="I11" s="84">
@@ -3703,7 +3661,7 @@
       </c>
       <c r="L11" s="85">
         <f t="shared" si="1"/>
-        <v>173749.613472</v>
+        <v>142043.13367400001</v>
       </c>
       <c r="M11" s="154"/>
       <c r="N11" s="86">
@@ -3711,18 +3669,18 @@
       </c>
       <c r="O11" s="87">
         <f t="shared" si="2"/>
-        <v>173750.03</v>
+        <v>142043.03</v>
       </c>
       <c r="P11" s="88">
         <f t="shared" si="3"/>
-        <v>178963.03</v>
+        <v>146304.03</v>
       </c>
       <c r="Q11" s="22">
         <f>Q10+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="119" t="s">
         <v>14</v>
       </c>
@@ -3740,11 +3698,11 @@
         <v>1.62</v>
       </c>
       <c r="F12" s="32">
-        <v>135758.04</v>
+        <v>162876.04</v>
       </c>
       <c r="G12" s="32">
         <f>F12</f>
-        <v>135758.04</v>
+        <v>162876.04</v>
       </c>
       <c r="H12" s="33"/>
       <c r="I12" s="34">
@@ -3761,7 +3719,7 @@
       </c>
       <c r="L12" s="35">
         <f t="shared" si="1"/>
-        <v>158131.67068800004</v>
+        <v>129275.21154600002</v>
       </c>
       <c r="M12" s="153"/>
       <c r="N12" s="36">
@@ -3769,11 +3727,11 @@
       </c>
       <c r="O12" s="37">
         <f t="shared" si="2"/>
-        <v>158132.04</v>
+        <v>129275.04</v>
       </c>
       <c r="P12" s="38">
         <f t="shared" si="3"/>
-        <v>162876.04</v>
+        <v>133153.03999999998</v>
       </c>
       <c r="Q12" s="22">
         <f t="shared" ref="Q12:Q66" si="7">Q11+0.01</f>
@@ -3784,7 +3742,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="144" t="s">
         <v>14</v>
       </c>
@@ -3802,7 +3760,7 @@
         <v>1.94</v>
       </c>
       <c r="F13" s="32">
-        <v>668146.05000000005</v>
+        <v>877224.05</v>
       </c>
       <c r="G13" s="32">
         <v>0</v>
@@ -3810,11 +3768,11 @@
       <c r="H13" s="33"/>
       <c r="I13" s="34">
         <f t="shared" si="4"/>
-        <v>668146.05000000005</v>
+        <v>877224.05</v>
       </c>
       <c r="J13" s="34">
         <f t="shared" si="5"/>
-        <v>19710.308475000002</v>
+        <v>25878.109475000005</v>
       </c>
       <c r="K13" s="35">
         <f t="shared" si="0"/>
@@ -3822,7 +3780,7 @@
       </c>
       <c r="L13" s="35">
         <f t="shared" si="1"/>
-        <v>189367.55625600001</v>
+        <v>154811.05580200002</v>
       </c>
       <c r="M13" s="153"/>
       <c r="N13" s="36">
@@ -3830,11 +3788,11 @@
       </c>
       <c r="O13" s="37">
         <f t="shared" si="2"/>
-        <v>877224.05</v>
+        <v>1057913.05</v>
       </c>
       <c r="P13" s="38">
         <f t="shared" si="3"/>
-        <v>903541.05</v>
+        <v>1089650.05</v>
       </c>
       <c r="Q13" s="22">
         <f t="shared" si="7"/>
@@ -3842,7 +3800,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="119"/>
       <c r="B14" s="149">
         <f t="shared" si="6"/>
@@ -3858,15 +3816,16 @@
         <v>1.78</v>
       </c>
       <c r="F14" s="32">
-        <v>140586.06</v>
+        <v>169532.06</v>
       </c>
       <c r="G14" s="32">
-        <v>144804.06</v>
+        <f>F14</f>
+        <v>169532.06</v>
       </c>
       <c r="H14" s="33"/>
       <c r="I14" s="34">
         <f t="shared" si="4"/>
-        <v>-4218</v>
+        <v>0</v>
       </c>
       <c r="J14" s="34">
         <f t="shared" si="5"/>
@@ -3878,7 +3837,7 @@
       </c>
       <c r="L14" s="35">
         <f t="shared" si="1"/>
-        <v>173749.613472</v>
+        <v>142043.13367400001</v>
       </c>
       <c r="M14" s="153"/>
       <c r="N14" s="36">
@@ -3886,11 +3845,11 @@
       </c>
       <c r="O14" s="37">
         <f t="shared" si="2"/>
-        <v>169532.06</v>
+        <v>142043.06</v>
       </c>
       <c r="P14" s="38">
         <f t="shared" si="3"/>
-        <v>174618.06</v>
+        <v>146304.06</v>
       </c>
       <c r="Q14" s="22">
         <f t="shared" si="7"/>
@@ -3898,7 +3857,7 @@
       </c>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="119"/>
       <c r="B15" s="149">
         <f t="shared" si="6"/>
@@ -3914,11 +3873,11 @@
         <v>1.62</v>
       </c>
       <c r="F15" s="32">
-        <v>135758.07</v>
+        <v>162876.07</v>
       </c>
       <c r="G15" s="32">
         <f>F15</f>
-        <v>135758.07</v>
+        <v>162876.07</v>
       </c>
       <c r="H15" s="33"/>
       <c r="I15" s="34">
@@ -3935,7 +3894,7 @@
       </c>
       <c r="L15" s="35">
         <f t="shared" si="1"/>
-        <v>158131.67068800004</v>
+        <v>129275.21154600002</v>
       </c>
       <c r="M15" s="153"/>
       <c r="N15" s="36">
@@ -3943,11 +3902,11 @@
       </c>
       <c r="O15" s="37">
         <f t="shared" si="2"/>
-        <v>158132.07</v>
+        <v>129275.07</v>
       </c>
       <c r="P15" s="38">
         <f t="shared" si="3"/>
-        <v>162876.07</v>
+        <v>133153.07</v>
       </c>
       <c r="Q15" s="22">
         <f t="shared" si="7"/>
@@ -3958,7 +3917,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="119"/>
       <c r="B16" s="149">
         <f t="shared" si="6"/>
@@ -3974,19 +3933,19 @@
         <v>1.62</v>
       </c>
       <c r="F16" s="32">
-        <v>131081.07999999999</v>
+        <v>154193.07999999999</v>
       </c>
       <c r="G16" s="32">
-        <v>135020</v>
+        <v>154100</v>
       </c>
       <c r="H16" s="33"/>
       <c r="I16" s="84">
         <f t="shared" si="4"/>
-        <v>-3938.9200000000128</v>
+        <v>93.079999999987194</v>
       </c>
       <c r="J16" s="84">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.7458599999996225</v>
       </c>
       <c r="K16" s="85">
         <f t="shared" si="0"/>
@@ -3994,7 +3953,7 @@
       </c>
       <c r="L16" s="85">
         <f t="shared" si="1"/>
-        <v>158131.67068800004</v>
+        <v>129275.21154600002</v>
       </c>
       <c r="M16" s="154"/>
       <c r="N16" s="86">
@@ -4002,11 +3961,11 @@
       </c>
       <c r="O16" s="87">
         <f t="shared" si="2"/>
-        <v>154193.07999999999</v>
+        <v>129371.08</v>
       </c>
       <c r="P16" s="88">
         <f t="shared" si="3"/>
-        <v>158819.07999999999</v>
+        <v>133252.08000000002</v>
       </c>
       <c r="Q16" s="22">
         <f t="shared" si="7"/>
@@ -4014,7 +3973,7 @@
       </c>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="119"/>
       <c r="B17" s="149">
         <f t="shared" si="6"/>
@@ -4030,15 +3989,15 @@
         <v>7.59</v>
       </c>
       <c r="F17" s="32">
-        <v>617052.09</v>
+        <v>740858.09</v>
       </c>
       <c r="G17" s="32">
-        <v>617070</v>
+        <v>750000</v>
       </c>
       <c r="H17" s="33"/>
       <c r="I17" s="84">
         <f t="shared" si="4"/>
-        <v>-17.910000000032596</v>
+        <v>-9141.9100000000326</v>
       </c>
       <c r="J17" s="84">
         <f t="shared" si="5"/>
@@ -4050,7 +4009,7 @@
       </c>
       <c r="L17" s="85">
         <f t="shared" si="1"/>
-        <v>740876.16081599996</v>
+        <v>605678.30594699993</v>
       </c>
       <c r="M17" s="154"/>
       <c r="N17" s="86">
@@ -4058,11 +4017,11 @@
       </c>
       <c r="O17" s="87">
         <f t="shared" si="2"/>
-        <v>740858.09</v>
+        <v>596536.09</v>
       </c>
       <c r="P17" s="88">
         <f t="shared" si="3"/>
-        <v>763084.09</v>
+        <v>614432.09</v>
       </c>
       <c r="Q17" s="22">
         <f t="shared" si="7"/>
@@ -4070,36 +4029,36 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="119"/>
-      <c r="B18" s="183">
+      <c r="B18" s="149">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C18" s="183" t="s">
+      <c r="C18" s="149" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="183" t="s">
+      <c r="D18" s="149" t="s">
         <v>83</v>
       </c>
       <c r="E18" s="150">
         <v>1.62</v>
       </c>
       <c r="F18" s="32">
-        <v>138854.1</v>
+        <v>162877.1</v>
       </c>
       <c r="G18" s="32">
-        <f>F18</f>
-        <v>138854.1</v>
+        <f>162877</f>
+        <v>162877</v>
       </c>
       <c r="H18" s="33"/>
       <c r="I18" s="84">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.10000000000582077</v>
       </c>
       <c r="J18" s="84">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.9500000001717128E-3</v>
       </c>
       <c r="K18" s="85">
         <f t="shared" si="0"/>
@@ -4107,7 +4066,7 @@
       </c>
       <c r="L18" s="85">
         <f t="shared" si="1"/>
-        <v>158131.67068800004</v>
+        <v>129275.21154600002</v>
       </c>
       <c r="M18" s="154"/>
       <c r="N18" s="86">
@@ -4115,11 +4074,11 @@
       </c>
       <c r="O18" s="87">
         <f t="shared" si="2"/>
-        <v>158132.1</v>
+        <v>129275.1</v>
       </c>
       <c r="P18" s="88">
         <f t="shared" si="3"/>
-        <v>162876.1</v>
+        <v>133153.1</v>
       </c>
       <c r="Q18" s="22">
         <f t="shared" si="7"/>
@@ -4130,7 +4089,7 @@
       </c>
       <c r="S18" s="22"/>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="119"/>
       <c r="B19" s="149">
         <f t="shared" si="6"/>
@@ -4146,16 +4105,16 @@
         <v>1.78</v>
       </c>
       <c r="F19" s="32">
-        <v>585279.11</v>
+        <v>-97403.89</v>
       </c>
       <c r="G19" s="32">
-        <f>260000+300000+686788.23-G20</f>
-        <v>856433.11</v>
+        <f>224300.01-G20</f>
+        <v>97403.890000000014</v>
       </c>
       <c r="H19" s="33"/>
       <c r="I19" s="84">
         <f t="shared" si="4"/>
-        <v>-271154</v>
+        <v>-194807.78000000003</v>
       </c>
       <c r="J19" s="84">
         <f t="shared" si="5"/>
@@ -4167,7 +4126,7 @@
       </c>
       <c r="L19" s="85">
         <f t="shared" si="1"/>
-        <v>173749.613472</v>
+        <v>142043.13367400001</v>
       </c>
       <c r="M19" s="154"/>
       <c r="N19" s="86">
@@ -4175,22 +4134,22 @@
       </c>
       <c r="O19" s="87">
         <f t="shared" si="2"/>
-        <v>-97403.89</v>
+        <v>-52764.89</v>
       </c>
       <c r="P19" s="88">
         <f t="shared" si="3"/>
-        <v>-100325.89</v>
+        <v>-54347.89</v>
       </c>
       <c r="Q19" s="22">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="R19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S19" s="22"/>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="119"/>
       <c r="B20" s="149">
         <f t="shared" si="6"/>
@@ -4206,11 +4165,11 @@
         <v>1.3</v>
       </c>
       <c r="F20" s="32">
-        <v>390355.12</v>
+        <v>126896.12</v>
       </c>
       <c r="G20" s="32">
         <f>F20</f>
-        <v>390355.12</v>
+        <v>126896.12</v>
       </c>
       <c r="H20" s="33"/>
       <c r="I20" s="84">
@@ -4227,7 +4186,7 @@
       </c>
       <c r="L20" s="85">
         <f t="shared" si="1"/>
-        <v>126895.78512000002</v>
+        <v>103739.36729000001</v>
       </c>
       <c r="M20" s="154"/>
       <c r="N20" s="86">
@@ -4235,22 +4194,22 @@
       </c>
       <c r="O20" s="87">
         <f t="shared" si="2"/>
-        <v>126896.12</v>
+        <v>103739.12</v>
       </c>
       <c r="P20" s="88">
         <f t="shared" si="3"/>
-        <v>130703.12</v>
+        <v>106851.12</v>
       </c>
       <c r="Q20" s="22">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
       <c r="R20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="119"/>
       <c r="B21" s="149">
         <f t="shared" si="6"/>
@@ -4266,11 +4225,11 @@
         <v>1.38</v>
       </c>
       <c r="F21" s="32">
-        <v>115645.13</v>
+        <v>138746.13</v>
       </c>
       <c r="G21" s="32">
         <f>F21</f>
-        <v>115645.13</v>
+        <v>138746.13</v>
       </c>
       <c r="H21" s="33"/>
       <c r="I21" s="84">
@@ -4287,7 +4246,7 @@
       </c>
       <c r="L21" s="85">
         <f t="shared" si="1"/>
-        <v>134704.75651199999</v>
+        <v>110123.328354</v>
       </c>
       <c r="M21" s="154"/>
       <c r="N21" s="86">
@@ -4295,11 +4254,11 @@
       </c>
       <c r="O21" s="87">
         <f t="shared" si="2"/>
-        <v>134705.13</v>
+        <v>110123.13</v>
       </c>
       <c r="P21" s="88">
         <f t="shared" si="3"/>
-        <v>138746.13</v>
+        <v>113427.13</v>
       </c>
       <c r="Q21" s="22">
         <f t="shared" si="7"/>
@@ -4310,7 +4269,7 @@
       </c>
       <c r="S21" s="22"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="119"/>
       <c r="B22" s="149">
         <f t="shared" si="6"/>
@@ -4326,11 +4285,11 @@
         <v>1.87</v>
       </c>
       <c r="F22" s="32">
-        <v>156708.14000000001</v>
+        <v>188011.14</v>
       </c>
       <c r="G22" s="32">
         <f>F22</f>
-        <v>156708.14000000001</v>
+        <v>188011.14</v>
       </c>
       <c r="H22" s="33"/>
       <c r="I22" s="84">
@@ -4347,7 +4306,7 @@
       </c>
       <c r="L22" s="85">
         <f t="shared" si="1"/>
-        <v>182534.70628800002</v>
+        <v>149225.089871</v>
       </c>
       <c r="M22" s="154"/>
       <c r="N22" s="86">
@@ -4355,11 +4314,11 @@
       </c>
       <c r="O22" s="87">
         <f t="shared" si="2"/>
-        <v>182535.14</v>
+        <v>149225.14000000001</v>
       </c>
       <c r="P22" s="88">
         <f t="shared" si="3"/>
-        <v>188011.14</v>
+        <v>153702.14000000001</v>
       </c>
       <c r="Q22" s="22">
         <f t="shared" si="7"/>
@@ -4370,7 +4329,7 @@
       </c>
       <c r="S22" s="22"/>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="119"/>
       <c r="B23" s="149">
         <f t="shared" si="6"/>
@@ -4386,19 +4345,19 @@
         <v>2.91</v>
       </c>
       <c r="F23" s="32">
-        <v>818472.15</v>
+        <v>920768.15</v>
       </c>
       <c r="G23" s="32">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="H23" s="33"/>
       <c r="I23" s="84">
         <f t="shared" si="4"/>
-        <v>618472.15</v>
+        <v>920768.15</v>
       </c>
       <c r="J23" s="84">
         <f t="shared" si="5"/>
-        <v>18244.928425000002</v>
+        <v>27162.660425000002</v>
       </c>
       <c r="K23" s="85">
         <f t="shared" si="0"/>
@@ -4406,7 +4365,7 @@
       </c>
       <c r="L23" s="85">
         <f t="shared" si="1"/>
-        <v>284051.33438399999</v>
+        <v>232216.58370300001</v>
       </c>
       <c r="M23" s="154"/>
       <c r="N23" s="86">
@@ -4414,22 +4373,22 @@
       </c>
       <c r="O23" s="87">
         <f t="shared" si="2"/>
-        <v>920768.15</v>
+        <v>1180147.1499999999</v>
       </c>
       <c r="P23" s="88">
         <f t="shared" si="3"/>
-        <v>948391.15</v>
+        <v>1215551.1499999999</v>
       </c>
       <c r="Q23" s="22">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
       <c r="R23" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="S23" s="22"/>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="119"/>
       <c r="B24" s="149">
         <f t="shared" si="6"/>
@@ -4445,10 +4404,10 @@
         <v>2.14</v>
       </c>
       <c r="F24" s="32">
-        <v>184488.16</v>
+        <v>215157.16</v>
       </c>
       <c r="G24" s="32">
-        <v>184488</v>
+        <v>215157</v>
       </c>
       <c r="H24" s="33"/>
       <c r="I24" s="84">
@@ -4465,7 +4424,7 @@
       </c>
       <c r="L24" s="85">
         <f t="shared" si="1"/>
-        <v>208889.98473600004</v>
+        <v>170770.95846200001</v>
       </c>
       <c r="M24" s="154"/>
       <c r="N24" s="86">
@@ -4473,11 +4432,11 @@
       </c>
       <c r="O24" s="87">
         <f t="shared" si="2"/>
-        <v>208890.16</v>
+        <v>170771.16</v>
       </c>
       <c r="P24" s="88">
         <f t="shared" si="3"/>
-        <v>215157.16</v>
+        <v>175894.16</v>
       </c>
       <c r="Q24" s="22">
         <f t="shared" si="7"/>
@@ -4488,7 +4447,7 @@
       </c>
       <c r="S24" s="22"/>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="119" t="s">
         <v>15</v>
       </c>
@@ -4506,15 +4465,15 @@
         <v>0.89</v>
       </c>
       <c r="F25" s="32">
-        <v>70782.17</v>
+        <v>86857.17</v>
       </c>
       <c r="G25" s="32">
-        <v>70800</v>
+        <v>90000</v>
       </c>
       <c r="H25" s="33"/>
       <c r="I25" s="84">
         <f t="shared" si="4"/>
-        <v>-17.830000000001746</v>
+        <v>-3142.8300000000017</v>
       </c>
       <c r="J25" s="84">
         <f t="shared" si="5"/>
@@ -4526,7 +4485,7 @@
       </c>
       <c r="L25" s="85">
         <f t="shared" si="1"/>
-        <v>86874.806735999999</v>
+        <v>71021.566837000006</v>
       </c>
       <c r="M25" s="154"/>
       <c r="N25" s="86">
@@ -4534,18 +4493,18 @@
       </c>
       <c r="O25" s="87">
         <f t="shared" si="2"/>
-        <v>86857.17</v>
+        <v>67879.17</v>
       </c>
       <c r="P25" s="88">
         <f t="shared" si="3"/>
-        <v>89463.17</v>
+        <v>69915.17</v>
       </c>
       <c r="Q25" s="22">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="119" t="s">
         <v>15</v>
       </c>
@@ -4563,7 +4522,7 @@
         <v>0.95</v>
       </c>
       <c r="F26" s="32">
-        <v>3333182.18</v>
+        <v>3524243.18</v>
       </c>
       <c r="G26" s="32">
         <v>0</v>
@@ -4571,11 +4530,11 @@
       <c r="H26" s="33"/>
       <c r="I26" s="84">
         <f t="shared" si="4"/>
-        <v>3333182.18</v>
+        <v>3524243.18</v>
       </c>
       <c r="J26" s="84">
         <f t="shared" si="5"/>
-        <v>98328.874310000014</v>
+        <v>103965.17381000001</v>
       </c>
       <c r="K26" s="85">
         <f t="shared" si="0"/>
@@ -4583,7 +4542,7 @@
       </c>
       <c r="L26" s="85">
         <f t="shared" si="1"/>
-        <v>92731.535279999996</v>
+        <v>75809.537635000001</v>
       </c>
       <c r="M26" s="154"/>
       <c r="N26" s="86">
@@ -4591,11 +4550,11 @@
       </c>
       <c r="O26" s="87">
         <f t="shared" si="2"/>
-        <v>3524243.18</v>
+        <v>3704018.18</v>
       </c>
       <c r="P26" s="88">
         <f t="shared" si="3"/>
-        <v>3629970.18</v>
+        <v>3815139.18</v>
       </c>
       <c r="Q26" s="22">
         <f t="shared" si="7"/>
@@ -4604,7 +4563,7 @@
       <c r="R26" s="73"/>
       <c r="S26" s="72"/>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="119" t="s">
         <v>16</v>
       </c>
@@ -4622,19 +4581,19 @@
         <v>1.94</v>
       </c>
       <c r="F27" s="32">
-        <v>156999.19</v>
+        <v>195154.19</v>
       </c>
       <c r="G27" s="32">
-        <v>156900</v>
+        <v>195100</v>
       </c>
       <c r="H27" s="33"/>
       <c r="I27" s="84">
         <f t="shared" si="4"/>
-        <v>99.190000000002328</v>
+        <v>54.190000000002328</v>
       </c>
       <c r="J27" s="84">
         <f t="shared" si="5"/>
-        <v>2.926105000000069</v>
+        <v>1.5986050000000689</v>
       </c>
       <c r="K27" s="85">
         <f t="shared" si="0"/>
@@ -4642,7 +4601,7 @@
       </c>
       <c r="L27" s="85">
         <f t="shared" si="1"/>
-        <v>189367.55625600001</v>
+        <v>154811.05580200002</v>
       </c>
       <c r="M27" s="154"/>
       <c r="N27" s="86">
@@ -4650,18 +4609,18 @@
       </c>
       <c r="O27" s="87">
         <f t="shared" si="2"/>
-        <v>189470.19</v>
+        <v>154867.19</v>
       </c>
       <c r="P27" s="88">
         <f t="shared" si="3"/>
-        <v>195154.19</v>
+        <v>159513.19</v>
       </c>
       <c r="Q27" s="22">
         <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="119" t="s">
         <v>16</v>
       </c>
@@ -4679,19 +4638,19 @@
         <v>1.84</v>
       </c>
       <c r="F28" s="32">
-        <v>378029.2</v>
+        <v>414668.2</v>
       </c>
       <c r="G28" s="32">
-        <v>149703.20000000001</v>
+        <v>179606.2</v>
       </c>
       <c r="H28" s="33"/>
       <c r="I28" s="84">
         <f t="shared" si="4"/>
-        <v>228326</v>
+        <v>235062</v>
       </c>
       <c r="J28" s="84">
         <f t="shared" si="5"/>
-        <v>6735.6170000000002</v>
+        <v>6934.3290000000006</v>
       </c>
       <c r="K28" s="85">
         <f t="shared" si="0"/>
@@ -4699,7 +4658,7 @@
       </c>
       <c r="L28" s="85">
         <f t="shared" si="1"/>
-        <v>179606.34201600001</v>
+        <v>146831.10447200001</v>
       </c>
       <c r="M28" s="154"/>
       <c r="N28" s="86">
@@ -4707,18 +4666,18 @@
       </c>
       <c r="O28" s="87">
         <f t="shared" si="2"/>
-        <v>414668.2</v>
+        <v>388827.2</v>
       </c>
       <c r="P28" s="88">
         <f t="shared" si="3"/>
-        <v>427108.2</v>
+        <v>400492.2</v>
       </c>
       <c r="Q28" s="22">
         <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="119" t="s">
         <v>17</v>
       </c>
@@ -4736,19 +4695,19 @@
         <v>5.12</v>
       </c>
       <c r="F29" s="32">
-        <v>5460375.21</v>
+        <v>5728329.21</v>
       </c>
       <c r="G29" s="32">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="33"/>
       <c r="I29" s="84">
         <f t="shared" si="4"/>
-        <v>4860375.21</v>
+        <v>5728329.21</v>
       </c>
       <c r="J29" s="84">
         <f t="shared" si="5"/>
-        <v>143381.06869499999</v>
+        <v>168985.71169500001</v>
       </c>
       <c r="K29" s="85">
         <f t="shared" si="0"/>
@@ -4756,56 +4715,55 @@
       </c>
       <c r="L29" s="85">
         <f t="shared" si="1"/>
-        <v>499774.16908800002</v>
+        <v>408573.50809600001</v>
       </c>
       <c r="M29" s="85">
         <f>O$3*E29%</f>
-        <v>224798.05440000002</v>
+        <v>274505.36960000003</v>
       </c>
       <c r="N29" s="86">
         <v>0</v>
       </c>
       <c r="O29" s="87">
         <f t="shared" si="2"/>
-        <v>5728329.21</v>
+        <v>6580394.21</v>
       </c>
       <c r="P29" s="88">
         <f t="shared" si="3"/>
-        <v>5900179.21</v>
+        <v>6777806.21</v>
       </c>
       <c r="Q29" s="22">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="176">
+      <c r="B30" s="149">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="C30" s="176">
+      <c r="C30" s="149">
         <v>1101</v>
       </c>
-      <c r="D30" s="176" t="s">
+      <c r="D30" s="149" t="s">
         <v>82</v>
       </c>
       <c r="E30" s="150">
         <v>3.88</v>
       </c>
       <c r="F30" s="32">
-        <v>315679.21999999997</v>
+        <v>548769.22</v>
       </c>
       <c r="G30" s="32">
-        <f>316000</f>
-        <v>316000</v>
+        <v>550000</v>
       </c>
       <c r="H30" s="33"/>
       <c r="I30" s="84">
         <f t="shared" si="4"/>
-        <v>-320.78000000002794</v>
+        <v>-1230.7800000000279</v>
       </c>
       <c r="J30" s="84">
         <f t="shared" si="5"/>
@@ -4817,22 +4775,22 @@
       </c>
       <c r="L30" s="85">
         <f t="shared" si="1"/>
-        <v>378735.11251200002</v>
+        <v>309622.11160400003</v>
       </c>
       <c r="M30" s="85">
         <f t="shared" ref="M30:M66" si="8">O$3*E30%</f>
-        <v>170354.77559999999</v>
+        <v>208023.6004</v>
       </c>
       <c r="N30" s="86">
         <v>0</v>
       </c>
       <c r="O30" s="87">
         <f t="shared" si="2"/>
-        <v>548769.22</v>
+        <v>516415.22</v>
       </c>
       <c r="P30" s="88">
         <f t="shared" si="3"/>
-        <v>565232.22</v>
+        <v>531907.22</v>
       </c>
       <c r="Q30" s="22">
         <f t="shared" si="7"/>
@@ -4842,7 +4800,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="119" t="s">
         <v>18</v>
       </c>
@@ -4860,20 +4818,19 @@
         <v>0.92</v>
       </c>
       <c r="F31" s="32">
-        <v>156469.23000000001</v>
+        <v>130197.23</v>
       </c>
       <c r="G31" s="32">
-        <f>F31</f>
-        <v>156469.23000000001</v>
+        <v>0</v>
       </c>
       <c r="H31" s="33"/>
       <c r="I31" s="84">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>130197.23</v>
       </c>
       <c r="J31" s="84">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3840.8182850000003</v>
       </c>
       <c r="K31" s="85">
         <f t="shared" si="0"/>
@@ -4881,29 +4838,29 @@
       </c>
       <c r="L31" s="85">
         <f t="shared" si="1"/>
-        <v>89803.171008000005</v>
+        <v>73415.552236000003</v>
       </c>
       <c r="M31" s="85">
         <f t="shared" si="8"/>
-        <v>40393.400399999999</v>
+        <v>49325.183599999997</v>
       </c>
       <c r="N31" s="86">
         <v>0</v>
       </c>
       <c r="O31" s="87">
         <f t="shared" si="2"/>
-        <v>130197.23</v>
+        <v>256779.23</v>
       </c>
       <c r="P31" s="88">
         <f t="shared" si="3"/>
-        <v>134103.22999999998</v>
+        <v>264482.23</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="119" t="s">
         <v>18</v>
       </c>
@@ -4921,7 +4878,7 @@
         <v>1.43</v>
       </c>
       <c r="F32" s="32">
-        <v>5575057.2400000002</v>
+        <v>5941892.2400000002</v>
       </c>
       <c r="G32" s="32">
         <v>0</v>
@@ -4929,11 +4886,11 @@
       <c r="H32" s="33"/>
       <c r="I32" s="84">
         <f t="shared" si="4"/>
-        <v>5575057.2400000002</v>
+        <v>5941892.2400000002</v>
       </c>
       <c r="J32" s="84">
         <f t="shared" si="5"/>
-        <v>164464.18858000002</v>
+        <v>175285.82108000002</v>
       </c>
       <c r="K32" s="85">
         <f t="shared" si="0"/>
@@ -4941,29 +4898,29 @@
       </c>
       <c r="L32" s="85">
         <f t="shared" si="1"/>
-        <v>139585.36363199999</v>
+        <v>114113.304019</v>
       </c>
       <c r="M32" s="85">
         <f t="shared" si="8"/>
-        <v>62785.394099999998</v>
+        <v>76668.491900000008</v>
       </c>
       <c r="N32" s="86">
         <v>0</v>
       </c>
       <c r="O32" s="87">
         <f t="shared" si="2"/>
-        <v>5941892.2400000002</v>
+        <v>6307960.2400000002</v>
       </c>
       <c r="P32" s="88">
         <f t="shared" si="3"/>
-        <v>6120149.2400000002</v>
+        <v>6497199.2400000002</v>
       </c>
       <c r="Q32" s="22">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="119" t="s">
         <v>19</v>
       </c>
@@ -4981,15 +4938,15 @@
         <v>2.19</v>
       </c>
       <c r="F33" s="32">
-        <v>168427.25</v>
+        <v>304871.25</v>
       </c>
       <c r="G33" s="32">
-        <v>173480.25</v>
+        <v>314017.25</v>
       </c>
       <c r="H33" s="33"/>
       <c r="I33" s="84">
         <f t="shared" si="4"/>
-        <v>-5053</v>
+        <v>-9146</v>
       </c>
       <c r="J33" s="84">
         <f t="shared" si="5"/>
@@ -5001,29 +4958,29 @@
       </c>
       <c r="L33" s="85">
         <f t="shared" si="1"/>
-        <v>213770.59185599998</v>
+        <v>174760.93412699999</v>
       </c>
       <c r="M33" s="85">
         <f t="shared" si="8"/>
-        <v>96153.855299999996</v>
+        <v>117415.3827</v>
       </c>
       <c r="N33" s="86">
         <v>0</v>
       </c>
       <c r="O33" s="87">
         <f t="shared" si="2"/>
-        <v>304871.25</v>
+        <v>283030.25</v>
       </c>
       <c r="P33" s="88">
         <f t="shared" si="3"/>
-        <v>314017.25</v>
+        <v>291521.25</v>
       </c>
       <c r="Q33" s="22">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="119" t="s">
         <v>19</v>
       </c>
@@ -5041,11 +4998,11 @@
         <v>1.94</v>
       </c>
       <c r="F34" s="32">
-        <v>157839.26</v>
+        <v>282781.26</v>
       </c>
       <c r="G34" s="32">
         <f>F34</f>
-        <v>157839.26</v>
+        <v>282781.26</v>
       </c>
       <c r="H34" s="33"/>
       <c r="I34" s="84">
@@ -5062,29 +5019,29 @@
       </c>
       <c r="L34" s="85">
         <f t="shared" si="1"/>
-        <v>189367.55625600001</v>
+        <v>154811.05580200002</v>
       </c>
       <c r="M34" s="85">
         <f t="shared" si="8"/>
-        <v>85177.387799999997</v>
+        <v>104011.8002</v>
       </c>
       <c r="N34" s="86">
         <v>0</v>
       </c>
       <c r="O34" s="87">
         <f t="shared" si="2"/>
-        <v>274545.26</v>
+        <v>258823.26</v>
       </c>
       <c r="P34" s="88">
         <f t="shared" si="3"/>
-        <v>282781.26</v>
+        <v>266588.26</v>
       </c>
       <c r="Q34" s="22">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="119" t="s">
         <v>20</v>
       </c>
@@ -5102,19 +5059,20 @@
         <v>2.17</v>
       </c>
       <c r="F35" s="32">
-        <v>176552.27</v>
+        <v>488855.27</v>
       </c>
       <c r="G35" s="32">
-        <v>0</v>
+        <f>F35</f>
+        <v>488855.27</v>
       </c>
       <c r="H35" s="33"/>
       <c r="I35" s="84">
         <f t="shared" si="4"/>
-        <v>176552.27</v>
+        <v>0</v>
       </c>
       <c r="J35" s="84">
         <f t="shared" si="5"/>
-        <v>5208.2919650000003</v>
+        <v>0</v>
       </c>
       <c r="K35" s="85">
         <f t="shared" si="0"/>
@@ -5122,22 +5080,22 @@
       </c>
       <c r="L35" s="85">
         <f t="shared" si="1"/>
-        <v>211818.34900800002</v>
+        <v>173164.94386100001</v>
       </c>
       <c r="M35" s="85">
         <f t="shared" si="8"/>
-        <v>95275.737900000007</v>
+        <v>116343.09610000001</v>
       </c>
       <c r="N35" s="86">
         <v>0</v>
       </c>
       <c r="O35" s="87">
         <f t="shared" si="2"/>
-        <v>488855.27</v>
+        <v>289508.27</v>
       </c>
       <c r="P35" s="88">
         <f t="shared" si="3"/>
-        <v>503521.27</v>
+        <v>298193.27</v>
       </c>
       <c r="Q35" s="22">
         <f t="shared" si="7"/>
@@ -5148,7 +5106,7 @@
       </c>
       <c r="S35" s="21"/>
     </row>
-    <row r="36" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="119" t="s">
         <v>20</v>
       </c>
@@ -5166,20 +5124,19 @@
         <v>1.23</v>
       </c>
       <c r="F36" s="32">
-        <v>100073.28</v>
+        <v>179289.28</v>
       </c>
       <c r="G36" s="32">
-        <f>F36</f>
-        <v>100073.28</v>
+        <v>175000</v>
       </c>
       <c r="H36" s="33"/>
       <c r="I36" s="84">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4289.2799999999988</v>
       </c>
       <c r="J36" s="84">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>126.53375999999997</v>
       </c>
       <c r="K36" s="85">
         <f t="shared" si="0"/>
@@ -5187,22 +5144,22 @@
       </c>
       <c r="L36" s="85">
         <f t="shared" si="1"/>
-        <v>120062.93515200001</v>
+        <v>98153.401358999996</v>
       </c>
       <c r="M36" s="85">
         <f t="shared" si="8"/>
-        <v>54004.220099999999</v>
+        <v>65945.625899999999</v>
       </c>
       <c r="N36" s="86">
         <v>0</v>
       </c>
       <c r="O36" s="87">
         <f t="shared" si="2"/>
-        <v>174067.28</v>
+        <v>168515.28</v>
       </c>
       <c r="P36" s="88">
         <f t="shared" si="3"/>
-        <v>179289.28</v>
+        <v>173570.28</v>
       </c>
       <c r="Q36" s="22">
         <f t="shared" si="7"/>
@@ -5212,7 +5169,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="119" t="s">
         <v>21</v>
       </c>
@@ -5230,16 +5187,16 @@
         <v>1.29</v>
       </c>
       <c r="F37" s="32">
-        <v>213006.29</v>
+        <v>182558.29</v>
       </c>
       <c r="G37" s="32">
-        <f>104955.29*2+3096</f>
-        <v>213006.58</v>
+        <f>F37</f>
+        <v>182558.29</v>
       </c>
       <c r="H37" s="33"/>
       <c r="I37" s="84">
         <f t="shared" si="4"/>
-        <v>-0.28999999997904524</v>
+        <v>0</v>
       </c>
       <c r="J37" s="84">
         <f t="shared" si="5"/>
@@ -5251,29 +5208,29 @@
       </c>
       <c r="L37" s="85">
         <f t="shared" si="1"/>
-        <v>125919.663696</v>
+        <v>102941.37215700001</v>
       </c>
       <c r="M37" s="85">
         <f t="shared" si="8"/>
-        <v>56638.5723</v>
+        <v>69162.485700000005</v>
       </c>
       <c r="N37" s="86">
         <v>0</v>
       </c>
       <c r="O37" s="87">
         <f t="shared" si="2"/>
-        <v>182558.29</v>
+        <v>172104.29</v>
       </c>
       <c r="P37" s="88">
         <f t="shared" si="3"/>
-        <v>188035.29</v>
+        <v>177267.29</v>
       </c>
       <c r="Q37" s="22">
         <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="119" t="s">
         <v>21</v>
       </c>
@@ -5291,11 +5248,11 @@
         <v>1.36</v>
       </c>
       <c r="F38" s="32">
-        <v>110650.3</v>
+        <v>192464.3</v>
       </c>
       <c r="G38" s="32">
         <f>F38</f>
-        <v>110650.3</v>
+        <v>192464.3</v>
       </c>
       <c r="H38" s="33"/>
       <c r="I38" s="84">
@@ -5312,29 +5269,29 @@
       </c>
       <c r="L38" s="85">
         <f t="shared" si="1"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M38" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N38" s="86">
         <v>0</v>
       </c>
       <c r="O38" s="87">
         <f t="shared" si="2"/>
-        <v>192464.3</v>
+        <v>181443.3</v>
       </c>
       <c r="P38" s="88">
         <f t="shared" si="3"/>
-        <v>198238.3</v>
+        <v>186886.3</v>
       </c>
       <c r="Q38" s="22">
         <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="119" t="s">
         <v>22</v>
       </c>
@@ -5352,11 +5309,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F39" s="32">
-        <v>47189.31</v>
+        <v>82080.31</v>
       </c>
       <c r="G39" s="32">
         <f>F39</f>
-        <v>47189.31</v>
+        <v>82080.31</v>
       </c>
       <c r="H39" s="33"/>
       <c r="I39" s="84">
@@ -5373,22 +5330,22 @@
       </c>
       <c r="L39" s="85">
         <f t="shared" si="1"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M39" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N39" s="86">
         <v>0</v>
       </c>
       <c r="O39" s="87">
         <f t="shared" si="2"/>
-        <v>82080.31</v>
+        <v>77380.31</v>
       </c>
       <c r="P39" s="88">
         <f t="shared" si="3"/>
-        <v>84542.31</v>
+        <v>79701.31</v>
       </c>
       <c r="Q39" s="22">
         <f t="shared" si="7"/>
@@ -5398,7 +5355,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="119" t="s">
         <v>23</v>
       </c>
@@ -5416,11 +5373,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F40" s="32">
-        <v>47189.32</v>
+        <v>82080.320000000007</v>
       </c>
       <c r="G40" s="32">
         <f>F40</f>
-        <v>47189.32</v>
+        <v>82080.320000000007</v>
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="84">
@@ -5437,22 +5394,22 @@
       </c>
       <c r="L40" s="85">
         <f t="shared" ref="L40:L66" si="10">O$1*E40%</f>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M40" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N40" s="86">
         <v>0</v>
       </c>
       <c r="O40" s="87">
         <f t="shared" ref="O40:O66" si="11">ROUND(SUM(I40:N40),0) + Q40</f>
-        <v>82080.320000000007</v>
+        <v>77380.320000000007</v>
       </c>
       <c r="P40" s="88">
         <f t="shared" si="3"/>
-        <v>84542.32</v>
+        <v>79701.320000000007</v>
       </c>
       <c r="Q40" s="22">
         <f t="shared" si="7"/>
@@ -5462,7 +5419,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="119" t="s">
         <v>24</v>
       </c>
@@ -5480,11 +5437,11 @@
         <v>1.36</v>
       </c>
       <c r="F41" s="32">
-        <v>110650.33</v>
+        <v>192464.33</v>
       </c>
       <c r="G41" s="32">
         <f>F41</f>
-        <v>110650.33</v>
+        <v>192464.33</v>
       </c>
       <c r="H41" s="33"/>
       <c r="I41" s="84">
@@ -5501,22 +5458,22 @@
       </c>
       <c r="L41" s="85">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M41" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N41" s="86">
         <v>0</v>
       </c>
       <c r="O41" s="87">
         <f t="shared" si="11"/>
-        <v>192464.33</v>
+        <v>181443.33</v>
       </c>
       <c r="P41" s="88">
         <f t="shared" si="3"/>
-        <v>198238.33</v>
+        <v>186886.33</v>
       </c>
       <c r="Q41" s="22">
         <f t="shared" si="7"/>
@@ -5526,7 +5483,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="119" t="s">
         <v>25</v>
       </c>
@@ -5544,11 +5501,11 @@
         <v>1.67</v>
       </c>
       <c r="F42" s="32">
-        <v>135872.34</v>
+        <v>236335.34</v>
       </c>
       <c r="G42" s="32">
         <f>F42</f>
-        <v>135872.34</v>
+        <v>236335.34</v>
       </c>
       <c r="H42" s="33"/>
       <c r="I42" s="84">
@@ -5565,22 +5522,22 @@
       </c>
       <c r="L42" s="85">
         <f t="shared" si="10"/>
-        <v>163012.27780800001</v>
+        <v>133265.18721100001</v>
       </c>
       <c r="M42" s="85">
         <f t="shared" si="8"/>
-        <v>73322.802899999995</v>
+        <v>89535.931100000002</v>
       </c>
       <c r="N42" s="86">
         <v>0</v>
       </c>
       <c r="O42" s="87">
         <f t="shared" si="11"/>
-        <v>236335.34</v>
+        <v>222801.34</v>
       </c>
       <c r="P42" s="88">
         <f t="shared" si="3"/>
-        <v>243425.34</v>
+        <v>229485.34</v>
       </c>
       <c r="Q42" s="22">
         <f t="shared" si="7"/>
@@ -5590,7 +5547,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="119" t="s">
         <v>27</v>
       </c>
@@ -5608,16 +5565,16 @@
         <v>2.17</v>
       </c>
       <c r="F43" s="32">
-        <v>176553.35</v>
+        <v>298795.34999999998</v>
       </c>
       <c r="G43" s="32">
-        <f>284925.71-G44</f>
-        <v>184852.35000000003</v>
+        <f>472862.71-G44</f>
+        <v>298795.35000000003</v>
       </c>
       <c r="H43" s="33"/>
       <c r="I43" s="84">
         <f t="shared" si="4"/>
-        <v>-8299.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="J43" s="84">
         <f t="shared" si="5"/>
@@ -5629,22 +5586,22 @@
       </c>
       <c r="L43" s="85">
         <f t="shared" si="10"/>
-        <v>211818.34900800002</v>
+        <v>173164.94386100001</v>
       </c>
       <c r="M43" s="85">
         <f t="shared" si="8"/>
-        <v>95275.737900000007</v>
+        <v>116343.09610000001</v>
       </c>
       <c r="N43" s="86">
         <v>0</v>
       </c>
       <c r="O43" s="87">
         <f t="shared" si="11"/>
-        <v>298795.34999999998</v>
+        <v>289508.34999999998</v>
       </c>
       <c r="P43" s="88">
         <f t="shared" si="3"/>
-        <v>307759.34999999998</v>
+        <v>298193.34999999998</v>
       </c>
       <c r="Q43" s="22">
         <f t="shared" si="7"/>
@@ -5654,7 +5611,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="119" t="s">
         <v>27</v>
       </c>
@@ -5672,11 +5629,11 @@
         <v>1.23</v>
       </c>
       <c r="F44" s="32">
-        <v>100073.36</v>
+        <v>174067.36</v>
       </c>
       <c r="G44" s="32">
         <f>F44</f>
-        <v>100073.36</v>
+        <v>174067.36</v>
       </c>
       <c r="H44" s="33"/>
       <c r="I44" s="84">
@@ -5693,22 +5650,22 @@
       </c>
       <c r="L44" s="85">
         <f t="shared" si="10"/>
-        <v>120062.93515200001</v>
+        <v>98153.401358999996</v>
       </c>
       <c r="M44" s="85">
         <f t="shared" si="8"/>
-        <v>54004.220099999999</v>
+        <v>65945.625899999999</v>
       </c>
       <c r="N44" s="86">
         <v>0</v>
       </c>
       <c r="O44" s="87">
         <f t="shared" si="11"/>
-        <v>174067.36</v>
+        <v>164099.35999999999</v>
       </c>
       <c r="P44" s="88">
         <f t="shared" si="3"/>
-        <v>179289.36</v>
+        <v>169022.36</v>
       </c>
       <c r="Q44" s="22">
         <f t="shared" si="7"/>
@@ -5718,7 +5675,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="119" t="s">
         <v>27</v>
       </c>
@@ -5736,19 +5693,20 @@
         <v>1.23</v>
       </c>
       <c r="F45" s="32">
-        <v>100073.37</v>
+        <v>277093.37</v>
       </c>
       <c r="G45" s="32">
-        <v>0</v>
+        <f>120063.37+100073.37</f>
+        <v>220136.74</v>
       </c>
       <c r="H45" s="33"/>
       <c r="I45" s="84">
         <f t="shared" si="4"/>
-        <v>100073.37</v>
+        <v>56956.630000000005</v>
       </c>
       <c r="J45" s="84">
         <f t="shared" si="5"/>
-        <v>2952.1644150000002</v>
+        <v>1680.2205850000003</v>
       </c>
       <c r="K45" s="85">
         <f t="shared" si="9"/>
@@ -5756,22 +5714,22 @@
       </c>
       <c r="L45" s="85">
         <f t="shared" si="10"/>
-        <v>120062.93515200001</v>
+        <v>98153.401358999996</v>
       </c>
       <c r="M45" s="85">
         <f t="shared" si="8"/>
-        <v>54004.220099999999</v>
+        <v>65945.625899999999</v>
       </c>
       <c r="N45" s="86">
         <v>0</v>
       </c>
       <c r="O45" s="87">
         <f t="shared" si="11"/>
-        <v>277093.37</v>
+        <v>222736.37</v>
       </c>
       <c r="P45" s="88">
         <f t="shared" si="3"/>
-        <v>285406.37</v>
+        <v>229418.37</v>
       </c>
       <c r="Q45" s="22">
         <f t="shared" si="7"/>
@@ -5779,7 +5737,7 @@
       </c>
       <c r="R45" s="72"/>
     </row>
-    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="119" t="s">
         <v>27</v>
       </c>
@@ -5797,19 +5755,19 @@
         <v>1.36</v>
       </c>
       <c r="F46" s="32">
-        <v>710065.38</v>
+        <v>192430.38</v>
       </c>
       <c r="G46" s="32">
-        <v>710100</v>
+        <v>0</v>
       </c>
       <c r="H46" s="33"/>
       <c r="I46" s="84">
         <f t="shared" si="4"/>
-        <v>-34.619999999995343</v>
+        <v>192430.38</v>
       </c>
       <c r="J46" s="84">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5676.6962100000001</v>
       </c>
       <c r="K46" s="85">
         <f t="shared" si="9"/>
@@ -5817,29 +5775,29 @@
       </c>
       <c r="L46" s="85">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M46" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N46" s="86">
         <v>0</v>
       </c>
       <c r="O46" s="87">
         <f t="shared" si="11"/>
-        <v>192430.38</v>
+        <v>379550.38</v>
       </c>
       <c r="P46" s="88">
         <f t="shared" si="3"/>
-        <v>198203.38</v>
+        <v>390937.38</v>
       </c>
       <c r="Q46" s="22">
         <f t="shared" si="7"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="119" t="s">
         <v>27</v>
       </c>
@@ -5857,11 +5815,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F47" s="32">
-        <v>48605.39</v>
+        <v>84542.39</v>
       </c>
       <c r="G47" s="32">
         <f>F47</f>
-        <v>48605.39</v>
+        <v>84542.39</v>
       </c>
       <c r="H47" s="40"/>
       <c r="I47" s="84">
@@ -5878,29 +5836,29 @@
       </c>
       <c r="L47" s="85">
         <f t="shared" si="10"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M47" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N47" s="86">
         <v>0</v>
       </c>
       <c r="O47" s="87">
         <f t="shared" si="11"/>
-        <v>82080.39</v>
+        <v>77380.39</v>
       </c>
       <c r="P47" s="88">
         <f t="shared" si="3"/>
-        <v>84542.39</v>
+        <v>79701.39</v>
       </c>
       <c r="Q47" s="22">
         <f t="shared" si="7"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="72"/>
       <c r="B48" s="149">
         <f t="shared" ref="B48:B66" si="12">B47+1</f>
@@ -5916,11 +5874,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F48" s="32">
-        <v>48605.4</v>
+        <v>84542.399999999994</v>
       </c>
       <c r="G48" s="32">
         <f>F48</f>
-        <v>48605.4</v>
+        <v>84542.399999999994</v>
       </c>
       <c r="H48" s="40"/>
       <c r="I48" s="84">
@@ -5937,29 +5895,29 @@
       </c>
       <c r="L48" s="85">
         <f t="shared" si="10"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M48" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N48" s="86">
         <v>0</v>
       </c>
       <c r="O48" s="87">
         <f t="shared" si="11"/>
-        <v>82080.399999999994</v>
+        <v>77380.399999999994</v>
       </c>
       <c r="P48" s="88">
         <f t="shared" si="3"/>
-        <v>84542.399999999994</v>
+        <v>79701.399999999994</v>
       </c>
       <c r="Q48" s="22">
         <f t="shared" si="7"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="72"/>
       <c r="B49" s="149">
         <f t="shared" si="12"/>
@@ -5975,15 +5933,15 @@
         <v>1.36</v>
       </c>
       <c r="F49" s="32">
-        <v>106466.41</v>
+        <v>188931.41</v>
       </c>
       <c r="G49" s="32">
-        <v>110000</v>
+        <v>190000</v>
       </c>
       <c r="H49" s="40"/>
       <c r="I49" s="84">
         <f t="shared" si="4"/>
-        <v>-3533.5899999999965</v>
+        <v>-1068.5899999999965</v>
       </c>
       <c r="J49" s="84">
         <f t="shared" si="5"/>
@@ -5995,29 +5953,32 @@
       </c>
       <c r="L49" s="85">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M49" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N49" s="86">
         <v>0</v>
       </c>
       <c r="O49" s="87">
         <f t="shared" si="11"/>
-        <v>188931.41</v>
+        <v>180374.41</v>
       </c>
       <c r="P49" s="88">
         <f t="shared" si="3"/>
-        <v>194599.41</v>
+        <v>185785.41</v>
       </c>
       <c r="Q49" s="22">
         <f t="shared" si="7"/>
         <v>0.4100000000000002</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R49" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="72"/>
       <c r="B50" s="149">
         <f t="shared" si="12"/>
@@ -6033,7 +5994,7 @@
         <v>1.67</v>
       </c>
       <c r="F50" s="32">
-        <v>1749607.42</v>
+        <v>2037556.42</v>
       </c>
       <c r="G50" s="32">
         <v>0</v>
@@ -6041,11 +6002,11 @@
       <c r="H50" s="40"/>
       <c r="I50" s="84">
         <f t="shared" si="4"/>
-        <v>1749607.42</v>
+        <v>2037556.42</v>
       </c>
       <c r="J50" s="84">
         <f t="shared" si="5"/>
-        <v>51613.418890000001</v>
+        <v>60107.914389999998</v>
       </c>
       <c r="K50" s="85">
         <f t="shared" si="9"/>
@@ -6053,29 +6014,29 @@
       </c>
       <c r="L50" s="85">
         <f t="shared" si="10"/>
-        <v>163012.27780800001</v>
+        <v>133265.18721100001</v>
       </c>
       <c r="M50" s="85">
         <f t="shared" si="8"/>
-        <v>73322.802899999995</v>
+        <v>89535.931100000002</v>
       </c>
       <c r="N50" s="86">
         <v>0</v>
       </c>
       <c r="O50" s="87">
         <f t="shared" si="11"/>
-        <v>2037556.42</v>
+        <v>2320465.42</v>
       </c>
       <c r="P50" s="88">
         <f t="shared" si="3"/>
-        <v>2098683.42</v>
+        <v>2390079.42</v>
       </c>
       <c r="Q50" s="22">
         <f t="shared" si="7"/>
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="72"/>
       <c r="B51" s="149">
         <f t="shared" si="12"/>
@@ -6091,11 +6052,11 @@
         <v>2.17</v>
       </c>
       <c r="F51" s="32">
-        <v>170988.43</v>
+        <v>307094.43</v>
       </c>
       <c r="G51" s="32">
         <f>F51</f>
-        <v>170988.43</v>
+        <v>307094.43</v>
       </c>
       <c r="H51" s="40"/>
       <c r="I51" s="84">
@@ -6112,29 +6073,29 @@
       </c>
       <c r="L51" s="85">
         <f t="shared" si="10"/>
-        <v>211818.34900800002</v>
+        <v>173164.94386100001</v>
       </c>
       <c r="M51" s="85">
         <f t="shared" si="8"/>
-        <v>95275.737900000007</v>
+        <v>116343.09610000001</v>
       </c>
       <c r="N51" s="86">
         <v>0</v>
       </c>
       <c r="O51" s="87">
         <f t="shared" si="11"/>
-        <v>307094.43</v>
+        <v>289508.43</v>
       </c>
       <c r="P51" s="88">
         <f t="shared" si="3"/>
-        <v>316307.43</v>
+        <v>298193.43</v>
       </c>
       <c r="Q51" s="22">
         <f t="shared" si="7"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="72"/>
       <c r="B52" s="149">
         <f t="shared" si="12"/>
@@ -6150,19 +6111,20 @@
         <v>1.23</v>
       </c>
       <c r="F52" s="32">
-        <v>100073.44</v>
+        <v>277093.44</v>
       </c>
       <c r="G52" s="32">
-        <v>0</v>
+        <f>F52</f>
+        <v>277093.44</v>
       </c>
       <c r="H52" s="40"/>
       <c r="I52" s="84">
         <f t="shared" si="4"/>
-        <v>100073.44</v>
+        <v>0</v>
       </c>
       <c r="J52" s="84">
         <f t="shared" si="5"/>
-        <v>2952.1664800000003</v>
+        <v>0</v>
       </c>
       <c r="K52" s="85">
         <f t="shared" si="9"/>
@@ -6170,29 +6132,29 @@
       </c>
       <c r="L52" s="85">
         <f t="shared" si="10"/>
-        <v>120062.93515200001</v>
+        <v>98153.401358999996</v>
       </c>
       <c r="M52" s="85">
         <f t="shared" si="8"/>
-        <v>54004.220099999999</v>
+        <v>65945.625899999999</v>
       </c>
       <c r="N52" s="86">
         <v>0</v>
       </c>
       <c r="O52" s="87">
         <f t="shared" si="11"/>
-        <v>277093.44</v>
+        <v>164099.44</v>
       </c>
       <c r="P52" s="88">
         <f t="shared" si="3"/>
-        <v>285406.44</v>
+        <v>169022.44</v>
       </c>
       <c r="Q52" s="22">
         <f t="shared" si="7"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="72"/>
       <c r="B53" s="149">
         <f t="shared" si="12"/>
@@ -6208,15 +6170,15 @@
         <v>1.29</v>
       </c>
       <c r="F53" s="32">
-        <v>104955.45</v>
+        <v>179409.45</v>
       </c>
       <c r="G53" s="32">
-        <v>108104.45</v>
+        <v>184791.45</v>
       </c>
       <c r="H53" s="40"/>
       <c r="I53" s="84">
         <f t="shared" si="4"/>
-        <v>-3149</v>
+        <v>-5382</v>
       </c>
       <c r="J53" s="84">
         <f t="shared" si="5"/>
@@ -6228,29 +6190,29 @@
       </c>
       <c r="L53" s="85">
         <f t="shared" si="10"/>
-        <v>125919.663696</v>
+        <v>102941.37215700001</v>
       </c>
       <c r="M53" s="85">
         <f t="shared" si="8"/>
-        <v>56638.5723</v>
+        <v>69162.485700000005</v>
       </c>
       <c r="N53" s="86">
         <v>0</v>
       </c>
       <c r="O53" s="87">
         <f t="shared" si="11"/>
-        <v>179409.45</v>
+        <v>166722.45000000001</v>
       </c>
       <c r="P53" s="88">
         <f t="shared" si="3"/>
-        <v>184791.45</v>
+        <v>171724.45</v>
       </c>
       <c r="Q53" s="22">
         <f t="shared" si="7"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="72"/>
       <c r="B54" s="149">
         <f t="shared" si="12"/>
@@ -6266,11 +6228,11 @@
         <v>1.36</v>
       </c>
       <c r="F54" s="32">
-        <v>110650.46</v>
+        <v>192464.46</v>
       </c>
       <c r="G54" s="32">
         <f>F54</f>
-        <v>110650.46</v>
+        <v>192464.46</v>
       </c>
       <c r="H54" s="40"/>
       <c r="I54" s="84">
@@ -6287,29 +6249,29 @@
       </c>
       <c r="L54" s="85">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M54" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N54" s="86">
         <v>0</v>
       </c>
       <c r="O54" s="87">
         <f t="shared" si="11"/>
-        <v>192464.46</v>
+        <v>181443.46</v>
       </c>
       <c r="P54" s="88">
         <f t="shared" si="3"/>
-        <v>198238.46</v>
+        <v>186886.46</v>
       </c>
       <c r="Q54" s="22">
         <f t="shared" si="7"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="72"/>
       <c r="B55" s="149">
         <f t="shared" si="12"/>
@@ -6325,11 +6287,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F55" s="32">
-        <v>47189.47</v>
+        <v>82080.47</v>
       </c>
       <c r="G55" s="32">
         <f>F55</f>
-        <v>47189.47</v>
+        <v>82080.47</v>
       </c>
       <c r="H55" s="40"/>
       <c r="I55" s="84">
@@ -6346,29 +6308,29 @@
       </c>
       <c r="L55" s="85">
         <f t="shared" si="10"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M55" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N55" s="86">
         <v>0</v>
       </c>
       <c r="O55" s="87">
         <f t="shared" si="11"/>
-        <v>82080.47</v>
+        <v>77380.47</v>
       </c>
       <c r="P55" s="88">
         <f t="shared" si="3"/>
-        <v>84542.47</v>
+        <v>79701.47</v>
       </c>
       <c r="Q55" s="22">
         <f t="shared" si="7"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="72"/>
       <c r="B56" s="149">
         <f t="shared" si="12"/>
@@ -6384,15 +6346,15 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F56" s="32">
-        <v>45773.48</v>
+        <v>80707.48</v>
       </c>
       <c r="G56" s="32">
-        <v>47146.48</v>
+        <v>83128.479999999996</v>
       </c>
       <c r="H56" s="40"/>
       <c r="I56" s="84">
         <f t="shared" si="4"/>
-        <v>-1373</v>
+        <v>-2421</v>
       </c>
       <c r="J56" s="84">
         <f t="shared" si="5"/>
@@ -6404,22 +6366,22 @@
       </c>
       <c r="L56" s="85">
         <f t="shared" si="10"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M56" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N56" s="86">
         <v>0</v>
       </c>
       <c r="O56" s="87">
         <f t="shared" si="11"/>
-        <v>80707.48</v>
+        <v>74959.48</v>
       </c>
       <c r="P56" s="88">
         <f t="shared" si="3"/>
-        <v>83128.479999999996</v>
+        <v>77208.479999999996</v>
       </c>
       <c r="Q56" s="22">
         <f t="shared" si="7"/>
@@ -6429,7 +6391,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="72"/>
       <c r="B57" s="149">
         <f t="shared" si="12"/>
@@ -6445,15 +6407,15 @@
         <v>1.36</v>
       </c>
       <c r="F57" s="32">
-        <v>107330.49</v>
+        <v>189244.49</v>
       </c>
       <c r="G57" s="32">
-        <v>110550.49</v>
+        <v>194921.49</v>
       </c>
       <c r="H57" s="40"/>
       <c r="I57" s="84">
         <f t="shared" si="4"/>
-        <v>-3220</v>
+        <v>-5677</v>
       </c>
       <c r="J57" s="84">
         <f t="shared" si="5"/>
@@ -6465,22 +6427,22 @@
       </c>
       <c r="L57" s="85">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M57" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N57" s="86">
         <v>0</v>
       </c>
       <c r="O57" s="87">
         <f t="shared" si="11"/>
-        <v>189244.49</v>
+        <v>175766.49</v>
       </c>
       <c r="P57" s="88">
         <f t="shared" si="3"/>
-        <v>194921.49</v>
+        <v>181039.49</v>
       </c>
       <c r="Q57" s="22">
         <f t="shared" si="7"/>
@@ -6490,7 +6452,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="72"/>
       <c r="B58" s="149">
         <f t="shared" si="12"/>
@@ -6506,15 +6468,15 @@
         <v>1.67</v>
       </c>
       <c r="F58" s="32">
-        <v>131796.5</v>
+        <v>232381.5</v>
       </c>
       <c r="G58" s="32">
-        <v>135750.5</v>
+        <v>239352.5</v>
       </c>
       <c r="H58" s="40"/>
       <c r="I58" s="84">
         <f t="shared" si="4"/>
-        <v>-3954</v>
+        <v>-6971</v>
       </c>
       <c r="J58" s="84">
         <f t="shared" si="5"/>
@@ -6526,22 +6488,22 @@
       </c>
       <c r="L58" s="85">
         <f t="shared" si="10"/>
-        <v>163012.27780800001</v>
+        <v>133265.18721100001</v>
       </c>
       <c r="M58" s="85">
         <f t="shared" si="8"/>
-        <v>73322.802899999995</v>
+        <v>89535.931100000002</v>
       </c>
       <c r="N58" s="86">
         <v>0</v>
       </c>
       <c r="O58" s="87">
         <f t="shared" si="11"/>
-        <v>232381.5</v>
+        <v>215830.5</v>
       </c>
       <c r="P58" s="88">
         <f t="shared" si="3"/>
-        <v>239352.5</v>
+        <v>222305.5</v>
       </c>
       <c r="Q58" s="22">
         <f t="shared" si="7"/>
@@ -6551,7 +6513,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="72"/>
       <c r="B59" s="149">
         <f t="shared" si="12"/>
@@ -6567,15 +6529,15 @@
         <v>2.17</v>
       </c>
       <c r="F59" s="32">
-        <v>171385.51</v>
+        <v>301952.51</v>
       </c>
       <c r="G59" s="32">
-        <v>176527.51</v>
+        <v>311011.51</v>
       </c>
       <c r="H59" s="40"/>
       <c r="I59" s="84">
         <f t="shared" si="4"/>
-        <v>-5142</v>
+        <v>-9059</v>
       </c>
       <c r="J59" s="84">
         <f t="shared" si="5"/>
@@ -6587,53 +6549,53 @@
       </c>
       <c r="L59" s="85">
         <f t="shared" si="10"/>
-        <v>211818.34900800002</v>
+        <v>173164.94386100001</v>
       </c>
       <c r="M59" s="85">
         <f t="shared" si="8"/>
-        <v>95275.737900000007</v>
+        <v>116343.09610000001</v>
       </c>
       <c r="N59" s="86">
         <v>0</v>
       </c>
       <c r="O59" s="87">
         <f t="shared" si="11"/>
-        <v>301952.51</v>
+        <v>280449.51</v>
       </c>
       <c r="P59" s="88">
         <f t="shared" si="3"/>
-        <v>311011.51</v>
+        <v>288862.51</v>
       </c>
       <c r="Q59" s="22">
         <f t="shared" si="7"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" s="167"/>
-      <c r="B60" s="168">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="164"/>
+      <c r="B60" s="149">
         <f t="shared" si="12"/>
         <v>52</v>
       </c>
-      <c r="C60" s="168">
+      <c r="C60" s="149">
         <v>5507</v>
       </c>
-      <c r="D60" s="168" t="s">
+      <c r="D60" s="149" t="s">
         <v>139</v>
       </c>
       <c r="E60" s="150">
         <v>1.79</v>
       </c>
       <c r="F60" s="32">
-        <v>141266.51999999999</v>
+        <v>248584.52</v>
       </c>
       <c r="G60" s="32">
-        <v>146000</v>
+        <v>260000</v>
       </c>
       <c r="H60" s="40"/>
       <c r="I60" s="84">
         <f t="shared" si="4"/>
-        <v>-4733.4800000000105</v>
+        <v>-11415.48000000001</v>
       </c>
       <c r="J60" s="84">
         <f t="shared" si="5"/>
@@ -6645,29 +6607,29 @@
       </c>
       <c r="L60" s="85">
         <f t="shared" si="10"/>
-        <v>174725.73489600001</v>
+        <v>142841.128807</v>
       </c>
       <c r="M60" s="85">
         <f t="shared" si="8"/>
-        <v>78591.507299999997</v>
+        <v>95969.650699999998</v>
       </c>
       <c r="N60" s="86">
         <v>0</v>
       </c>
       <c r="O60" s="87">
         <f t="shared" si="11"/>
-        <v>248584.52</v>
+        <v>227395.52</v>
       </c>
       <c r="P60" s="88">
         <f t="shared" si="3"/>
-        <v>256042.52</v>
+        <v>234217.52</v>
       </c>
       <c r="Q60" s="22">
         <f t="shared" si="7"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="72"/>
       <c r="B61" s="149">
         <f t="shared" si="12"/>
@@ -6683,7 +6645,7 @@
         <v>1.29</v>
       </c>
       <c r="F61" s="32">
-        <v>127518.53</v>
+        <v>313839.53000000003</v>
       </c>
       <c r="G61" s="32">
         <v>0</v>
@@ -6691,11 +6653,11 @@
       <c r="H61" s="40"/>
       <c r="I61" s="84">
         <f t="shared" si="4"/>
-        <v>127518.53</v>
+        <v>313839.53000000003</v>
       </c>
       <c r="J61" s="84">
         <f t="shared" si="5"/>
-        <v>3761.7966350000002</v>
+        <v>9258.2661350000017</v>
       </c>
       <c r="K61" s="85">
         <f t="shared" si="9"/>
@@ -6703,54 +6665,53 @@
       </c>
       <c r="L61" s="85">
         <f t="shared" si="10"/>
-        <v>125919.663696</v>
+        <v>102941.37215700001</v>
       </c>
       <c r="M61" s="85">
         <f t="shared" si="8"/>
-        <v>56638.5723</v>
+        <v>69162.485700000005</v>
       </c>
       <c r="N61" s="86">
         <v>0</v>
       </c>
       <c r="O61" s="87">
         <f t="shared" si="11"/>
-        <v>313839.53000000003</v>
+        <v>495202.53</v>
       </c>
       <c r="P61" s="88">
         <f t="shared" si="3"/>
-        <v>323254.53000000003</v>
+        <v>510058.53</v>
       </c>
       <c r="Q61" s="22">
         <f t="shared" si="7"/>
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="72"/>
-      <c r="B62" s="164">
+      <c r="B62" s="149">
         <f t="shared" si="12"/>
         <v>54</v>
       </c>
-      <c r="C62" s="164">
+      <c r="C62" s="149">
         <v>5501</v>
       </c>
-      <c r="D62" s="164" t="s">
+      <c r="D62" s="149" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="165">
+      <c r="E62" s="150">
         <v>1.36</v>
       </c>
-      <c r="F62" s="166">
-        <v>221075.54</v>
+      <c r="F62" s="32">
+        <v>185829.54</v>
       </c>
       <c r="G62" s="32">
-        <f>227710.54</f>
-        <v>227710.54</v>
+        <v>186000</v>
       </c>
       <c r="H62" s="40"/>
       <c r="I62" s="84">
         <f t="shared" si="4"/>
-        <v>-6635</v>
+        <v>-170.45999999999185</v>
       </c>
       <c r="J62" s="84">
         <f t="shared" si="5"/>
@@ -6762,29 +6723,29 @@
       </c>
       <c r="L62" s="85">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M62" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N62" s="86">
         <v>0</v>
       </c>
       <c r="O62" s="87">
         <f t="shared" si="11"/>
-        <v>185829.54</v>
+        <v>181272.54</v>
       </c>
       <c r="P62" s="88">
         <f t="shared" si="3"/>
-        <v>191404.54</v>
+        <v>186710.54</v>
       </c>
       <c r="Q62" s="22">
         <f t="shared" si="7"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="72"/>
       <c r="B63" s="149">
         <f t="shared" si="12"/>
@@ -6800,7 +6761,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F63" s="32">
-        <v>-398591.45</v>
+        <v>-316510.45</v>
       </c>
       <c r="G63" s="32">
         <v>0</v>
@@ -6808,7 +6769,7 @@
       <c r="H63" s="40"/>
       <c r="I63" s="84">
         <f t="shared" si="4"/>
-        <v>-398591.45</v>
+        <v>-316510.45</v>
       </c>
       <c r="J63" s="84">
         <f t="shared" si="5"/>
@@ -6820,22 +6781,22 @@
       </c>
       <c r="L63" s="85">
         <f t="shared" si="10"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M63" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N63" s="86">
         <v>0</v>
       </c>
       <c r="O63" s="87">
         <f t="shared" si="11"/>
-        <v>-316510.45</v>
+        <v>-239129.45</v>
       </c>
       <c r="P63" s="88">
         <f t="shared" si="3"/>
-        <v>-326005.45</v>
+        <v>-246303.45</v>
       </c>
       <c r="Q63" s="22">
         <f t="shared" si="7"/>
@@ -6845,7 +6806,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="72"/>
       <c r="B64" s="149">
         <f t="shared" si="12"/>
@@ -6861,19 +6822,19 @@
         <v>1.36</v>
       </c>
       <c r="F64" s="32">
-        <v>110596.56</v>
+        <v>192461.56</v>
       </c>
       <c r="G64" s="32">
-        <v>110600</v>
+        <v>191570</v>
       </c>
       <c r="H64" s="40"/>
       <c r="I64" s="34">
         <f t="shared" si="4"/>
-        <v>-3.4400000000023283</v>
+        <v>891.55999999999767</v>
       </c>
       <c r="J64" s="34">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>26.301019999999934</v>
       </c>
       <c r="K64" s="35">
         <f t="shared" si="9"/>
@@ -6881,22 +6842,22 @@
       </c>
       <c r="L64" s="35">
         <f t="shared" si="10"/>
-        <v>132752.513664</v>
+        <v>108527.338088</v>
       </c>
       <c r="M64" s="85">
         <f t="shared" si="8"/>
-        <v>59711.983200000002</v>
+        <v>72915.488800000006</v>
       </c>
       <c r="N64" s="36">
         <v>0</v>
       </c>
       <c r="O64" s="37">
         <f t="shared" si="11"/>
-        <v>192461.56</v>
+        <v>182361.56</v>
       </c>
       <c r="P64" s="38">
         <f t="shared" si="3"/>
-        <v>198235.56</v>
+        <v>187832.56</v>
       </c>
       <c r="Q64" s="22">
         <f t="shared" si="7"/>
@@ -6906,7 +6867,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="72"/>
       <c r="B65" s="149">
         <f t="shared" si="12"/>
@@ -6922,11 +6883,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F65" s="32">
-        <v>193403.57</v>
+        <v>84542.57</v>
       </c>
       <c r="G65" s="32">
-        <f>47189.57+47189+92118+6907</f>
-        <v>193403.57</v>
+        <f>F65</f>
+        <v>84542.57</v>
       </c>
       <c r="H65" s="40"/>
       <c r="I65" s="34">
@@ -6943,32 +6904,32 @@
       </c>
       <c r="L65" s="35">
         <f t="shared" si="10"/>
-        <v>56615.042591999998</v>
+        <v>46283.717713999999</v>
       </c>
       <c r="M65" s="85">
         <f t="shared" si="8"/>
-        <v>25465.404599999998</v>
+        <v>31096.311399999999</v>
       </c>
       <c r="N65" s="36">
         <v>0</v>
       </c>
       <c r="O65" s="37">
         <f t="shared" si="11"/>
-        <v>82080.570000000007</v>
+        <v>77380.570000000007</v>
       </c>
       <c r="P65" s="38">
         <f t="shared" si="3"/>
-        <v>84542.57</v>
+        <v>79701.570000000007</v>
       </c>
       <c r="Q65" s="22">
         <f t="shared" si="7"/>
         <v>0.57000000000000028</v>
       </c>
       <c r="R65" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B66" s="149">
         <f t="shared" si="12"/>
         <v>58</v>
@@ -6983,11 +6944,11 @@
         <v>1.67</v>
       </c>
       <c r="F66" s="32">
-        <v>283965.58</v>
+        <v>243425.58</v>
       </c>
       <c r="G66" s="32">
         <f>F66</f>
-        <v>283965.58</v>
+        <v>243425.58</v>
       </c>
       <c r="H66" s="40"/>
       <c r="I66" s="34">
@@ -7004,29 +6965,29 @@
       </c>
       <c r="L66" s="35">
         <f t="shared" si="10"/>
-        <v>163012.27780800001</v>
+        <v>133265.18721100001</v>
       </c>
       <c r="M66" s="85">
         <f t="shared" si="8"/>
-        <v>73322.802899999995</v>
+        <v>89535.931100000002</v>
       </c>
       <c r="N66" s="36">
         <v>0</v>
       </c>
       <c r="O66" s="37">
         <f t="shared" si="11"/>
-        <v>236335.58</v>
+        <v>222801.58</v>
       </c>
       <c r="P66" s="38">
         <f t="shared" si="3"/>
-        <v>243425.58</v>
+        <v>229485.58</v>
       </c>
       <c r="Q66" s="22">
         <f t="shared" si="7"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B67" s="83"/>
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
@@ -7044,7 +7005,7 @@
       <c r="P67" s="31"/>
       <c r="Q67" s="22"/>
     </row>
-    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="43"/>
       <c r="C68" s="44"/>
       <c r="D68" s="96"/>
@@ -7054,11 +7015,11 @@
       </c>
       <c r="F68" s="45">
         <f>SUM(F8:F66)</f>
-        <v>30276851.109999999</v>
+        <v>33179570.109999999</v>
       </c>
       <c r="G68" s="45">
         <f>SUM(G8:G66)</f>
-        <v>10043048.190000001</v>
+        <v>9927701.9800000004</v>
       </c>
       <c r="H68" s="97">
         <f t="shared" ref="H68" si="13">SUM(H8:H47)</f>
@@ -7066,11 +7027,11 @@
       </c>
       <c r="I68" s="45">
         <f t="shared" ref="I68:P68" si="14">SUM(I8:I66)</f>
-        <v>20233802.920000002</v>
+        <v>23251868.129999999</v>
       </c>
       <c r="J68" s="45">
         <f t="shared" si="14"/>
-        <v>618237.17078499997</v>
+        <v>702926.36609500018</v>
       </c>
       <c r="K68" s="45">
         <f t="shared" si="14"/>
@@ -7078,11 +7039,11 @@
       </c>
       <c r="L68" s="45">
         <f t="shared" si="14"/>
-        <v>9755357.5114560015</v>
+        <v>7975163.3592020022</v>
       </c>
       <c r="M68" s="97">
         <f t="shared" si="14"/>
-        <v>2500000.2378000007</v>
+        <v>3052799.9502000003</v>
       </c>
       <c r="N68" s="45">
         <f t="shared" si="14"/>
@@ -7090,105 +7051,110 @@
       </c>
       <c r="O68" s="45">
         <f t="shared" si="14"/>
-        <v>33107413.109999999</v>
+        <v>34982772.109999999</v>
       </c>
       <c r="P68" s="45">
         <f t="shared" si="14"/>
-        <v>34100637.109999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>36032249.109999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="24"/>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="210" t="s">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D71" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="210"/>
-      <c r="F71" s="210"/>
-      <c r="G71" s="210"/>
-      <c r="H71" s="210"/>
-      <c r="I71" s="210"/>
-      <c r="J71" s="210"/>
-      <c r="K71" s="210"/>
-      <c r="L71" s="210"/>
-      <c r="M71" s="210"/>
-      <c r="N71" s="210"/>
-      <c r="O71" s="210"/>
-    </row>
-    <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="210"/>
-      <c r="E72" s="210"/>
-      <c r="F72" s="210"/>
-      <c r="G72" s="210"/>
-      <c r="H72" s="210"/>
-      <c r="I72" s="210"/>
-      <c r="J72" s="210"/>
-      <c r="K72" s="210"/>
-      <c r="L72" s="210"/>
-      <c r="M72" s="210"/>
-      <c r="N72" s="210"/>
-      <c r="O72" s="210"/>
-    </row>
-    <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="210"/>
-      <c r="E73" s="210"/>
-      <c r="F73" s="210"/>
-      <c r="G73" s="210"/>
-      <c r="H73" s="210"/>
-      <c r="I73" s="210"/>
-      <c r="J73" s="210"/>
-      <c r="K73" s="210"/>
-      <c r="L73" s="210"/>
-      <c r="M73" s="210"/>
-      <c r="N73" s="210"/>
-      <c r="O73" s="210"/>
-    </row>
-    <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="210"/>
-      <c r="E74" s="210"/>
-      <c r="F74" s="210"/>
-      <c r="G74" s="210"/>
-      <c r="H74" s="210"/>
-      <c r="I74" s="210"/>
-      <c r="J74" s="210"/>
-      <c r="K74" s="210"/>
-      <c r="L74" s="210"/>
-      <c r="M74" s="210"/>
-      <c r="N74" s="210"/>
-      <c r="O74" s="210"/>
-    </row>
-    <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D75" s="210"/>
-      <c r="E75" s="210"/>
-      <c r="F75" s="210"/>
-      <c r="G75" s="210"/>
-      <c r="H75" s="210"/>
-      <c r="I75" s="210"/>
-      <c r="J75" s="210"/>
-      <c r="K75" s="210"/>
-      <c r="L75" s="210"/>
-      <c r="M75" s="210"/>
-      <c r="N75" s="210"/>
-      <c r="O75" s="210"/>
-    </row>
-    <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D76" s="210"/>
-      <c r="E76" s="210"/>
-      <c r="F76" s="210"/>
-      <c r="G76" s="210"/>
-      <c r="H76" s="210"/>
-      <c r="I76" s="210"/>
-      <c r="J76" s="210"/>
-      <c r="K76" s="210"/>
-      <c r="L76" s="210"/>
-      <c r="M76" s="210"/>
-      <c r="N76" s="210"/>
-      <c r="O76" s="210"/>
+      <c r="E71" s="196"/>
+      <c r="F71" s="196"/>
+      <c r="G71" s="196"/>
+      <c r="H71" s="196"/>
+      <c r="I71" s="196"/>
+      <c r="J71" s="196"/>
+      <c r="K71" s="196"/>
+      <c r="L71" s="196"/>
+      <c r="M71" s="196"/>
+      <c r="N71" s="196"/>
+      <c r="O71" s="196"/>
+    </row>
+    <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D72" s="196"/>
+      <c r="E72" s="196"/>
+      <c r="F72" s="196"/>
+      <c r="G72" s="196"/>
+      <c r="H72" s="196"/>
+      <c r="I72" s="196"/>
+      <c r="J72" s="196"/>
+      <c r="K72" s="196"/>
+      <c r="L72" s="196"/>
+      <c r="M72" s="196"/>
+      <c r="N72" s="196"/>
+      <c r="O72" s="196"/>
+    </row>
+    <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D73" s="196"/>
+      <c r="E73" s="196"/>
+      <c r="F73" s="196"/>
+      <c r="G73" s="196"/>
+      <c r="H73" s="196"/>
+      <c r="I73" s="196"/>
+      <c r="J73" s="196"/>
+      <c r="K73" s="196"/>
+      <c r="L73" s="196"/>
+      <c r="M73" s="196"/>
+      <c r="N73" s="196"/>
+      <c r="O73" s="196"/>
+    </row>
+    <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D74" s="196"/>
+      <c r="E74" s="196"/>
+      <c r="F74" s="196"/>
+      <c r="G74" s="196"/>
+      <c r="H74" s="196"/>
+      <c r="I74" s="196"/>
+      <c r="J74" s="196"/>
+      <c r="K74" s="196"/>
+      <c r="L74" s="196"/>
+      <c r="M74" s="196"/>
+      <c r="N74" s="196"/>
+      <c r="O74" s="196"/>
+    </row>
+    <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D75" s="196"/>
+      <c r="E75" s="196"/>
+      <c r="F75" s="196"/>
+      <c r="G75" s="196"/>
+      <c r="H75" s="196"/>
+      <c r="I75" s="196"/>
+      <c r="J75" s="196"/>
+      <c r="K75" s="196"/>
+      <c r="L75" s="196"/>
+      <c r="M75" s="196"/>
+      <c r="N75" s="196"/>
+      <c r="O75" s="196"/>
+    </row>
+    <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D76" s="196"/>
+      <c r="E76" s="196"/>
+      <c r="F76" s="196"/>
+      <c r="G76" s="196"/>
+      <c r="H76" s="196"/>
+      <c r="I76" s="196"/>
+      <c r="J76" s="196"/>
+      <c r="K76" s="196"/>
+      <c r="L76" s="196"/>
+      <c r="M76" s="196"/>
+      <c r="N76" s="196"/>
+      <c r="O76" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="D71:O76"/>
@@ -7203,11 +7169,6 @@
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="M6:M7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -7217,14 +7178,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C2:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I2" s="72"/>
       <c r="J2" s="72"/>
       <c r="K2" s="72"/>
     </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C3" s="111" t="s">
         <v>153</v>
       </c>
@@ -7235,11 +7196,11 @@
       <c r="F3" s="108"/>
       <c r="G3" s="108"/>
       <c r="H3" s="109"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="I3" s="226"/>
+      <c r="J3" s="226"/>
       <c r="K3" s="72"/>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C4" s="113" t="s">
         <v>154</v>
       </c>
@@ -7247,64 +7208,64 @@
         <v>54</v>
       </c>
       <c r="H4" s="110"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="226"/>
       <c r="K4" s="72"/>
     </row>
-    <row r="5" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="113"/>
       <c r="D5" s="114"/>
       <c r="H5" s="110"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
       <c r="K5" s="72"/>
     </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C6" s="225" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="227"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C6" s="217" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="218"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
+      <c r="H6" s="219"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
       <c r="K6" s="72"/>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C7" s="228"/>
-      <c r="D7" s="229"/>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
-      <c r="G7" s="229"/>
-      <c r="H7" s="230"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C7" s="220"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
       <c r="K7" s="72"/>
     </row>
-    <row r="8" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="231"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
+    <row r="8" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="223"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="224"/>
+      <c r="H8" s="225"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
       <c r="K8" s="72"/>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="I9" s="72"/>
       <c r="J9" s="72"/>
       <c r="K9" s="72"/>
     </row>
-    <row r="10" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C11" s="169" t="s">
+    <row r="10" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C11" s="165" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="170">
+      <c r="D11" s="166">
         <f>D3+1</f>
         <v>2</v>
       </c>
@@ -7313,52 +7274,62 @@
       <c r="G11" s="108"/>
       <c r="H11" s="109"/>
     </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C12" s="171" t="s">
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C12" s="167" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="167" t="s">
-        <v>192</v>
+      <c r="D12" s="164" t="s">
+        <v>174</v>
       </c>
       <c r="H12" s="110"/>
-    </row>
-    <row r="13" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="171"/>
-      <c r="D13" s="167"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+    </row>
+    <row r="13" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="167"/>
+      <c r="D13" s="164"/>
       <c r="H13" s="110"/>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="225" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14" s="226"/>
-      <c r="E14" s="226"/>
-      <c r="F14" s="226"/>
-      <c r="G14" s="226"/>
-      <c r="H14" s="227"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C15" s="228"/>
-      <c r="D15" s="229"/>
-      <c r="E15" s="229"/>
-      <c r="F15" s="229"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="230"/>
-    </row>
-    <row r="16" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="231"/>
-      <c r="D16" s="232"/>
-      <c r="E16" s="232"/>
-      <c r="F16" s="232"/>
-      <c r="G16" s="232"/>
-      <c r="H16" s="233"/>
-    </row>
-    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C19" s="172" t="s">
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C14" s="217" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="218"/>
+      <c r="G14" s="218"/>
+      <c r="H14" s="219"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+    </row>
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C15" s="220"/>
+      <c r="D15" s="221"/>
+      <c r="E15" s="221"/>
+      <c r="F15" s="221"/>
+      <c r="G15" s="221"/>
+      <c r="H15" s="222"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+    </row>
+    <row r="16" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="223"/>
+      <c r="D16" s="224"/>
+      <c r="E16" s="224"/>
+      <c r="F16" s="224"/>
+      <c r="G16" s="224"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+    </row>
+    <row r="18" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" s="168" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="173">
+      <c r="D19" s="169">
         <f>D11+1</f>
         <v>3</v>
       </c>
@@ -7367,55 +7338,70 @@
       <c r="G19" s="108"/>
       <c r="H19" s="109"/>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C20" s="174" t="s">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C20" s="170" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="175" t="s">
-        <v>192</v>
+      <c r="D20" s="171" t="s">
+        <v>174</v>
       </c>
       <c r="F20" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="H20" s="110"/>
-    </row>
-    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="174"/>
-      <c r="D21" s="175"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="118"/>
+    </row>
+    <row r="21" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="170"/>
+      <c r="D21" s="171"/>
       <c r="H21" s="110"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="225" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="227"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="228"/>
-      <c r="D23" s="229"/>
-      <c r="E23" s="229"/>
-      <c r="F23" s="229"/>
-      <c r="G23" s="229"/>
-      <c r="H23" s="230"/>
-    </row>
-    <row r="24" spans="3:8" ht="62.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="231"/>
-      <c r="D24" s="232"/>
-      <c r="E24" s="232"/>
-      <c r="F24" s="232"/>
-      <c r="G24" s="232"/>
-      <c r="H24" s="233"/>
-    </row>
-    <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C27" s="179" t="s">
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" s="217" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="218"/>
+      <c r="E22" s="218"/>
+      <c r="F22" s="218"/>
+      <c r="G22" s="218"/>
+      <c r="H22" s="219"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="118"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C23" s="220"/>
+      <c r="D23" s="221"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="221"/>
+      <c r="G23" s="221"/>
+      <c r="H23" s="222"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+    </row>
+    <row r="24" spans="3:11" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="223"/>
+      <c r="D24" s="224"/>
+      <c r="E24" s="224"/>
+      <c r="F24" s="224"/>
+      <c r="G24" s="224"/>
+      <c r="H24" s="225"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+    </row>
+    <row r="26" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="172" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="180">
+      <c r="D27" s="173">
         <f>D19+1</f>
         <v>4</v>
       </c>
@@ -7423,46 +7409,54 @@
       <c r="F27" s="108"/>
       <c r="G27" s="108"/>
       <c r="H27" s="109"/>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C28" s="181" t="s">
+      <c r="I27" s="118"/>
+      <c r="J27" s="118"/>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" s="174" t="s">
         <v>154</v>
       </c>
-      <c r="D28" s="182" t="s">
-        <v>212</v>
+      <c r="D28" s="175" t="s">
+        <v>191</v>
       </c>
       <c r="H28" s="110"/>
-    </row>
-    <row r="29" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="181"/>
-      <c r="D29" s="182"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="118"/>
+    </row>
+    <row r="29" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="174"/>
+      <c r="D29" s="175"/>
       <c r="H29" s="110"/>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="225" t="s">
-        <v>211</v>
-      </c>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="226"/>
-      <c r="H30" s="227"/>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="228"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="230"/>
-    </row>
-    <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="231"/>
-      <c r="D32" s="232"/>
-      <c r="E32" s="232"/>
-      <c r="F32" s="232"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="233"/>
+      <c r="I29" s="118"/>
+      <c r="J29" s="118"/>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="217" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="218"/>
+      <c r="E30" s="218"/>
+      <c r="F30" s="218"/>
+      <c r="G30" s="218"/>
+      <c r="H30" s="219"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="118"/>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="220"/>
+      <c r="D31" s="221"/>
+      <c r="E31" s="221"/>
+      <c r="F31" s="221"/>
+      <c r="G31" s="221"/>
+      <c r="H31" s="222"/>
+    </row>
+    <row r="32" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="223"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="225"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7478,38 +7472,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6BF67-58D9-44B8-9885-F86EBBDE6C60}">
   <dimension ref="A7:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D7" s="145">
         <v>712896.01</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="145">
         <v>476368</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D9">
         <v>13644</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" s="22">
         <f>D7-D8-D9</f>

--- a/2026/GALERIA MITRE/Septiembre/Septiembre MITRE.xlsx
+++ b/2026/GALERIA MITRE/Septiembre/Septiembre MITRE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07BD377-8C45-4D96-8F42-EC8D74AD867A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE680FB-0338-484D-9F25-9B22E853D941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,16 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$130</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="205">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -553,27 +548,6 @@
     <t>Gasto oficinas - Ascensor</t>
   </si>
   <si>
-    <t xml:space="preserve">Uf que paga con 54 centavos abono $186.000 el 08/9
-</t>
-  </si>
-  <si>
-    <t>52??</t>
-  </si>
-  <si>
-    <t>Iparraguirre Inmobiliaria deposita $260.000 el 08/09 para la uf 52</t>
-  </si>
-  <si>
-    <t>local 19 deposito 21/9 $195.100
-local 8 deposito $154.100 el 16/09
-local 9 deposito $750.000 el 16/09
-oficina 56 deposito $191.570 el 16/09
-oficina 12 (101) deposito $550.000 el 16/09
-local 17 deposito $90.000 el 16/09</t>
-  </si>
-  <si>
-    <t>Laura boras</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
@@ -608,12 +582,6 @@
   </si>
   <si>
     <t>Debito 09/09</t>
-  </si>
-  <si>
-    <t>Local 10 transfirio $162.877 el 26/09</t>
-  </si>
-  <si>
-    <t>Local 10</t>
   </si>
   <si>
     <t>Transf 07/09</t>
@@ -669,6 +637,15 @@
 Asimismo, se contempla un gasto adicional de PESOS CIENTO OCHENTA MIL ($180.000), vinculado a trabajos y/o gastos complementarios relacionados con la intervención realizada en el ascensor.
 En consecuencia, durante el presente mes resulta necesario reunir un total de PESOS TRES MILLONES CINCUENTA Y TRES MIL OCHOCIENTOS ($3.053.800), monto que será prorrateado exclusivamente entre las oficinas.
 De esta manera, el importe a prorratear se incrementa respecto del mes anterior debido tanto al mayor valor de la segunda cuota como a los gastos adicionales mencionados.</t>
+  </si>
+  <si>
+    <t>Iparraguirre Inmobiliaria deposita $235,000</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Deiana KleKotz Ayelen transfirio $650.000 pero no dijo de que UF - Le preguntamos y estimo nos contestara por mail</t>
   </si>
 </sst>
 </file>
@@ -859,7 +836,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -952,13 +929,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1322,7 +1293,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1470,10 +1441,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1556,17 +1523,11 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="9" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1717,7 +1678,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1786,9 +1750,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1826,9 +1790,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1861,26 +1825,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1913,26 +1860,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2107,269 +2037,269 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="123" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="119" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="123" t="s">
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+    </row>
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-    </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="176" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+    </row>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="166" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="176"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="176"/>
-      <c r="B5" s="176"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="176"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-    </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="176"/>
-      <c r="B7" s="176"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="124"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="166"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="166"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="166"/>
+      <c r="B6" s="166"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+    </row>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="166"/>
+      <c r="B7" s="166"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="61"/>
-      <c r="B9" s="185" t="s">
-        <v>178</v>
+      <c r="B9" s="175" t="s">
+        <v>173</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
-      <c r="B10" s="185"/>
+      <c r="B10" s="175"/>
       <c r="C10" s="61"/>
       <c r="D10" s="61"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="61"/>
-      <c r="B11" s="185"/>
+      <c r="B11" s="175"/>
       <c r="C11" s="61"/>
       <c r="D11" s="61"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="176" t="s">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="166" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="176"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="176"/>
-      <c r="B15" s="176"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="176"/>
-      <c r="B16" s="176"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-    </row>
-    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="176"/>
-      <c r="B17" s="176"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="176"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="166"/>
+      <c r="C14" s="166"/>
+      <c r="D14" s="166"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="166"/>
+      <c r="B15" s="166"/>
+      <c r="C15" s="166"/>
+      <c r="D15" s="166"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="166"/>
+      <c r="B16" s="166"/>
+      <c r="C16" s="166"/>
+      <c r="D16" s="166"/>
+    </row>
+    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="166"/>
+      <c r="B17" s="166"/>
+      <c r="C17" s="166"/>
+      <c r="D17" s="166"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
       <c r="C18" s="61"/>
       <c r="D18" s="61"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="125"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="121"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
       <c r="D19" s="61"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
       <c r="C20" s="61"/>
       <c r="D20" s="61"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="126" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="127"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="65"/>
       <c r="D21" s="66"/>
-      <c r="E21" s="118" t="s">
+      <c r="E21" s="114" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="118"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="114"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="182" t="s">
-        <v>204</v>
-      </c>
-      <c r="B23" s="183"/>
-      <c r="C23" s="160">
+      <c r="E22" s="114"/>
+      <c r="F22" s="114"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="172" t="s">
+        <v>197</v>
+      </c>
+      <c r="B23" s="173"/>
+      <c r="C23" s="156">
         <v>1416263.46</v>
       </c>
       <c r="D23" s="46"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E23" s="114"/>
+      <c r="F23" s="114"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="46"/>
-      <c r="C24" s="160">
+      <c r="C24" s="156">
         <v>-223061.46</v>
       </c>
       <c r="D24" s="46"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E24" s="114"/>
+      <c r="F24" s="114"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
         <v>54</v>
       </c>
       <c r="B25" s="46"/>
-      <c r="C25" s="160">
+      <c r="C25" s="156">
         <v>0</v>
       </c>
       <c r="D25" s="46"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
       <c r="G25" s="89"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="128" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="128"/>
+      <c r="B26" s="124"/>
       <c r="C26" s="70">
         <f>SUM(C23:C25)</f>
         <v>1193202</v>
       </c>
-      <c r="D26" s="128"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="182" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="183"/>
-      <c r="C27" s="160">
+      <c r="D26" s="124"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="114"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="172" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="173"/>
+      <c r="C27" s="156">
         <v>967913.48</v>
       </c>
       <c r="D27" s="46"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E27" s="114"/>
+      <c r="F27" s="114"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B28" s="46"/>
-      <c r="C28" s="160">
+      <c r="C28" s="156">
         <v>-239558.48</v>
       </c>
       <c r="D28" s="71"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="46"/>
-      <c r="C29" s="160">
+      <c r="C29" s="156">
         <v>0</v>
       </c>
       <c r="D29" s="71"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="128" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="129"/>
+      <c r="B30" s="125"/>
       <c r="C30" s="25">
         <f>SUM(C27:C29)</f>
         <v>728355</v>
       </c>
       <c r="D30" s="47"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
       <c r="C31" s="91">
@@ -2377,24 +2307,24 @@
       </c>
       <c r="D31" s="71"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
       <c r="C32" s="91"/>
       <c r="D32" s="71"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="128" t="s">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="129"/>
+      <c r="B33" s="125"/>
       <c r="C33" s="25">
         <f>SUM(C31:C32)</f>
         <v>0</v>
       </c>
       <c r="D33" s="47"/>
     </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>0</v>
       </c>
@@ -2407,7 +2337,7 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -2416,70 +2346,70 @@
       <c r="D35" s="49"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="180" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" s="181"/>
-      <c r="C36" s="160">
+    <row r="36" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="170" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" s="171"/>
+      <c r="C36" s="156">
         <v>650000</v>
       </c>
       <c r="D36" s="78" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="180" t="s">
-        <v>187</v>
-      </c>
-      <c r="B37" s="181"/>
+    <row r="37" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="170" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" s="171"/>
       <c r="C37" s="81">
         <v>100000</v>
       </c>
       <c r="D37" s="75" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="180" t="s">
-        <v>194</v>
-      </c>
-      <c r="B38" s="181"/>
+    <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="170" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="171"/>
       <c r="C38" s="81">
         <v>495000</v>
       </c>
       <c r="D38" s="75" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="180" t="s">
-        <v>186</v>
-      </c>
-      <c r="B39" s="181"/>
-      <c r="C39" s="160">
+    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="170" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" s="171"/>
+      <c r="C39" s="156">
         <v>200000</v>
       </c>
       <c r="D39" s="75" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B40" s="11"/>
-      <c r="C40" s="115"/>
+      <c r="C40" s="111"/>
       <c r="D40" s="48">
         <f>SUM(C36:C39)</f>
         <v>1445000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>49</v>
       </c>
@@ -2487,19 +2417,19 @@
       <c r="C41" s="13"/>
       <c r="D41" s="29"/>
     </row>
-    <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="180" t="s">
+    <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="181"/>
-      <c r="C42" s="161">
+      <c r="B42" s="171"/>
+      <c r="C42" s="157">
         <v>128114</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>1</v>
       </c>
@@ -2510,7 +2440,7 @@
         <v>128114</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>35</v>
       </c>
@@ -2518,7 +2448,7 @@
       <c r="C44" s="16"/>
       <c r="D44" s="51"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="71" t="s">
         <v>65</v>
       </c>
@@ -2529,20 +2459,20 @@
       <c r="D45" s="75"/>
       <c r="F45" s="72"/>
     </row>
-    <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="180" t="s">
+    <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="170" t="s">
         <v>167</v>
       </c>
-      <c r="B46" s="181"/>
+      <c r="B46" s="171"/>
       <c r="C46" s="81">
         <v>11930.96</v>
       </c>
       <c r="D46" s="75" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F46" s="72"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="71" t="s">
         <v>66</v>
       </c>
@@ -2551,10 +2481,10 @@
         <v>107287.94</v>
       </c>
       <c r="D47" s="77" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="71" t="s">
         <v>67</v>
       </c>
@@ -2567,7 +2497,7 @@
         <v>Debito 14/09</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="71" t="s">
         <v>68</v>
       </c>
@@ -2580,7 +2510,7 @@
         <v>Debito 14/09</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
         <v>2</v>
       </c>
@@ -2591,7 +2521,7 @@
         <v>361606.24</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>37</v>
       </c>
@@ -2599,7 +2529,7 @@
       <c r="C51" s="16"/>
       <c r="D51" s="51"/>
     </row>
-    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="71" t="s">
         <v>127</v>
       </c>
@@ -2608,10 +2538,10 @@
         <v>363925.4</v>
       </c>
       <c r="D52" s="77" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="71" t="s">
         <v>126</v>
       </c>
@@ -2620,22 +2550,22 @@
         <v>394235.68</v>
       </c>
       <c r="D53" s="77" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="71" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B54" s="71"/>
       <c r="C54" s="81">
         <v>1439199.84</v>
       </c>
       <c r="D54" s="75" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="71" t="s">
         <v>128</v>
       </c>
@@ -2644,22 +2574,22 @@
         <v>36551.61</v>
       </c>
       <c r="D55" s="77" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B56" s="159"/>
+      <c r="B56" s="155"/>
       <c r="C56" s="81">
         <v>85591</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
         <v>3</v>
       </c>
@@ -2670,7 +2600,7 @@
         <v>2319503.5299999998</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>36</v>
       </c>
@@ -2678,62 +2608,62 @@
       <c r="C58" s="15"/>
       <c r="D58" s="53"/>
     </row>
-    <row r="59" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="180" t="s">
-        <v>182</v>
-      </c>
-      <c r="B59" s="181"/>
+    <row r="59" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="170" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" s="171"/>
       <c r="C59" s="81">
         <v>202000</v>
       </c>
       <c r="D59" s="75" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G59" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="180" t="s">
-        <v>197</v>
-      </c>
-      <c r="B60" s="181"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="170" t="s">
+        <v>190</v>
+      </c>
+      <c r="B60" s="171"/>
       <c r="C60" s="81">
         <v>2866240</v>
       </c>
       <c r="D60" s="75" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F60" s="22"/>
     </row>
-    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="180" t="s">
-        <v>202</v>
-      </c>
-      <c r="B61" s="181"/>
+    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="170" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="171"/>
       <c r="C61" s="81">
         <v>157100</v>
       </c>
       <c r="D61" s="75" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F61" s="22"/>
     </row>
-    <row r="62" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="180" t="s">
-        <v>183</v>
-      </c>
-      <c r="B62" s="181"/>
+    <row r="62" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="170" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="171"/>
       <c r="C62" s="81">
         <v>128900</v>
       </c>
       <c r="D62" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="E62" s="116"/>
+        <v>179</v>
+      </c>
+      <c r="E62" s="112"/>
       <c r="F62" s="22"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
         <v>11</v>
       </c>
@@ -2744,7 +2674,7 @@
         <v>3354240</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>29</v>
       </c>
@@ -2752,17 +2682,17 @@
       <c r="C64" s="7"/>
       <c r="D64" s="53"/>
     </row>
-    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="182" t="s">
+    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="183"/>
+      <c r="B65" s="173"/>
       <c r="C65" s="81">
         <v>75000</v>
       </c>
       <c r="D65" s="57"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="46" t="s">
         <v>71</v>
       </c>
@@ -2772,45 +2702,45 @@
       </c>
       <c r="D66" s="55"/>
     </row>
-    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="130" t="s">
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="130"/>
+      <c r="B67" s="126"/>
       <c r="C67" s="58"/>
       <c r="D67" s="50">
         <f>SUM(C65:C66)</f>
         <v>316170.56</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="46"/>
       <c r="B68" s="46"/>
       <c r="C68" s="46"/>
       <c r="D68" s="59"/>
     </row>
-    <row r="69" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="177" t="s">
-        <v>198</v>
-      </c>
-      <c r="B69" s="178"/>
-      <c r="C69" s="179"/>
+    <row r="69" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="167" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" s="168"/>
+      <c r="C69" s="169"/>
       <c r="D69" s="60">
         <v>1000000</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="131"/>
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="127"/>
       <c r="B70" s="61"/>
       <c r="C70" s="61"/>
       <c r="D70" s="62"/>
       <c r="E70" s="22"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="132" t="s">
+    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="B71" s="133"/>
+      <c r="B71" s="129"/>
       <c r="C71" s="63"/>
       <c r="D71" s="64">
         <f>(SUM(D23:D69))</f>
@@ -2819,278 +2749,278 @@
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="61"/>
       <c r="B72" s="61"/>
       <c r="C72" s="61"/>
       <c r="D72" s="61"/>
       <c r="F72" s="73"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="61"/>
       <c r="B73" s="61"/>
       <c r="C73" s="61"/>
       <c r="D73" s="61"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="126" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B74" s="127"/>
+      <c r="B74" s="123"/>
       <c r="C74" s="65"/>
       <c r="D74" s="66"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="182"/>
-      <c r="B75" s="183"/>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="172"/>
+      <c r="B75" s="173"/>
       <c r="C75" s="54"/>
       <c r="D75" s="52"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="182"/>
-      <c r="B76" s="183"/>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="172"/>
+      <c r="B76" s="173"/>
       <c r="C76" s="54"/>
       <c r="D76" s="52"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="117"/>
-      <c r="B77" s="134"/>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="113"/>
+      <c r="B77" s="130"/>
       <c r="C77" s="54"/>
       <c r="D77" s="52"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="135"/>
-      <c r="B78" s="136"/>
-      <c r="C78" s="137"/>
-      <c r="D78" s="137">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="131"/>
+      <c r="B78" s="132"/>
+      <c r="C78" s="133"/>
+      <c r="D78" s="133">
         <f>SUM(C75:C77)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="61"/>
       <c r="B79" s="61"/>
       <c r="C79" s="61"/>
       <c r="D79" s="61"/>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="61"/>
       <c r="B80" s="61"/>
       <c r="C80" s="61"/>
       <c r="D80" s="61"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="138" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="B81" s="138"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="134"/>
+      <c r="C81" s="135"/>
+      <c r="D81" s="136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="61"/>
       <c r="B82" s="61"/>
       <c r="C82" s="61"/>
       <c r="D82" s="61"/>
     </row>
-    <row r="83" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="132" t="s">
+    <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="128" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="133"/>
+      <c r="B83" s="129"/>
       <c r="C83" s="63"/>
       <c r="D83" s="64">
         <f>D78+D81</f>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="61"/>
       <c r="B84" s="61"/>
       <c r="C84" s="61"/>
       <c r="D84" s="61"/>
     </row>
-    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="141" t="s">
+    <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="B85" s="142">
+      <c r="B85" s="138">
         <f>D71</f>
         <v>10846191.33</v>
       </c>
-      <c r="C85" s="143"/>
+      <c r="C85" s="139"/>
       <c r="D85" s="61"/>
     </row>
-    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="141" t="s">
+    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="B86" s="142">
+      <c r="B86" s="138">
         <f>D71-D69</f>
         <v>9846191.3300000001</v>
       </c>
       <c r="C86" s="61"/>
       <c r="D86" s="61"/>
     </row>
-    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="141" t="s">
+    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B87" s="142">
+      <c r="B87" s="138">
         <f>D83-D81</f>
         <v>0</v>
       </c>
       <c r="C87" s="61"/>
       <c r="D87" s="61"/>
     </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="141" t="s">
+    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="137" t="s">
         <v>59</v>
       </c>
-      <c r="B88" s="142">
+      <c r="B88" s="138">
         <f>D83</f>
         <v>0</v>
       </c>
       <c r="C88" s="61"/>
       <c r="D88" s="61"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="186" t="s">
-        <v>208</v>
-      </c>
-      <c r="B91" s="187"/>
-      <c r="C91" s="187"/>
-      <c r="D91" s="187"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="187"/>
-      <c r="B92" s="187"/>
-      <c r="C92" s="187"/>
-      <c r="D92" s="187"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="187"/>
-      <c r="B93" s="187"/>
-      <c r="C93" s="187"/>
-      <c r="D93" s="187"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="187"/>
-      <c r="B94" s="187"/>
-      <c r="C94" s="187"/>
-      <c r="D94" s="187"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="187"/>
-      <c r="B95" s="187"/>
-      <c r="C95" s="187"/>
-      <c r="D95" s="187"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="187"/>
-      <c r="B96" s="187"/>
-      <c r="C96" s="187"/>
-      <c r="D96" s="187"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="187"/>
-      <c r="B97" s="187"/>
-      <c r="C97" s="187"/>
-      <c r="D97" s="187"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="187"/>
-      <c r="B98" s="187"/>
-      <c r="C98" s="187"/>
-      <c r="D98" s="187"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="187"/>
-      <c r="B99" s="187"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="187"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="187"/>
-      <c r="B100" s="187"/>
-      <c r="C100" s="187"/>
-      <c r="D100" s="187"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="187"/>
-      <c r="B101" s="187"/>
-      <c r="C101" s="187"/>
-      <c r="D101" s="187"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="187"/>
-      <c r="B102" s="187"/>
-      <c r="C102" s="187"/>
-      <c r="D102" s="187"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="187"/>
-      <c r="B103" s="187"/>
-      <c r="C103" s="187"/>
-      <c r="D103" s="187"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="187"/>
-      <c r="B104" s="187"/>
-      <c r="C104" s="187"/>
-      <c r="D104" s="187"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="187"/>
-      <c r="B105" s="187"/>
-      <c r="C105" s="187"/>
-      <c r="D105" s="187"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="187"/>
-      <c r="B106" s="187"/>
-      <c r="C106" s="187"/>
-      <c r="D106" s="187"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="187"/>
-      <c r="B107" s="187"/>
-      <c r="C107" s="187"/>
-      <c r="D107" s="187"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="187"/>
-      <c r="B108" s="187"/>
-      <c r="C108" s="187"/>
-      <c r="D108" s="187"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="187"/>
-      <c r="B109" s="187"/>
-      <c r="C109" s="187"/>
-      <c r="D109" s="187"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="187"/>
-      <c r="B110" s="187"/>
-      <c r="C110" s="187"/>
-      <c r="D110" s="187"/>
-    </row>
-    <row r="111" spans="1:4" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="187"/>
-      <c r="B111" s="187"/>
-      <c r="C111" s="187"/>
-      <c r="D111" s="187"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="176" t="s">
+        <v>201</v>
+      </c>
+      <c r="B91" s="177"/>
+      <c r="C91" s="177"/>
+      <c r="D91" s="177"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="177"/>
+      <c r="B92" s="177"/>
+      <c r="C92" s="177"/>
+      <c r="D92" s="177"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="177"/>
+      <c r="B93" s="177"/>
+      <c r="C93" s="177"/>
+      <c r="D93" s="177"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="177"/>
+      <c r="B94" s="177"/>
+      <c r="C94" s="177"/>
+      <c r="D94" s="177"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="177"/>
+      <c r="B95" s="177"/>
+      <c r="C95" s="177"/>
+      <c r="D95" s="177"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="177"/>
+      <c r="B96" s="177"/>
+      <c r="C96" s="177"/>
+      <c r="D96" s="177"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="177"/>
+      <c r="B97" s="177"/>
+      <c r="C97" s="177"/>
+      <c r="D97" s="177"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="177"/>
+      <c r="B98" s="177"/>
+      <c r="C98" s="177"/>
+      <c r="D98" s="177"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="177"/>
+      <c r="B99" s="177"/>
+      <c r="C99" s="177"/>
+      <c r="D99" s="177"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="177"/>
+      <c r="B100" s="177"/>
+      <c r="C100" s="177"/>
+      <c r="D100" s="177"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="177"/>
+      <c r="B101" s="177"/>
+      <c r="C101" s="177"/>
+      <c r="D101" s="177"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="177"/>
+      <c r="B102" s="177"/>
+      <c r="C102" s="177"/>
+      <c r="D102" s="177"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="177"/>
+      <c r="B103" s="177"/>
+      <c r="C103" s="177"/>
+      <c r="D103" s="177"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="177"/>
+      <c r="B104" s="177"/>
+      <c r="C104" s="177"/>
+      <c r="D104" s="177"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="177"/>
+      <c r="B105" s="177"/>
+      <c r="C105" s="177"/>
+      <c r="D105" s="177"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="177"/>
+      <c r="B106" s="177"/>
+      <c r="C106" s="177"/>
+      <c r="D106" s="177"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="177"/>
+      <c r="B107" s="177"/>
+      <c r="C107" s="177"/>
+      <c r="D107" s="177"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="177"/>
+      <c r="B108" s="177"/>
+      <c r="C108" s="177"/>
+      <c r="D108" s="177"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="177"/>
+      <c r="B109" s="177"/>
+      <c r="C109" s="177"/>
+      <c r="D109" s="177"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="177"/>
+      <c r="B110" s="177"/>
+      <c r="C110" s="177"/>
+      <c r="D110" s="177"/>
+    </row>
+    <row r="111" spans="1:4" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="177"/>
+      <c r="B111" s="177"/>
+      <c r="C111" s="177"/>
+      <c r="D111" s="177"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B114" s="19"/>
     </row>
-    <row r="115" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
         <v>33</v>
       </c>
@@ -3098,7 +3028,7 @@
         <v>3201830.870000001</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="94" t="s">
         <v>62</v>
       </c>
@@ -3107,7 +3037,7 @@
         <v>9927701.9800000004</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="94" t="s">
         <v>61</v>
       </c>
@@ -3116,7 +3046,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>72</v>
       </c>
@@ -3124,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>43</v>
       </c>
@@ -3133,7 +3063,7 @@
         <v>-9846191.3300000001</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>44</v>
       </c>
@@ -3142,7 +3072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3153,51 +3083,51 @@
       <c r="C121" s="22"/>
       <c r="D121" s="92"/>
     </row>
-    <row r="122" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1"/>
       <c r="B122" s="95"/>
       <c r="D122" s="92"/>
     </row>
-    <row r="123" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="106" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B123" s="107">
         <v>1305847.3899999999</v>
       </c>
       <c r="D123" s="92"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="162" t="s">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="B124" s="163">
+      <c r="B124" s="159">
         <v>92133</v>
       </c>
       <c r="D124" s="92"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D125" s="93"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="184" t="s">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="B126" s="184"/>
-    </row>
-    <row r="127" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="184"/>
-      <c r="B127" s="184"/>
-    </row>
-    <row r="128" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="174"/>
+    </row>
+    <row r="127" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="174"/>
+      <c r="B127" s="174"/>
+    </row>
+    <row r="128" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="67" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B128" s="14">
         <v>550000</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="23" t="s">
         <v>11</v>
       </c>
@@ -3206,7 +3136,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L130" s="3"/>
     </row>
   </sheetData>
@@ -3242,41 +3172,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" customWidth="1"/>
-    <col min="12" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
+    <col min="12" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="188" t="s">
+      <c r="B1" s="178" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
-      <c r="J1" s="190"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="180"/>
       <c r="K1" s="102" t="s">
         <v>4</v>
       </c>
@@ -3292,17 +3222,17 @@
         <v>8136047.4719999991</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="191"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="192"/>
-      <c r="J2" s="193"/>
+      <c r="B2" s="181"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="183"/>
       <c r="K2" s="104" t="s">
         <v>63</v>
       </c>
@@ -3314,155 +3244,155 @@
       </c>
       <c r="P2" s="101"/>
     </row>
-    <row r="3" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="155" t="s">
+      <c r="B3" s="142"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="151" t="s">
         <v>170</v>
       </c>
-      <c r="L3" s="156"/>
-      <c r="M3" s="156"/>
-      <c r="N3" s="156"/>
-      <c r="O3" s="157">
+      <c r="L3" s="152"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="152"/>
+      <c r="O3" s="153">
         <f>5361706-200-50-15-5-2-1</f>
         <v>5361433</v>
       </c>
-      <c r="P3" s="158"/>
-    </row>
-    <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P3" s="154"/>
+    </row>
+    <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="207" t="s">
+      <c r="B4" s="197" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="209"/>
-    </row>
-    <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
+      <c r="K4" s="198"/>
+      <c r="L4" s="198"/>
+      <c r="M4" s="198"/>
+      <c r="N4" s="198"/>
+      <c r="O4" s="198"/>
+      <c r="P4" s="199"/>
+    </row>
+    <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="200" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="211"/>
-      <c r="P5" s="212"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="213" t="s">
+      <c r="C5" s="201"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="201"/>
+      <c r="L5" s="201"/>
+      <c r="M5" s="201"/>
+      <c r="N5" s="201"/>
+      <c r="O5" s="201"/>
+      <c r="P5" s="202"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="203" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="215" t="s">
+      <c r="B6" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="197" t="s">
+      <c r="C6" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="197" t="s">
+      <c r="D6" s="187" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="197" t="s">
+      <c r="E6" s="187" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="197" t="s">
+      <c r="F6" s="187" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="197" t="s">
+      <c r="G6" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="197" t="s">
+      <c r="H6" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="202" t="s">
+      <c r="I6" s="192" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="199" t="s">
+      <c r="J6" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="199" t="s">
+      <c r="K6" s="189" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="199" t="s">
+      <c r="L6" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="199" t="s">
+      <c r="M6" s="189" t="s">
         <v>172</v>
       </c>
-      <c r="N6" s="205" t="s">
+      <c r="N6" s="195" t="s">
         <v>58</v>
       </c>
       <c r="O6" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="194" t="s">
+      <c r="P6" s="184" t="s">
         <v>56</v>
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="214"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="201"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
-      <c r="F7" s="201"/>
-      <c r="G7" s="201"/>
-      <c r="H7" s="198"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="200"/>
-      <c r="K7" s="204"/>
-      <c r="L7" s="200"/>
-      <c r="M7" s="200"/>
-      <c r="N7" s="206"/>
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="204"/>
+      <c r="B7" s="206"/>
+      <c r="C7" s="191"/>
+      <c r="D7" s="191"/>
+      <c r="E7" s="191"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="188"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="194"/>
+      <c r="L7" s="190"/>
+      <c r="M7" s="190"/>
+      <c r="N7" s="196"/>
       <c r="O7" s="26" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P7" s="195"/>
-    </row>
-    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="119" t="s">
+      <c r="P7" s="185"/>
+    </row>
+    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="149">
-        <v>0</v>
-      </c>
-      <c r="C8" s="149" t="s">
+      <c r="B8" s="145">
+        <v>0</v>
+      </c>
+      <c r="C8" s="145" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="149" t="s">
+      <c r="D8" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="150">
+      <c r="E8" s="146">
         <v>1.58</v>
       </c>
       <c r="F8" s="32">
@@ -3488,7 +3418,7 @@
         <f t="shared" ref="L8:L39" si="1">O$1*E8%</f>
         <v>126083.23101400002</v>
       </c>
-      <c r="M8" s="153"/>
+      <c r="M8" s="149"/>
       <c r="N8" s="36">
         <v>0</v>
       </c>
@@ -3504,18 +3434,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="148"/>
-      <c r="B9" s="149">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="144"/>
+      <c r="B9" s="145">
         <v>1</v>
       </c>
-      <c r="C9" s="149" t="s">
+      <c r="C9" s="145" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="149" t="s">
+      <c r="D9" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="150">
+      <c r="E9" s="146">
         <v>2.91</v>
       </c>
       <c r="F9" s="32">
@@ -3542,7 +3472,7 @@
         <f t="shared" si="1"/>
         <v>232216.58370300001</v>
       </c>
-      <c r="M9" s="153"/>
+      <c r="M9" s="149"/>
       <c r="N9" s="36">
         <v>0</v>
       </c>
@@ -3562,21 +3492,21 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="119" t="s">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="149">
+      <c r="B10" s="145">
         <f>B9+1</f>
         <v>2</v>
       </c>
-      <c r="C10" s="149" t="s">
+      <c r="C10" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="149" t="s">
+      <c r="D10" s="145" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="150">
+      <c r="E10" s="146">
         <v>1.94</v>
       </c>
       <c r="F10" s="32">
@@ -3602,7 +3532,7 @@
         <f t="shared" si="1"/>
         <v>154811.05580200002</v>
       </c>
-      <c r="M10" s="154"/>
+      <c r="M10" s="150"/>
       <c r="N10" s="86">
         <v>0</v>
       </c>
@@ -3622,21 +3552,21 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="119" t="s">
+    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="149">
+      <c r="B11" s="145">
         <f t="shared" ref="B11:B46" si="6">B10+1</f>
         <v>3</v>
       </c>
-      <c r="C11" s="149" t="s">
+      <c r="C11" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="151" t="s">
+      <c r="D11" s="147" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="150">
+      <c r="E11" s="146">
         <v>1.78</v>
       </c>
       <c r="F11" s="32">
@@ -3663,7 +3593,7 @@
         <f t="shared" si="1"/>
         <v>142043.13367400001</v>
       </c>
-      <c r="M11" s="154"/>
+      <c r="M11" s="150"/>
       <c r="N11" s="86">
         <v>0</v>
       </c>
@@ -3680,21 +3610,21 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="119" t="s">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="149">
+      <c r="B12" s="145">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="C12" s="149" t="s">
+      <c r="C12" s="145" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="149" t="s">
+      <c r="D12" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="150">
+      <c r="E12" s="146">
         <v>1.62</v>
       </c>
       <c r="F12" s="32">
@@ -3721,7 +3651,7 @@
         <f t="shared" si="1"/>
         <v>129275.21154600002</v>
       </c>
-      <c r="M12" s="153"/>
+      <c r="M12" s="149"/>
       <c r="N12" s="36">
         <v>0</v>
       </c>
@@ -3742,21 +3672,21 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144" t="s">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="149">
+      <c r="B13" s="145">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="C13" s="149" t="s">
+      <c r="C13" s="145" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="149" t="s">
+      <c r="D13" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="150">
+      <c r="E13" s="146">
         <v>1.94</v>
       </c>
       <c r="F13" s="32">
@@ -3782,7 +3712,7 @@
         <f t="shared" si="1"/>
         <v>154811.05580200002</v>
       </c>
-      <c r="M13" s="153"/>
+      <c r="M13" s="149"/>
       <c r="N13" s="36">
         <v>0</v>
       </c>
@@ -3800,19 +3730,19 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="119"/>
-      <c r="B14" s="149">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="115"/>
+      <c r="B14" s="145">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="C14" s="149" t="s">
+      <c r="C14" s="145" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="149" t="s">
+      <c r="D14" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="150">
+      <c r="E14" s="146">
         <v>1.78</v>
       </c>
       <c r="F14" s="32">
@@ -3839,7 +3769,7 @@
         <f t="shared" si="1"/>
         <v>142043.13367400001</v>
       </c>
-      <c r="M14" s="153"/>
+      <c r="M14" s="149"/>
       <c r="N14" s="36">
         <v>0</v>
       </c>
@@ -3857,19 +3787,19 @@
       </c>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="119"/>
-      <c r="B15" s="149">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="115"/>
+      <c r="B15" s="145">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C15" s="149" t="s">
+      <c r="C15" s="145" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="149" t="s">
+      <c r="D15" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="150">
+      <c r="E15" s="146">
         <v>1.62</v>
       </c>
       <c r="F15" s="32">
@@ -3896,7 +3826,7 @@
         <f t="shared" si="1"/>
         <v>129275.21154600002</v>
       </c>
-      <c r="M15" s="153"/>
+      <c r="M15" s="149"/>
       <c r="N15" s="36">
         <v>0</v>
       </c>
@@ -3917,19 +3847,19 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="119"/>
-      <c r="B16" s="149">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="115"/>
+      <c r="B16" s="145">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="C16" s="149" t="s">
+      <c r="C16" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="149" t="s">
+      <c r="D16" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="150">
+      <c r="E16" s="146">
         <v>1.62</v>
       </c>
       <c r="F16" s="32">
@@ -3955,7 +3885,7 @@
         <f t="shared" si="1"/>
         <v>129275.21154600002</v>
       </c>
-      <c r="M16" s="154"/>
+      <c r="M16" s="150"/>
       <c r="N16" s="86">
         <v>0</v>
       </c>
@@ -3973,19 +3903,19 @@
       </c>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="119"/>
-      <c r="B17" s="149">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="115"/>
+      <c r="B17" s="145">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="C17" s="149" t="s">
+      <c r="C17" s="145" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="149" t="s">
+      <c r="D17" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="150">
+      <c r="E17" s="146">
         <v>7.59</v>
       </c>
       <c r="F17" s="32">
@@ -4011,7 +3941,7 @@
         <f t="shared" si="1"/>
         <v>605678.30594699993</v>
       </c>
-      <c r="M17" s="154"/>
+      <c r="M17" s="150"/>
       <c r="N17" s="86">
         <v>0</v>
       </c>
@@ -4029,19 +3959,19 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="119"/>
-      <c r="B18" s="149">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="115"/>
+      <c r="B18" s="145">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C18" s="149" t="s">
+      <c r="C18" s="145" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="149" t="s">
+      <c r="D18" s="145" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="150">
+      <c r="E18" s="146">
         <v>1.62</v>
       </c>
       <c r="F18" s="32">
@@ -4068,7 +3998,7 @@
         <f t="shared" si="1"/>
         <v>129275.21154600002</v>
       </c>
-      <c r="M18" s="154"/>
+      <c r="M18" s="150"/>
       <c r="N18" s="86">
         <v>0</v>
       </c>
@@ -4089,19 +4019,19 @@
       </c>
       <c r="S18" s="22"/>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="119"/>
-      <c r="B19" s="149">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="115"/>
+      <c r="B19" s="145">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C19" s="149" t="s">
+      <c r="C19" s="145" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="149" t="s">
+      <c r="D19" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="150">
+      <c r="E19" s="146">
         <v>1.78</v>
       </c>
       <c r="F19" s="32">
@@ -4128,7 +4058,7 @@
         <f t="shared" si="1"/>
         <v>142043.13367400001</v>
       </c>
-      <c r="M19" s="154"/>
+      <c r="M19" s="150"/>
       <c r="N19" s="86">
         <v>0</v>
       </c>
@@ -4149,19 +4079,19 @@
       </c>
       <c r="S19" s="22"/>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="119"/>
-      <c r="B20" s="149">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="115"/>
+      <c r="B20" s="145">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C20" s="149" t="s">
+      <c r="C20" s="145" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="149" t="s">
+      <c r="D20" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="150">
+      <c r="E20" s="146">
         <v>1.3</v>
       </c>
       <c r="F20" s="32">
@@ -4188,7 +4118,7 @@
         <f t="shared" si="1"/>
         <v>103739.36729000001</v>
       </c>
-      <c r="M20" s="154"/>
+      <c r="M20" s="150"/>
       <c r="N20" s="86">
         <v>0</v>
       </c>
@@ -4209,19 +4139,19 @@
       </c>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="119"/>
-      <c r="B21" s="149">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="115"/>
+      <c r="B21" s="145">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C21" s="149" t="s">
+      <c r="C21" s="145" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="149" t="s">
+      <c r="D21" s="145" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="150">
+      <c r="E21" s="146">
         <v>1.38</v>
       </c>
       <c r="F21" s="32">
@@ -4248,7 +4178,7 @@
         <f t="shared" si="1"/>
         <v>110123.328354</v>
       </c>
-      <c r="M21" s="154"/>
+      <c r="M21" s="150"/>
       <c r="N21" s="86">
         <v>0</v>
       </c>
@@ -4269,19 +4199,19 @@
       </c>
       <c r="S21" s="22"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="119"/>
-      <c r="B22" s="149">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="115"/>
+      <c r="B22" s="145">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C22" s="149" t="s">
+      <c r="C22" s="145" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="149" t="s">
+      <c r="D22" s="145" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="150">
+      <c r="E22" s="146">
         <v>1.87</v>
       </c>
       <c r="F22" s="32">
@@ -4308,7 +4238,7 @@
         <f t="shared" si="1"/>
         <v>149225.089871</v>
       </c>
-      <c r="M22" s="154"/>
+      <c r="M22" s="150"/>
       <c r="N22" s="86">
         <v>0</v>
       </c>
@@ -4329,19 +4259,19 @@
       </c>
       <c r="S22" s="22"/>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="119"/>
-      <c r="B23" s="149">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="115"/>
+      <c r="B23" s="145">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C23" s="149" t="s">
+      <c r="C23" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="149" t="s">
+      <c r="D23" s="145" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="150">
+      <c r="E23" s="146">
         <v>2.91</v>
       </c>
       <c r="F23" s="32">
@@ -4367,7 +4297,7 @@
         <f t="shared" si="1"/>
         <v>232216.58370300001</v>
       </c>
-      <c r="M23" s="154"/>
+      <c r="M23" s="150"/>
       <c r="N23" s="86">
         <v>0</v>
       </c>
@@ -4388,19 +4318,19 @@
       </c>
       <c r="S23" s="22"/>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="119"/>
-      <c r="B24" s="149">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="115"/>
+      <c r="B24" s="145">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C24" s="149" t="s">
+      <c r="C24" s="145" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="149" t="s">
+      <c r="D24" s="145" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="150">
+      <c r="E24" s="146">
         <v>2.14</v>
       </c>
       <c r="F24" s="32">
@@ -4426,7 +4356,7 @@
         <f t="shared" si="1"/>
         <v>170770.95846200001</v>
       </c>
-      <c r="M24" s="154"/>
+      <c r="M24" s="150"/>
       <c r="N24" s="86">
         <v>0</v>
       </c>
@@ -4447,21 +4377,21 @@
       </c>
       <c r="S24" s="22"/>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="119" t="s">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="149">
+      <c r="B25" s="145">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="C25" s="149" t="s">
+      <c r="C25" s="145" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="149" t="s">
+      <c r="D25" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="150">
+      <c r="E25" s="146">
         <v>0.89</v>
       </c>
       <c r="F25" s="32">
@@ -4487,7 +4417,7 @@
         <f t="shared" si="1"/>
         <v>71021.566837000006</v>
       </c>
-      <c r="M25" s="154"/>
+      <c r="M25" s="150"/>
       <c r="N25" s="86">
         <v>0</v>
       </c>
@@ -4504,21 +4434,21 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="119" t="s">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="149">
+      <c r="B26" s="145">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="C26" s="149" t="s">
+      <c r="C26" s="145" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="149" t="s">
+      <c r="D26" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="150">
+      <c r="E26" s="146">
         <v>0.95</v>
       </c>
       <c r="F26" s="32">
@@ -4544,7 +4474,7 @@
         <f t="shared" si="1"/>
         <v>75809.537635000001</v>
       </c>
-      <c r="M26" s="154"/>
+      <c r="M26" s="150"/>
       <c r="N26" s="86">
         <v>0</v>
       </c>
@@ -4563,21 +4493,21 @@
       <c r="R26" s="73"/>
       <c r="S26" s="72"/>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119" t="s">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="149">
+      <c r="B27" s="145">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="C27" s="149" t="s">
+      <c r="C27" s="145" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="149" t="s">
+      <c r="D27" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="150">
+      <c r="E27" s="146">
         <v>1.94</v>
       </c>
       <c r="F27" s="32">
@@ -4603,7 +4533,7 @@
         <f t="shared" si="1"/>
         <v>154811.05580200002</v>
       </c>
-      <c r="M27" s="154"/>
+      <c r="M27" s="150"/>
       <c r="N27" s="86">
         <v>0</v>
       </c>
@@ -4620,21 +4550,21 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="119" t="s">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="149">
+      <c r="B28" s="145">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="C28" s="149" t="s">
+      <c r="C28" s="145" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="149" t="s">
+      <c r="D28" s="145" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="150">
+      <c r="E28" s="146">
         <v>1.84</v>
       </c>
       <c r="F28" s="32">
@@ -4660,7 +4590,7 @@
         <f t="shared" si="1"/>
         <v>146831.10447200001</v>
       </c>
-      <c r="M28" s="154"/>
+      <c r="M28" s="150"/>
       <c r="N28" s="86">
         <v>0</v>
       </c>
@@ -4677,21 +4607,21 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="119" t="s">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="149">
+      <c r="B29" s="145">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="C29" s="149">
+      <c r="C29" s="145">
         <v>1106</v>
       </c>
-      <c r="D29" s="149" t="s">
+      <c r="D29" s="145" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="150">
+      <c r="E29" s="146">
         <v>5.12</v>
       </c>
       <c r="F29" s="32">
@@ -4737,21 +4667,21 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="119" t="s">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="149">
+      <c r="B30" s="145">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="C30" s="149">
+      <c r="C30" s="145">
         <v>1101</v>
       </c>
-      <c r="D30" s="149" t="s">
+      <c r="D30" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="150">
+      <c r="E30" s="146">
         <v>3.88</v>
       </c>
       <c r="F30" s="32">
@@ -4800,21 +4730,21 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="119" t="s">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="149">
+      <c r="B31" s="145">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="C31" s="149">
+      <c r="C31" s="145">
         <v>1102</v>
       </c>
-      <c r="D31" s="149" t="s">
+      <c r="D31" s="145" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="150">
+      <c r="E31" s="146">
         <v>0.92</v>
       </c>
       <c r="F31" s="32">
@@ -4860,21 +4790,21 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="119" t="s">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="149">
+      <c r="B32" s="145">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="C32" s="149">
+      <c r="C32" s="145">
         <v>1103</v>
       </c>
-      <c r="D32" s="149" t="s">
+      <c r="D32" s="145" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="150">
+      <c r="E32" s="146">
         <v>1.43</v>
       </c>
       <c r="F32" s="32">
@@ -4920,21 +4850,21 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="119" t="s">
+    <row r="33" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="149">
+      <c r="B33" s="145">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="C33" s="149">
+      <c r="C33" s="145">
         <v>1104</v>
       </c>
-      <c r="D33" s="149" t="s">
+      <c r="D33" s="145" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="150">
+      <c r="E33" s="146">
         <v>2.19</v>
       </c>
       <c r="F33" s="32">
@@ -4980,21 +4910,21 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="119" t="s">
+    <row r="34" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="149">
+      <c r="B34" s="145">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="C34" s="149">
+      <c r="C34" s="145">
         <v>1105</v>
       </c>
-      <c r="D34" s="149" t="s">
+      <c r="D34" s="145" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="150">
+      <c r="E34" s="146">
         <v>1.94</v>
       </c>
       <c r="F34" s="32">
@@ -5041,21 +4971,21 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="119" t="s">
+    <row r="35" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="149">
+      <c r="B35" s="145">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="C35" s="149">
+      <c r="C35" s="145">
         <v>2206</v>
       </c>
-      <c r="D35" s="149" t="s">
+      <c r="D35" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="150">
+      <c r="E35" s="146">
         <v>2.17</v>
       </c>
       <c r="F35" s="32">
@@ -5106,21 +5036,21 @@
       </c>
       <c r="S35" s="21"/>
     </row>
-    <row r="36" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="119" t="s">
+    <row r="36" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="149">
+      <c r="B36" s="145">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="C36" s="149">
+      <c r="C36" s="145">
         <v>2207</v>
       </c>
-      <c r="D36" s="149" t="s">
+      <c r="D36" s="145" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="150">
+      <c r="E36" s="146">
         <v>1.23</v>
       </c>
       <c r="F36" s="32">
@@ -5169,28 +5099,28 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="119" t="s">
+    <row r="37" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="149">
+      <c r="B37" s="145">
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="C37" s="149">
+      <c r="C37" s="145">
         <v>2208</v>
       </c>
-      <c r="D37" s="149" t="s">
+      <c r="D37" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="E37" s="150">
+      <c r="E37" s="146">
         <v>1.29</v>
       </c>
       <c r="F37" s="32">
         <v>182558.29</v>
       </c>
       <c r="G37" s="32">
-        <f>F37</f>
+        <f t="shared" ref="G37:G42" si="9">F37</f>
         <v>182558.29</v>
       </c>
       <c r="H37" s="33"/>
@@ -5230,28 +5160,28 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="119" t="s">
+    <row r="38" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="149">
+      <c r="B38" s="145">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="C38" s="149">
+      <c r="C38" s="145">
         <v>2201</v>
       </c>
-      <c r="D38" s="149" t="s">
+      <c r="D38" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="150">
+      <c r="E38" s="146">
         <v>1.36</v>
       </c>
       <c r="F38" s="32">
         <v>192464.3</v>
       </c>
       <c r="G38" s="32">
-        <f>F38</f>
+        <f t="shared" si="9"/>
         <v>192464.3</v>
       </c>
       <c r="H38" s="33"/>
@@ -5291,28 +5221,28 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="119" t="s">
+    <row r="39" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="149">
+      <c r="B39" s="145">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="C39" s="149">
+      <c r="C39" s="145">
         <v>2202</v>
       </c>
-      <c r="D39" s="149" t="s">
+      <c r="D39" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="E39" s="150">
+      <c r="E39" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F39" s="32">
         <v>82080.31</v>
       </c>
       <c r="G39" s="32">
-        <f>F39</f>
+        <f t="shared" si="9"/>
         <v>82080.31</v>
       </c>
       <c r="H39" s="33"/>
@@ -5355,28 +5285,28 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="119" t="s">
+    <row r="40" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="149">
+      <c r="B40" s="145">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
-      <c r="C40" s="149">
+      <c r="C40" s="145">
         <v>2203</v>
       </c>
-      <c r="D40" s="149" t="s">
+      <c r="D40" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="150">
+      <c r="E40" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F40" s="32">
         <v>82080.320000000007</v>
       </c>
       <c r="G40" s="32">
-        <f>F40</f>
+        <f t="shared" si="9"/>
         <v>82080.320000000007</v>
       </c>
       <c r="H40" s="33"/>
@@ -5389,11 +5319,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="85">
-        <f t="shared" ref="K40:K66" si="9">O$2*E40%</f>
+        <f t="shared" ref="K40:K66" si="10">O$2*E40%</f>
         <v>0</v>
       </c>
       <c r="L40" s="85">
-        <f t="shared" ref="L40:L66" si="10">O$1*E40%</f>
+        <f t="shared" ref="L40:L66" si="11">O$1*E40%</f>
         <v>46283.717713999999</v>
       </c>
       <c r="M40" s="85">
@@ -5404,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="87">
-        <f t="shared" ref="O40:O66" si="11">ROUND(SUM(I40:N40),0) + Q40</f>
+        <f t="shared" ref="O40:O66" si="12">ROUND(SUM(I40:N40),0) + Q40</f>
         <v>77380.320000000007</v>
       </c>
       <c r="P40" s="88">
@@ -5419,28 +5349,28 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="119" t="s">
+    <row r="41" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="149">
+      <c r="B41" s="145">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="C41" s="149">
+      <c r="C41" s="145">
         <v>2204</v>
       </c>
-      <c r="D41" s="149" t="s">
+      <c r="D41" s="145" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="150">
+      <c r="E41" s="146">
         <v>1.36</v>
       </c>
       <c r="F41" s="32">
         <v>192464.33</v>
       </c>
       <c r="G41" s="32">
-        <f>F41</f>
+        <f t="shared" si="9"/>
         <v>192464.33</v>
       </c>
       <c r="H41" s="33"/>
@@ -5453,11 +5383,11 @@
         <v>0</v>
       </c>
       <c r="K41" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L41" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M41" s="85">
@@ -5468,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>181443.33</v>
       </c>
       <c r="P41" s="88">
@@ -5483,28 +5413,28 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="119" t="s">
+    <row r="42" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="149">
+      <c r="B42" s="145">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="C42" s="149">
+      <c r="C42" s="145">
         <v>2205</v>
       </c>
-      <c r="D42" s="149" t="s">
+      <c r="D42" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="E42" s="150">
+      <c r="E42" s="146">
         <v>1.67</v>
       </c>
       <c r="F42" s="32">
         <v>236335.34</v>
       </c>
       <c r="G42" s="32">
-        <f>F42</f>
+        <f t="shared" si="9"/>
         <v>236335.34</v>
       </c>
       <c r="H42" s="33"/>
@@ -5517,11 +5447,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L42" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>133265.18721100001</v>
       </c>
       <c r="M42" s="85">
@@ -5532,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>222801.34</v>
       </c>
       <c r="P42" s="88">
@@ -5547,21 +5477,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="119" t="s">
+    <row r="43" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="149">
+      <c r="B43" s="145">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="C43" s="149">
+      <c r="C43" s="145">
         <v>2206</v>
       </c>
-      <c r="D43" s="149" t="s">
+      <c r="D43" s="145" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="150">
+      <c r="E43" s="146">
         <v>2.17</v>
       </c>
       <c r="F43" s="32">
@@ -5581,11 +5511,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L43" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>173164.94386100001</v>
       </c>
       <c r="M43" s="85">
@@ -5596,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>289508.34999999998</v>
       </c>
       <c r="P43" s="88">
@@ -5611,21 +5541,21 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="119" t="s">
+    <row r="44" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="149">
+      <c r="B44" s="145">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="C44" s="149">
+      <c r="C44" s="145">
         <v>2207</v>
       </c>
-      <c r="D44" s="149" t="s">
+      <c r="D44" s="145" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="150">
+      <c r="E44" s="146">
         <v>1.23</v>
       </c>
       <c r="F44" s="32">
@@ -5645,11 +5575,11 @@
         <v>0</v>
       </c>
       <c r="K44" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L44" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>98153.401358999996</v>
       </c>
       <c r="M44" s="85">
@@ -5660,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>164099.35999999999</v>
       </c>
       <c r="P44" s="88">
@@ -5675,21 +5605,21 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="119" t="s">
+    <row r="45" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="149">
+      <c r="B45" s="145">
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
-      <c r="C45" s="149">
+      <c r="C45" s="145">
         <v>3308</v>
       </c>
-      <c r="D45" s="149" t="s">
+      <c r="D45" s="145" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="150">
+      <c r="E45" s="146">
         <v>1.23</v>
       </c>
       <c r="F45" s="32">
@@ -5709,11 +5639,11 @@
         <v>1680.2205850000003</v>
       </c>
       <c r="K45" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L45" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>98153.401358999996</v>
       </c>
       <c r="M45" s="85">
@@ -5724,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>222736.37</v>
       </c>
       <c r="P45" s="88">
@@ -5737,21 +5667,21 @@
       </c>
       <c r="R45" s="72"/>
     </row>
-    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="119" t="s">
+    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="149">
+      <c r="B46" s="145">
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="C46" s="149">
+      <c r="C46" s="145">
         <v>3301</v>
       </c>
-      <c r="D46" s="152" t="s">
+      <c r="D46" s="148" t="s">
         <v>124</v>
       </c>
-      <c r="E46" s="150">
+      <c r="E46" s="146">
         <v>1.36</v>
       </c>
       <c r="F46" s="32">
@@ -5770,11 +5700,11 @@
         <v>5676.6962100000001</v>
       </c>
       <c r="K46" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L46" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M46" s="85">
@@ -5785,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>379550.38</v>
       </c>
       <c r="P46" s="88">
@@ -5797,21 +5727,21 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="119" t="s">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B47" s="149">
+      <c r="B47" s="145">
         <f>B46+1</f>
         <v>39</v>
       </c>
-      <c r="C47" s="149">
+      <c r="C47" s="145">
         <v>3302</v>
       </c>
-      <c r="D47" s="149" t="s">
+      <c r="D47" s="145" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="150">
+      <c r="E47" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F47" s="32">
@@ -5831,11 +5761,11 @@
         <v>0</v>
       </c>
       <c r="K47" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L47" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46283.717713999999</v>
       </c>
       <c r="M47" s="85">
@@ -5846,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>77380.39</v>
       </c>
       <c r="P47" s="88">
@@ -5858,19 +5788,19 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="72"/>
-      <c r="B48" s="149">
-        <f t="shared" ref="B48:B66" si="12">B47+1</f>
+      <c r="B48" s="145">
+        <f t="shared" ref="B48:B66" si="13">B47+1</f>
         <v>40</v>
       </c>
-      <c r="C48" s="149">
+      <c r="C48" s="145">
         <v>3303</v>
       </c>
-      <c r="D48" s="149" t="s">
+      <c r="D48" s="145" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="150">
+      <c r="E48" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F48" s="32">
@@ -5890,11 +5820,11 @@
         <v>0</v>
       </c>
       <c r="K48" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L48" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46283.717713999999</v>
       </c>
       <c r="M48" s="85">
@@ -5905,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>77380.399999999994</v>
       </c>
       <c r="P48" s="88">
@@ -5917,19 +5847,19 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="72"/>
-      <c r="B49" s="149">
-        <f t="shared" si="12"/>
+      <c r="B49" s="145">
+        <f t="shared" si="13"/>
         <v>41</v>
       </c>
-      <c r="C49" s="149">
+      <c r="C49" s="145">
         <v>3304</v>
       </c>
-      <c r="D49" s="149" t="s">
+      <c r="D49" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="150">
+      <c r="E49" s="146">
         <v>1.36</v>
       </c>
       <c r="F49" s="32">
@@ -5948,11 +5878,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L49" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M49" s="85">
@@ -5963,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>180374.41</v>
       </c>
       <c r="P49" s="88">
@@ -5975,22 +5905,22 @@
         <v>0.4100000000000002</v>
       </c>
       <c r="R49" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="72"/>
-      <c r="B50" s="149">
-        <f t="shared" si="12"/>
+      <c r="B50" s="145">
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
-      <c r="C50" s="149">
+      <c r="C50" s="145">
         <v>3305</v>
       </c>
-      <c r="D50" s="149" t="s">
+      <c r="D50" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E50" s="150">
+      <c r="E50" s="146">
         <v>1.67</v>
       </c>
       <c r="F50" s="32">
@@ -6009,11 +5939,11 @@
         <v>60107.914389999998</v>
       </c>
       <c r="K50" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L50" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>133265.18721100001</v>
       </c>
       <c r="M50" s="85">
@@ -6024,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2320465.42</v>
       </c>
       <c r="P50" s="88">
@@ -6036,19 +5966,19 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="72"/>
-      <c r="B51" s="149">
-        <f t="shared" si="12"/>
+      <c r="B51" s="145">
+        <f t="shared" si="13"/>
         <v>43</v>
       </c>
-      <c r="C51" s="149">
+      <c r="C51" s="145">
         <v>4406</v>
       </c>
-      <c r="D51" s="149" t="s">
+      <c r="D51" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="E51" s="150">
+      <c r="E51" s="146">
         <v>2.17</v>
       </c>
       <c r="F51" s="32">
@@ -6068,11 +5998,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L51" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>173164.94386100001</v>
       </c>
       <c r="M51" s="85">
@@ -6083,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>289508.43</v>
       </c>
       <c r="P51" s="88">
@@ -6095,19 +6025,19 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="72"/>
-      <c r="B52" s="149">
-        <f t="shared" si="12"/>
+      <c r="B52" s="145">
+        <f t="shared" si="13"/>
         <v>44</v>
       </c>
-      <c r="C52" s="149">
+      <c r="C52" s="145">
         <v>4407</v>
       </c>
-      <c r="D52" s="149" t="s">
+      <c r="D52" s="145" t="s">
         <v>133</v>
       </c>
-      <c r="E52" s="150">
+      <c r="E52" s="146">
         <v>1.23</v>
       </c>
       <c r="F52" s="32">
@@ -6127,11 +6057,11 @@
         <v>0</v>
       </c>
       <c r="K52" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L52" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>98153.401358999996</v>
       </c>
       <c r="M52" s="85">
@@ -6142,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>164099.44</v>
       </c>
       <c r="P52" s="88">
@@ -6154,19 +6084,19 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="72"/>
-      <c r="B53" s="149">
-        <f t="shared" si="12"/>
+      <c r="B53" s="145">
+        <f t="shared" si="13"/>
         <v>45</v>
       </c>
-      <c r="C53" s="149">
+      <c r="C53" s="145">
         <v>4408</v>
       </c>
-      <c r="D53" s="149" t="s">
+      <c r="D53" s="145" t="s">
         <v>134</v>
       </c>
-      <c r="E53" s="150">
+      <c r="E53" s="146">
         <v>1.29</v>
       </c>
       <c r="F53" s="32">
@@ -6185,11 +6115,11 @@
         <v>0</v>
       </c>
       <c r="K53" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L53" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>102941.37215700001</v>
       </c>
       <c r="M53" s="85">
@@ -6200,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>166722.45000000001</v>
       </c>
       <c r="P53" s="88">
@@ -6212,19 +6142,19 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="72"/>
-      <c r="B54" s="149">
-        <f t="shared" si="12"/>
+      <c r="B54" s="145">
+        <f t="shared" si="13"/>
         <v>46</v>
       </c>
-      <c r="C54" s="149">
+      <c r="C54" s="145">
         <v>4401</v>
       </c>
-      <c r="D54" s="149" t="s">
+      <c r="D54" s="145" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="150">
+      <c r="E54" s="146">
         <v>1.36</v>
       </c>
       <c r="F54" s="32">
@@ -6244,11 +6174,11 @@
         <v>0</v>
       </c>
       <c r="K54" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L54" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M54" s="85">
@@ -6259,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>181443.46</v>
       </c>
       <c r="P54" s="88">
@@ -6271,19 +6201,19 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="72"/>
-      <c r="B55" s="149">
-        <f t="shared" si="12"/>
+      <c r="B55" s="145">
+        <f t="shared" si="13"/>
         <v>47</v>
       </c>
-      <c r="C55" s="149">
+      <c r="C55" s="145">
         <v>4402</v>
       </c>
-      <c r="D55" s="149" t="s">
+      <c r="D55" s="145" t="s">
         <v>136</v>
       </c>
-      <c r="E55" s="150">
+      <c r="E55" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F55" s="32">
@@ -6303,11 +6233,11 @@
         <v>0</v>
       </c>
       <c r="K55" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L55" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46283.717713999999</v>
       </c>
       <c r="M55" s="85">
@@ -6318,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>77380.47</v>
       </c>
       <c r="P55" s="88">
@@ -6330,19 +6260,19 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="72"/>
-      <c r="B56" s="149">
-        <f t="shared" si="12"/>
+      <c r="B56" s="145">
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
-      <c r="C56" s="149">
+      <c r="C56" s="145">
         <v>4403</v>
       </c>
-      <c r="D56" s="149" t="s">
+      <c r="D56" s="145" t="s">
         <v>137</v>
       </c>
-      <c r="E56" s="150">
+      <c r="E56" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F56" s="32">
@@ -6361,11 +6291,11 @@
         <v>0</v>
       </c>
       <c r="K56" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L56" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46283.717713999999</v>
       </c>
       <c r="M56" s="85">
@@ -6376,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>74959.48</v>
       </c>
       <c r="P56" s="88">
@@ -6391,19 +6321,19 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="72"/>
-      <c r="B57" s="149">
-        <f t="shared" si="12"/>
+      <c r="B57" s="145">
+        <f t="shared" si="13"/>
         <v>49</v>
       </c>
-      <c r="C57" s="149">
+      <c r="C57" s="145">
         <v>4404</v>
       </c>
-      <c r="D57" s="149" t="s">
+      <c r="D57" s="145" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="150">
+      <c r="E57" s="146">
         <v>1.36</v>
       </c>
       <c r="F57" s="32">
@@ -6422,11 +6352,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L57" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M57" s="85">
@@ -6437,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>175766.49</v>
       </c>
       <c r="P57" s="88">
@@ -6452,19 +6382,19 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="72"/>
-      <c r="B58" s="149">
-        <f t="shared" si="12"/>
+      <c r="B58" s="145">
+        <f t="shared" si="13"/>
         <v>50</v>
       </c>
-      <c r="C58" s="149">
+      <c r="C58" s="145">
         <v>4405</v>
       </c>
-      <c r="D58" s="149" t="s">
+      <c r="D58" s="145" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="150">
+      <c r="E58" s="146">
         <v>1.67</v>
       </c>
       <c r="F58" s="32">
@@ -6483,11 +6413,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L58" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>133265.18721100001</v>
       </c>
       <c r="M58" s="85">
@@ -6498,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>215830.5</v>
       </c>
       <c r="P58" s="88">
@@ -6513,19 +6443,19 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="72"/>
-      <c r="B59" s="149">
-        <f t="shared" si="12"/>
+      <c r="B59" s="145">
+        <f t="shared" si="13"/>
         <v>51</v>
       </c>
-      <c r="C59" s="149">
+      <c r="C59" s="145">
         <v>5506</v>
       </c>
-      <c r="D59" s="149" t="s">
+      <c r="D59" s="145" t="s">
         <v>138</v>
       </c>
-      <c r="E59" s="150">
+      <c r="E59" s="146">
         <v>2.17</v>
       </c>
       <c r="F59" s="32">
@@ -6544,11 +6474,11 @@
         <v>0</v>
       </c>
       <c r="K59" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L59" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>173164.94386100001</v>
       </c>
       <c r="M59" s="85">
@@ -6559,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>280449.51</v>
       </c>
       <c r="P59" s="88">
@@ -6571,19 +6501,19 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="164"/>
-      <c r="B60" s="149">
-        <f t="shared" si="12"/>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" s="160"/>
+      <c r="B60" s="161">
+        <f t="shared" si="13"/>
         <v>52</v>
       </c>
-      <c r="C60" s="149">
+      <c r="C60" s="161">
         <v>5507</v>
       </c>
-      <c r="D60" s="149" t="s">
+      <c r="D60" s="161" t="s">
         <v>139</v>
       </c>
-      <c r="E60" s="150">
+      <c r="E60" s="146">
         <v>1.79</v>
       </c>
       <c r="F60" s="32">
@@ -6602,11 +6532,11 @@
         <v>0</v>
       </c>
       <c r="K60" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L60" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>142841.128807</v>
       </c>
       <c r="M60" s="85">
@@ -6617,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>227395.52</v>
       </c>
       <c r="P60" s="88">
@@ -6629,19 +6559,19 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="72"/>
-      <c r="B61" s="149">
-        <f t="shared" si="12"/>
+      <c r="B61" s="145">
+        <f t="shared" si="13"/>
         <v>53</v>
       </c>
-      <c r="C61" s="149">
+      <c r="C61" s="145">
         <v>5508</v>
       </c>
-      <c r="D61" s="149" t="s">
+      <c r="D61" s="145" t="s">
         <v>140</v>
       </c>
-      <c r="E61" s="150">
+      <c r="E61" s="146">
         <v>1.29</v>
       </c>
       <c r="F61" s="32">
@@ -6660,11 +6590,11 @@
         <v>9258.2661350000017</v>
       </c>
       <c r="K61" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L61" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>102941.37215700001</v>
       </c>
       <c r="M61" s="85">
@@ -6675,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>495202.53</v>
       </c>
       <c r="P61" s="88">
@@ -6687,19 +6617,19 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="72"/>
-      <c r="B62" s="149">
-        <f t="shared" si="12"/>
+      <c r="B62" s="145">
+        <f t="shared" si="13"/>
         <v>54</v>
       </c>
-      <c r="C62" s="149">
+      <c r="C62" s="145">
         <v>5501</v>
       </c>
-      <c r="D62" s="149" t="s">
+      <c r="D62" s="145" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="150">
+      <c r="E62" s="146">
         <v>1.36</v>
       </c>
       <c r="F62" s="32">
@@ -6718,11 +6648,11 @@
         <v>0</v>
       </c>
       <c r="K62" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L62" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M62" s="85">
@@ -6733,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>181272.54</v>
       </c>
       <c r="P62" s="88">
@@ -6745,19 +6675,19 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="72"/>
-      <c r="B63" s="149">
-        <f t="shared" si="12"/>
+      <c r="B63" s="145">
+        <f t="shared" si="13"/>
         <v>55</v>
       </c>
-      <c r="C63" s="149">
+      <c r="C63" s="145">
         <v>5503</v>
       </c>
-      <c r="D63" s="149" t="s">
+      <c r="D63" s="145" t="s">
         <v>142</v>
       </c>
-      <c r="E63" s="150">
+      <c r="E63" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F63" s="32">
@@ -6776,11 +6706,11 @@
         <v>0</v>
       </c>
       <c r="K63" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L63" s="85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46283.717713999999</v>
       </c>
       <c r="M63" s="85">
@@ -6791,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-239129.45</v>
       </c>
       <c r="P63" s="88">
@@ -6806,19 +6736,19 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="72"/>
-      <c r="B64" s="149">
-        <f t="shared" si="12"/>
+      <c r="B64" s="145">
+        <f t="shared" si="13"/>
         <v>56</v>
       </c>
-      <c r="C64" s="149">
+      <c r="C64" s="145">
         <v>5504</v>
       </c>
-      <c r="D64" s="149" t="s">
+      <c r="D64" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="150">
+      <c r="E64" s="146">
         <v>1.36</v>
       </c>
       <c r="F64" s="32">
@@ -6837,11 +6767,11 @@
         <v>26.301019999999934</v>
       </c>
       <c r="K64" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L64" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>108527.338088</v>
       </c>
       <c r="M64" s="85">
@@ -6852,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>182361.56</v>
       </c>
       <c r="P64" s="38">
@@ -6867,19 +6797,19 @@
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="72"/>
-      <c r="B65" s="149">
-        <f t="shared" si="12"/>
+      <c r="B65" s="145">
+        <f t="shared" si="13"/>
         <v>57</v>
       </c>
-      <c r="C65" s="149">
+      <c r="C65" s="145">
         <v>5502</v>
       </c>
-      <c r="D65" s="149" t="s">
+      <c r="D65" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="E65" s="150">
+      <c r="E65" s="146">
         <v>0.57999999999999996</v>
       </c>
       <c r="F65" s="32">
@@ -6899,11 +6829,11 @@
         <v>0</v>
       </c>
       <c r="K65" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L65" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46283.717713999999</v>
       </c>
       <c r="M65" s="85">
@@ -6914,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>77380.570000000007</v>
       </c>
       <c r="P65" s="38">
@@ -6929,18 +6859,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B66" s="149">
-        <f t="shared" si="12"/>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B66" s="145">
+        <f t="shared" si="13"/>
         <v>58</v>
       </c>
-      <c r="C66" s="149">
+      <c r="C66" s="145">
         <v>5505</v>
       </c>
-      <c r="D66" s="149" t="s">
+      <c r="D66" s="145" t="s">
         <v>143</v>
       </c>
-      <c r="E66" s="150">
+      <c r="E66" s="146">
         <v>1.67</v>
       </c>
       <c r="F66" s="32">
@@ -6960,11 +6890,11 @@
         <v>0</v>
       </c>
       <c r="K66" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L66" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>133265.18721100001</v>
       </c>
       <c r="M66" s="85">
@@ -6975,7 +6905,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>222801.58</v>
       </c>
       <c r="P66" s="38">
@@ -6987,7 +6917,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B67" s="83"/>
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
@@ -7005,7 +6935,7 @@
       <c r="P67" s="31"/>
       <c r="Q67" s="22"/>
     </row>
-    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="43"/>
       <c r="C68" s="44"/>
       <c r="D68" s="96"/>
@@ -7022,131 +6952,131 @@
         <v>9927701.9800000004</v>
       </c>
       <c r="H68" s="97">
-        <f t="shared" ref="H68" si="13">SUM(H8:H47)</f>
+        <f t="shared" ref="H68" si="14">SUM(H8:H47)</f>
         <v>0</v>
       </c>
       <c r="I68" s="45">
-        <f t="shared" ref="I68:P68" si="14">SUM(I8:I66)</f>
+        <f t="shared" ref="I68:P68" si="15">SUM(I8:I66)</f>
         <v>23251868.129999999</v>
       </c>
       <c r="J68" s="45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>702926.36609500018</v>
       </c>
       <c r="K68" s="45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L68" s="45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7975163.3592020022</v>
       </c>
       <c r="M68" s="97">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3052799.9502000003</v>
       </c>
       <c r="N68" s="45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O68" s="45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>34982772.109999999</v>
       </c>
       <c r="P68" s="45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>36032249.109999999</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D69" s="24"/>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="196" t="s">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="196"/>
-      <c r="F71" s="196"/>
-      <c r="G71" s="196"/>
-      <c r="H71" s="196"/>
-      <c r="I71" s="196"/>
-      <c r="J71" s="196"/>
-      <c r="K71" s="196"/>
-      <c r="L71" s="196"/>
-      <c r="M71" s="196"/>
-      <c r="N71" s="196"/>
-      <c r="O71" s="196"/>
-    </row>
-    <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="196"/>
-      <c r="E72" s="196"/>
-      <c r="F72" s="196"/>
-      <c r="G72" s="196"/>
-      <c r="H72" s="196"/>
-      <c r="I72" s="196"/>
-      <c r="J72" s="196"/>
-      <c r="K72" s="196"/>
-      <c r="L72" s="196"/>
-      <c r="M72" s="196"/>
-      <c r="N72" s="196"/>
-      <c r="O72" s="196"/>
-    </row>
-    <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="196"/>
-      <c r="E73" s="196"/>
-      <c r="F73" s="196"/>
-      <c r="G73" s="196"/>
-      <c r="H73" s="196"/>
-      <c r="I73" s="196"/>
-      <c r="J73" s="196"/>
-      <c r="K73" s="196"/>
-      <c r="L73" s="196"/>
-      <c r="M73" s="196"/>
-      <c r="N73" s="196"/>
-      <c r="O73" s="196"/>
-    </row>
-    <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="196"/>
-      <c r="E74" s="196"/>
-      <c r="F74" s="196"/>
-      <c r="G74" s="196"/>
-      <c r="H74" s="196"/>
-      <c r="I74" s="196"/>
-      <c r="J74" s="196"/>
-      <c r="K74" s="196"/>
-      <c r="L74" s="196"/>
-      <c r="M74" s="196"/>
-      <c r="N74" s="196"/>
-      <c r="O74" s="196"/>
-    </row>
-    <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D75" s="196"/>
-      <c r="E75" s="196"/>
-      <c r="F75" s="196"/>
-      <c r="G75" s="196"/>
-      <c r="H75" s="196"/>
-      <c r="I75" s="196"/>
-      <c r="J75" s="196"/>
-      <c r="K75" s="196"/>
-      <c r="L75" s="196"/>
-      <c r="M75" s="196"/>
-      <c r="N75" s="196"/>
-      <c r="O75" s="196"/>
-    </row>
-    <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="196"/>
-      <c r="E76" s="196"/>
-      <c r="F76" s="196"/>
-      <c r="G76" s="196"/>
-      <c r="H76" s="196"/>
-      <c r="I76" s="196"/>
-      <c r="J76" s="196"/>
-      <c r="K76" s="196"/>
-      <c r="L76" s="196"/>
-      <c r="M76" s="196"/>
-      <c r="N76" s="196"/>
-      <c r="O76" s="196"/>
+      <c r="E71" s="186"/>
+      <c r="F71" s="186"/>
+      <c r="G71" s="186"/>
+      <c r="H71" s="186"/>
+      <c r="I71" s="186"/>
+      <c r="J71" s="186"/>
+      <c r="K71" s="186"/>
+      <c r="L71" s="186"/>
+      <c r="M71" s="186"/>
+      <c r="N71" s="186"/>
+      <c r="O71" s="186"/>
+    </row>
+    <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="186"/>
+      <c r="E72" s="186"/>
+      <c r="F72" s="186"/>
+      <c r="G72" s="186"/>
+      <c r="H72" s="186"/>
+      <c r="I72" s="186"/>
+      <c r="J72" s="186"/>
+      <c r="K72" s="186"/>
+      <c r="L72" s="186"/>
+      <c r="M72" s="186"/>
+      <c r="N72" s="186"/>
+      <c r="O72" s="186"/>
+    </row>
+    <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="186"/>
+      <c r="E73" s="186"/>
+      <c r="F73" s="186"/>
+      <c r="G73" s="186"/>
+      <c r="H73" s="186"/>
+      <c r="I73" s="186"/>
+      <c r="J73" s="186"/>
+      <c r="K73" s="186"/>
+      <c r="L73" s="186"/>
+      <c r="M73" s="186"/>
+      <c r="N73" s="186"/>
+      <c r="O73" s="186"/>
+    </row>
+    <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="186"/>
+      <c r="E74" s="186"/>
+      <c r="F74" s="186"/>
+      <c r="G74" s="186"/>
+      <c r="H74" s="186"/>
+      <c r="I74" s="186"/>
+      <c r="J74" s="186"/>
+      <c r="K74" s="186"/>
+      <c r="L74" s="186"/>
+      <c r="M74" s="186"/>
+      <c r="N74" s="186"/>
+      <c r="O74" s="186"/>
+    </row>
+    <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="186"/>
+      <c r="E75" s="186"/>
+      <c r="F75" s="186"/>
+      <c r="G75" s="186"/>
+      <c r="H75" s="186"/>
+      <c r="I75" s="186"/>
+      <c r="J75" s="186"/>
+      <c r="K75" s="186"/>
+      <c r="L75" s="186"/>
+      <c r="M75" s="186"/>
+      <c r="N75" s="186"/>
+      <c r="O75" s="186"/>
+    </row>
+    <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D76" s="186"/>
+      <c r="E76" s="186"/>
+      <c r="F76" s="186"/>
+      <c r="G76" s="186"/>
+      <c r="H76" s="186"/>
+      <c r="I76" s="186"/>
+      <c r="J76" s="186"/>
+      <c r="K76" s="186"/>
+      <c r="L76" s="186"/>
+      <c r="M76" s="186"/>
+      <c r="N76" s="186"/>
+      <c r="O76" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -7177,293 +7107,146 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="C2:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C2:K15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I2" s="72"/>
       <c r="J2" s="72"/>
       <c r="K2" s="72"/>
     </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="111" t="s">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="162" t="s">
         <v>153</v>
       </c>
-      <c r="D3" s="112">
+      <c r="D3" s="163">
         <v>1</v>
       </c>
       <c r="E3" s="108"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108"/>
       <c r="H3" s="109"/>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
       <c r="K3" s="72"/>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="113" t="s">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="164" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="114">
-        <v>54</v>
+      <c r="D4" s="165">
+        <v>53</v>
       </c>
       <c r="H4" s="110"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
       <c r="K4" s="72"/>
     </row>
-    <row r="5" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="113"/>
-      <c r="D5" s="114"/>
+    <row r="5" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="164"/>
+      <c r="D5" s="165"/>
       <c r="H5" s="110"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
       <c r="K5" s="72"/>
     </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="217" t="s">
-        <v>173</v>
-      </c>
-      <c r="D6" s="218"/>
-      <c r="E6" s="218"/>
-      <c r="F6" s="218"/>
-      <c r="G6" s="218"/>
-      <c r="H6" s="219"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
+    <row r="6" spans="3:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="207" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="208"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="209"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
       <c r="K6" s="72"/>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="220"/>
-      <c r="D7" s="221"/>
-      <c r="E7" s="221"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="221"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="210"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="211"/>
+      <c r="H7" s="212"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
       <c r="K7" s="72"/>
     </row>
-    <row r="8" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="223"/>
-      <c r="D8" s="224"/>
-      <c r="E8" s="224"/>
-      <c r="F8" s="224"/>
-      <c r="G8" s="224"/>
-      <c r="H8" s="225"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
+    <row r="8" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="213"/>
+      <c r="D8" s="214"/>
+      <c r="E8" s="214"/>
+      <c r="F8" s="214"/>
+      <c r="G8" s="214"/>
+      <c r="H8" s="215"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
       <c r="K8" s="72"/>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I9" s="72"/>
       <c r="J9" s="72"/>
       <c r="K9" s="72"/>
     </row>
-    <row r="10" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="165" t="s">
+    <row r="10" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C10" s="216" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="166">
+      <c r="D10" s="217">
         <f>D3+1</f>
         <v>2</v>
       </c>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="109"/>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C12" s="167" t="s">
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="109"/>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="218" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="164" t="s">
-        <v>174</v>
-      </c>
+      <c r="D11" s="219" t="s">
+        <v>203</v>
+      </c>
+      <c r="H11" s="110"/>
+    </row>
+    <row r="12" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="218"/>
+      <c r="D12" s="219"/>
       <c r="H12" s="110"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-    </row>
-    <row r="13" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="167"/>
-      <c r="D13" s="164"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C14" s="217" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="218"/>
-      <c r="E14" s="218"/>
-      <c r="F14" s="218"/>
-      <c r="G14" s="218"/>
-      <c r="H14" s="219"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C15" s="220"/>
-      <c r="D15" s="221"/>
-      <c r="E15" s="221"/>
-      <c r="F15" s="221"/>
-      <c r="G15" s="221"/>
-      <c r="H15" s="222"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-    </row>
-    <row r="16" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="223"/>
-      <c r="D16" s="224"/>
-      <c r="E16" s="224"/>
-      <c r="F16" s="224"/>
-      <c r="G16" s="224"/>
-      <c r="H16" s="225"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-    </row>
-    <row r="18" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="168" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" s="169">
-        <f>D11+1</f>
-        <v>3</v>
-      </c>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="109"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="170" t="s">
-        <v>154</v>
-      </c>
-      <c r="D20" s="171" t="s">
-        <v>174</v>
-      </c>
-      <c r="F20" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="110"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-    </row>
-    <row r="21" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="170"/>
-      <c r="D21" s="171"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="217" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" s="218"/>
-      <c r="E22" s="218"/>
-      <c r="F22" s="218"/>
-      <c r="G22" s="218"/>
-      <c r="H22" s="219"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="220"/>
-      <c r="D23" s="221"/>
-      <c r="E23" s="221"/>
-      <c r="F23" s="221"/>
-      <c r="G23" s="221"/>
-      <c r="H23" s="222"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-    </row>
-    <row r="24" spans="3:11" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="223"/>
-      <c r="D24" s="224"/>
-      <c r="E24" s="224"/>
-      <c r="F24" s="224"/>
-      <c r="G24" s="224"/>
-      <c r="H24" s="225"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-    </row>
-    <row r="26" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="172" t="s">
-        <v>153</v>
-      </c>
-      <c r="D27" s="173">
-        <f>D19+1</f>
-        <v>4</v>
-      </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C28" s="174" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="175" t="s">
-        <v>191</v>
-      </c>
-      <c r="H28" s="110"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-    </row>
-    <row r="29" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="174"/>
-      <c r="D29" s="175"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="217" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="218"/>
-      <c r="E30" s="218"/>
-      <c r="F30" s="218"/>
-      <c r="G30" s="218"/>
-      <c r="H30" s="219"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C31" s="220"/>
-      <c r="D31" s="221"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="221"/>
-      <c r="G31" s="221"/>
-      <c r="H31" s="222"/>
-    </row>
-    <row r="32" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="223"/>
-      <c r="D32" s="224"/>
-      <c r="E32" s="224"/>
-      <c r="F32" s="224"/>
-      <c r="G32" s="224"/>
-      <c r="H32" s="225"/>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C13" s="207" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="208"/>
+      <c r="G13" s="208"/>
+      <c r="H13" s="209"/>
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="210"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="211"/>
+      <c r="H14" s="212"/>
+    </row>
+    <row r="15" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="213"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="214"/>
+      <c r="F15" s="214"/>
+      <c r="G15" s="214"/>
+      <c r="H15" s="215"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="C6:H8"/>
-    <mergeCell ref="C14:H16"/>
-    <mergeCell ref="C22:H24"/>
-    <mergeCell ref="C30:H32"/>
+    <mergeCell ref="C13:H15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7472,28 +7255,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6BF67-58D9-44B8-9885-F86EBBDE6C60}">
   <dimension ref="A7:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>162</v>
       </c>
-      <c r="D7" s="145">
+      <c r="D7" s="141">
         <v>712896.01</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>163</v>
       </c>
-      <c r="D8" s="145">
+      <c r="D8" s="141">
         <v>476368</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>164</v>
       </c>
@@ -7501,7 +7284,7 @@
         <v>13644</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>165</v>
       </c>
